--- a/grupos/1AV - Estadisticos 20231.xlsx
+++ b/grupos/1AV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="97">
   <si>
     <t>Materia</t>
   </si>
@@ -4026,13 +4026,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S39"/>
+  <dimension ref="A1:V39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:22">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>49</v>
@@ -4042,211 +4042,241 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="1"/>
+      <c r="I1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
-    </row>
-    <row r="2" spans="1:19">
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="P2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:22">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:22">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C4">
+        <v>100</v>
+      </c>
+      <c r="D4">
         <v>91.7</v>
       </c>
-      <c r="D4">
-        <v>100</v>
-      </c>
       <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4">
         <v>90</v>
       </c>
-      <c r="F4">
-        <v>100</v>
-      </c>
       <c r="G4">
+        <v>100</v>
+      </c>
+      <c r="H4">
         <v>70</v>
       </c>
-      <c r="H4">
-        <v>100</v>
-      </c>
       <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>100</v>
+      </c>
+      <c r="K4">
         <v>91.7</v>
       </c>
-      <c r="J4">
-        <v>100</v>
-      </c>
-      <c r="K4">
+      <c r="L4">
+        <v>100</v>
+      </c>
+      <c r="M4">
         <v>90</v>
       </c>
-      <c r="L4">
-        <v>100</v>
-      </c>
-      <c r="M4">
+      <c r="N4">
+        <v>100</v>
+      </c>
+      <c r="O4">
         <v>70</v>
       </c>
-      <c r="N4">
-        <v>100</v>
-      </c>
-      <c r="O4">
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>100</v>
+      </c>
+      <c r="R4">
         <v>91.7</v>
       </c>
-      <c r="P4">
-        <v>100</v>
-      </c>
-      <c r="Q4">
+      <c r="S4">
+        <v>100</v>
+      </c>
+      <c r="T4">
         <v>90</v>
       </c>
-      <c r="R4">
-        <v>100</v>
-      </c>
-      <c r="S4">
+      <c r="U4">
+        <v>100</v>
+      </c>
+      <c r="V4">
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:22">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C5">
+        <v>100</v>
+      </c>
+      <c r="D5">
         <v>91.7</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>6.7</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
       <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
         <v>80</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
       <c r="H5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>100</v>
+      </c>
+      <c r="K5">
         <v>91.7</v>
       </c>
-      <c r="J5">
+      <c r="L5">
         <v>6.7</v>
       </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
         <v>80</v>
       </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>100</v>
-      </c>
       <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>100</v>
+      </c>
+      <c r="R5">
         <v>91.7</v>
       </c>
-      <c r="P5">
+      <c r="S5">
         <v>6.7</v>
       </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
         <v>80</v>
       </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19">
+      <c r="V5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -4267,7 +4297,7 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -4288,7 +4318,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -4299,20 +4329,29 @@
       <c r="S6">
         <v>100</v>
       </c>
-    </row>
-    <row r="7" spans="1:19">
+      <c r="T6">
+        <v>100</v>
+      </c>
+      <c r="U6">
+        <v>100</v>
+      </c>
+      <c r="V6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C7">
+        <v>100</v>
+      </c>
+      <c r="D7">
         <v>91.7</v>
       </c>
-      <c r="D7">
-        <v>100</v>
-      </c>
       <c r="E7">
         <v>100</v>
       </c>
@@ -4320,51 +4359,60 @@
         <v>100</v>
       </c>
       <c r="G7">
+        <v>100</v>
+      </c>
+      <c r="H7">
         <v>85</v>
       </c>
-      <c r="H7">
-        <v>100</v>
-      </c>
       <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>100</v>
+      </c>
+      <c r="K7">
         <v>91.7</v>
       </c>
-      <c r="J7">
-        <v>100</v>
-      </c>
-      <c r="K7">
-        <v>100</v>
-      </c>
       <c r="L7">
         <v>100</v>
       </c>
       <c r="M7">
+        <v>100</v>
+      </c>
+      <c r="N7">
+        <v>100</v>
+      </c>
+      <c r="O7">
         <v>85</v>
       </c>
-      <c r="N7">
-        <v>100</v>
-      </c>
-      <c r="O7">
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>100</v>
+      </c>
+      <c r="R7">
         <v>91.7</v>
       </c>
-      <c r="P7">
-        <v>100</v>
-      </c>
-      <c r="Q7">
-        <v>100</v>
-      </c>
-      <c r="R7">
-        <v>100</v>
-      </c>
       <c r="S7">
+        <v>100</v>
+      </c>
+      <c r="T7">
+        <v>100</v>
+      </c>
+      <c r="U7">
+        <v>100</v>
+      </c>
+      <c r="V7">
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:22">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -4379,13 +4427,13 @@
         <v>100</v>
       </c>
       <c r="G8">
+        <v>100</v>
+      </c>
+      <c r="H8">
         <v>95</v>
       </c>
-      <c r="H8">
-        <v>100</v>
-      </c>
       <c r="I8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <v>100</v>
@@ -4397,16 +4445,16 @@
         <v>100</v>
       </c>
       <c r="M8">
+        <v>100</v>
+      </c>
+      <c r="N8">
+        <v>100</v>
+      </c>
+      <c r="O8">
         <v>95</v>
       </c>
-      <c r="N8">
-        <v>100</v>
-      </c>
-      <c r="O8">
-        <v>100</v>
-      </c>
       <c r="P8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -4415,74 +4463,92 @@
         <v>100</v>
       </c>
       <c r="S8">
+        <v>100</v>
+      </c>
+      <c r="T8">
+        <v>100</v>
+      </c>
+      <c r="U8">
+        <v>100</v>
+      </c>
+      <c r="V8">
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:22">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C9">
+        <v>100</v>
+      </c>
+      <c r="D9">
         <v>91.7</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>86.7</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>90</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>80</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>70</v>
       </c>
-      <c r="H9">
-        <v>100</v>
-      </c>
       <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>100</v>
+      </c>
+      <c r="K9">
         <v>91.7</v>
       </c>
-      <c r="J9">
+      <c r="L9">
         <v>86.7</v>
       </c>
-      <c r="K9">
+      <c r="M9">
         <v>90</v>
       </c>
-      <c r="L9">
+      <c r="N9">
         <v>80</v>
       </c>
-      <c r="M9">
+      <c r="O9">
         <v>70</v>
       </c>
-      <c r="N9">
-        <v>100</v>
-      </c>
-      <c r="O9">
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>100</v>
+      </c>
+      <c r="R9">
         <v>91.7</v>
       </c>
-      <c r="P9">
+      <c r="S9">
         <v>86.7</v>
       </c>
-      <c r="Q9">
+      <c r="T9">
         <v>90</v>
       </c>
-      <c r="R9">
+      <c r="U9">
         <v>80</v>
       </c>
-      <c r="S9">
+      <c r="V9">
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:22">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C10">
         <v>100</v>
@@ -4503,7 +4569,7 @@
         <v>100</v>
       </c>
       <c r="I10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J10">
         <v>100</v>
@@ -4524,7 +4590,7 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -4535,13 +4601,22 @@
       <c r="S10">
         <v>100</v>
       </c>
-    </row>
-    <row r="11" spans="1:19">
+      <c r="T10">
+        <v>100</v>
+      </c>
+      <c r="U10">
+        <v>100</v>
+      </c>
+      <c r="V10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -4550,175 +4625,202 @@
         <v>100</v>
       </c>
       <c r="E11">
+        <v>100</v>
+      </c>
+      <c r="F11">
         <v>90</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>86.7</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>70</v>
       </c>
-      <c r="H11">
-        <v>100</v>
-      </c>
       <c r="I11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J11">
         <v>100</v>
       </c>
       <c r="K11">
+        <v>100</v>
+      </c>
+      <c r="L11">
+        <v>100</v>
+      </c>
+      <c r="M11">
         <v>90</v>
       </c>
-      <c r="L11">
+      <c r="N11">
         <v>86.7</v>
       </c>
-      <c r="M11">
+      <c r="O11">
         <v>70</v>
       </c>
-      <c r="N11">
-        <v>100</v>
-      </c>
-      <c r="O11">
-        <v>100</v>
-      </c>
       <c r="P11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q11">
+        <v>100</v>
+      </c>
+      <c r="R11">
+        <v>100</v>
+      </c>
+      <c r="S11">
+        <v>100</v>
+      </c>
+      <c r="T11">
         <v>90</v>
       </c>
-      <c r="R11">
+      <c r="U11">
         <v>86.7</v>
       </c>
-      <c r="S11">
+      <c r="V11">
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:22">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C12">
+        <v>100</v>
+      </c>
+      <c r="D12">
         <v>91.7</v>
       </c>
-      <c r="D12">
-        <v>100</v>
-      </c>
       <c r="E12">
+        <v>100</v>
+      </c>
+      <c r="F12">
         <v>90</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>93.3</v>
       </c>
-      <c r="G12">
-        <v>100</v>
-      </c>
       <c r="H12">
         <v>100</v>
       </c>
       <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>100</v>
+      </c>
+      <c r="K12">
         <v>91.7</v>
       </c>
-      <c r="J12">
-        <v>100</v>
-      </c>
-      <c r="K12">
+      <c r="L12">
+        <v>100</v>
+      </c>
+      <c r="M12">
         <v>90</v>
       </c>
-      <c r="L12">
+      <c r="N12">
         <v>93.3</v>
       </c>
-      <c r="M12">
-        <v>100</v>
-      </c>
-      <c r="N12">
-        <v>100</v>
-      </c>
       <c r="O12">
+        <v>100</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>100</v>
+      </c>
+      <c r="R12">
         <v>91.7</v>
       </c>
-      <c r="P12">
-        <v>100</v>
-      </c>
-      <c r="Q12">
+      <c r="S12">
+        <v>100</v>
+      </c>
+      <c r="T12">
         <v>90</v>
       </c>
-      <c r="R12">
+      <c r="U12">
         <v>93.3</v>
       </c>
-      <c r="S12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19">
+      <c r="V12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C13">
+        <v>100</v>
+      </c>
+      <c r="D13">
         <v>95.8</v>
       </c>
-      <c r="D13">
-        <v>100</v>
-      </c>
       <c r="E13">
+        <v>100</v>
+      </c>
+      <c r="F13">
         <v>90</v>
       </c>
-      <c r="F13">
-        <v>100</v>
-      </c>
       <c r="G13">
+        <v>100</v>
+      </c>
+      <c r="H13">
         <v>95</v>
       </c>
-      <c r="H13">
-        <v>100</v>
-      </c>
       <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>100</v>
+      </c>
+      <c r="K13">
         <v>95.8</v>
       </c>
-      <c r="J13">
-        <v>100</v>
-      </c>
-      <c r="K13">
+      <c r="L13">
+        <v>100</v>
+      </c>
+      <c r="M13">
         <v>90</v>
       </c>
-      <c r="L13">
-        <v>100</v>
-      </c>
-      <c r="M13">
+      <c r="N13">
+        <v>100</v>
+      </c>
+      <c r="O13">
         <v>95</v>
       </c>
-      <c r="N13">
-        <v>100</v>
-      </c>
-      <c r="O13">
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>100</v>
+      </c>
+      <c r="R13">
         <v>95.8</v>
       </c>
-      <c r="P13">
-        <v>100</v>
-      </c>
-      <c r="Q13">
+      <c r="S13">
+        <v>100</v>
+      </c>
+      <c r="T13">
         <v>90</v>
       </c>
-      <c r="R13">
-        <v>100</v>
-      </c>
-      <c r="S13">
+      <c r="U13">
+        <v>100</v>
+      </c>
+      <c r="V13">
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:22">
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C14">
         <v>100</v>
@@ -4727,116 +4829,134 @@
         <v>100</v>
       </c>
       <c r="E14">
+        <v>100</v>
+      </c>
+      <c r="F14">
         <v>90</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>86.7</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>95</v>
       </c>
-      <c r="H14">
-        <v>100</v>
-      </c>
       <c r="I14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J14">
         <v>100</v>
       </c>
       <c r="K14">
+        <v>100</v>
+      </c>
+      <c r="L14">
+        <v>100</v>
+      </c>
+      <c r="M14">
         <v>90</v>
       </c>
-      <c r="L14">
+      <c r="N14">
         <v>86.7</v>
       </c>
-      <c r="M14">
+      <c r="O14">
         <v>95</v>
       </c>
-      <c r="N14">
-        <v>100</v>
-      </c>
-      <c r="O14">
-        <v>100</v>
-      </c>
       <c r="P14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q14">
+        <v>100</v>
+      </c>
+      <c r="R14">
+        <v>100</v>
+      </c>
+      <c r="S14">
+        <v>100</v>
+      </c>
+      <c r="T14">
         <v>90</v>
       </c>
-      <c r="R14">
+      <c r="U14">
         <v>86.7</v>
       </c>
-      <c r="S14">
+      <c r="V14">
         <v>95</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:22">
       <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C15">
+        <v>100</v>
+      </c>
+      <c r="D15">
         <v>91.7</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>13.3</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>10</v>
       </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
       <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
         <v>20</v>
       </c>
-      <c r="H15">
-        <v>100</v>
-      </c>
       <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>100</v>
+      </c>
+      <c r="K15">
         <v>91.7</v>
       </c>
-      <c r="J15">
+      <c r="L15">
         <v>13.3</v>
       </c>
-      <c r="K15">
+      <c r="M15">
         <v>10</v>
       </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
         <v>20</v>
       </c>
-      <c r="N15">
-        <v>100</v>
-      </c>
-      <c r="O15">
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>100</v>
+      </c>
+      <c r="R15">
         <v>91.7</v>
       </c>
-      <c r="P15">
+      <c r="S15">
         <v>13.3</v>
       </c>
-      <c r="Q15">
+      <c r="T15">
         <v>10</v>
       </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:22">
       <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -4845,57 +4965,66 @@
         <v>100</v>
       </c>
       <c r="E16">
+        <v>100</v>
+      </c>
+      <c r="F16">
         <v>90</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>86.7</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>70</v>
       </c>
-      <c r="H16">
-        <v>100</v>
-      </c>
       <c r="I16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J16">
         <v>100</v>
       </c>
       <c r="K16">
+        <v>100</v>
+      </c>
+      <c r="L16">
+        <v>100</v>
+      </c>
+      <c r="M16">
         <v>90</v>
       </c>
-      <c r="L16">
+      <c r="N16">
         <v>86.7</v>
       </c>
-      <c r="M16">
+      <c r="O16">
         <v>70</v>
       </c>
-      <c r="N16">
-        <v>100</v>
-      </c>
-      <c r="O16">
-        <v>100</v>
-      </c>
       <c r="P16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q16">
+        <v>100</v>
+      </c>
+      <c r="R16">
+        <v>100</v>
+      </c>
+      <c r="S16">
+        <v>100</v>
+      </c>
+      <c r="T16">
         <v>90</v>
       </c>
-      <c r="R16">
+      <c r="U16">
         <v>86.7</v>
       </c>
-      <c r="S16">
+      <c r="V16">
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:22">
       <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C17">
         <v>100</v>
@@ -4916,7 +5045,7 @@
         <v>100</v>
       </c>
       <c r="I17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J17">
         <v>100</v>
@@ -4937,7 +5066,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -4948,13 +5077,22 @@
       <c r="S17">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="1:19">
+      <c r="T17">
+        <v>100</v>
+      </c>
+      <c r="U17">
+        <v>100</v>
+      </c>
+      <c r="V17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C18">
         <v>100</v>
@@ -4969,13 +5107,13 @@
         <v>100</v>
       </c>
       <c r="G18">
+        <v>100</v>
+      </c>
+      <c r="H18">
         <v>70</v>
       </c>
-      <c r="H18">
-        <v>100</v>
-      </c>
       <c r="I18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J18">
         <v>100</v>
@@ -4987,16 +5125,16 @@
         <v>100</v>
       </c>
       <c r="M18">
+        <v>100</v>
+      </c>
+      <c r="N18">
+        <v>100</v>
+      </c>
+      <c r="O18">
         <v>70</v>
       </c>
-      <c r="N18">
-        <v>100</v>
-      </c>
-      <c r="O18">
-        <v>100</v>
-      </c>
       <c r="P18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -5005,15 +5143,24 @@
         <v>100</v>
       </c>
       <c r="S18">
+        <v>100</v>
+      </c>
+      <c r="T18">
+        <v>100</v>
+      </c>
+      <c r="U18">
+        <v>100</v>
+      </c>
+      <c r="V18">
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:22">
       <c r="A19" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -5034,7 +5181,7 @@
         <v>100</v>
       </c>
       <c r="I19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J19">
         <v>100</v>
@@ -5055,7 +5202,7 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -5066,20 +5213,29 @@
       <c r="S19">
         <v>100</v>
       </c>
-    </row>
-    <row r="20" spans="1:19">
+      <c r="T19">
+        <v>100</v>
+      </c>
+      <c r="U19">
+        <v>100</v>
+      </c>
+      <c r="V19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C20">
+        <v>100</v>
+      </c>
+      <c r="D20">
         <v>95.8</v>
       </c>
-      <c r="D20">
-        <v>100</v>
-      </c>
       <c r="E20">
         <v>100</v>
       </c>
@@ -5093,14 +5249,14 @@
         <v>100</v>
       </c>
       <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>100</v>
+      </c>
+      <c r="K20">
         <v>95.8</v>
       </c>
-      <c r="J20">
-        <v>100</v>
-      </c>
-      <c r="K20">
-        <v>100</v>
-      </c>
       <c r="L20">
         <v>100</v>
       </c>
@@ -5111,329 +5267,383 @@
         <v>100</v>
       </c>
       <c r="O20">
+        <v>100</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>100</v>
+      </c>
+      <c r="R20">
         <v>95.8</v>
       </c>
-      <c r="P20">
-        <v>100</v>
-      </c>
-      <c r="Q20">
-        <v>100</v>
-      </c>
-      <c r="R20">
-        <v>100</v>
-      </c>
       <c r="S20">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="1:19">
+      <c r="T20">
+        <v>100</v>
+      </c>
+      <c r="U20">
+        <v>100</v>
+      </c>
+      <c r="V20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B21">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C21">
+        <v>100</v>
+      </c>
+      <c r="D21">
         <v>91.7</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>86.7</v>
-      </c>
-      <c r="E21">
-        <v>80</v>
       </c>
       <c r="F21">
         <v>80</v>
       </c>
       <c r="G21">
+        <v>80</v>
+      </c>
+      <c r="H21">
         <v>20</v>
       </c>
-      <c r="H21">
-        <v>100</v>
-      </c>
       <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>100</v>
+      </c>
+      <c r="K21">
         <v>91.7</v>
       </c>
-      <c r="J21">
+      <c r="L21">
         <v>86.7</v>
       </c>
-      <c r="K21">
+      <c r="M21">
         <v>80</v>
       </c>
-      <c r="L21">
+      <c r="N21">
         <v>80</v>
       </c>
-      <c r="M21">
+      <c r="O21">
         <v>20</v>
       </c>
-      <c r="N21">
-        <v>100</v>
-      </c>
-      <c r="O21">
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>100</v>
+      </c>
+      <c r="R21">
         <v>91.7</v>
       </c>
-      <c r="P21">
+      <c r="S21">
         <v>86.7</v>
       </c>
-      <c r="Q21">
+      <c r="T21">
         <v>80</v>
       </c>
-      <c r="R21">
+      <c r="U21">
         <v>80</v>
       </c>
-      <c r="S21">
+      <c r="V21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:22">
       <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B22">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C22">
+        <v>100</v>
+      </c>
+      <c r="D22">
         <v>87.5</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>86.7</v>
-      </c>
-      <c r="E22">
-        <v>80</v>
       </c>
       <c r="F22">
         <v>80</v>
       </c>
       <c r="G22">
+        <v>80</v>
+      </c>
+      <c r="H22">
         <v>60</v>
       </c>
-      <c r="H22">
-        <v>100</v>
-      </c>
       <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>100</v>
+      </c>
+      <c r="K22">
         <v>87.5</v>
       </c>
-      <c r="J22">
+      <c r="L22">
         <v>86.7</v>
       </c>
-      <c r="K22">
+      <c r="M22">
         <v>80</v>
       </c>
-      <c r="L22">
+      <c r="N22">
         <v>80</v>
       </c>
-      <c r="M22">
+      <c r="O22">
         <v>60</v>
       </c>
-      <c r="N22">
-        <v>100</v>
-      </c>
-      <c r="O22">
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>100</v>
+      </c>
+      <c r="R22">
         <v>87.5</v>
       </c>
-      <c r="P22">
+      <c r="S22">
         <v>86.7</v>
       </c>
-      <c r="Q22">
+      <c r="T22">
         <v>80</v>
       </c>
-      <c r="R22">
+      <c r="U22">
         <v>80</v>
       </c>
-      <c r="S22">
+      <c r="V22">
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:22">
       <c r="A23" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C23">
+        <v>100</v>
+      </c>
+      <c r="D23">
         <v>87.5</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>86.7</v>
       </c>
-      <c r="E23">
-        <v>100</v>
-      </c>
       <c r="F23">
+        <v>100</v>
+      </c>
+      <c r="G23">
         <v>93.3</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>60</v>
       </c>
-      <c r="H23">
-        <v>100</v>
-      </c>
       <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>100</v>
+      </c>
+      <c r="K23">
         <v>87.5</v>
       </c>
-      <c r="J23">
+      <c r="L23">
         <v>86.7</v>
       </c>
-      <c r="K23">
-        <v>100</v>
-      </c>
-      <c r="L23">
+      <c r="M23">
+        <v>100</v>
+      </c>
+      <c r="N23">
         <v>93.3</v>
       </c>
-      <c r="M23">
+      <c r="O23">
         <v>60</v>
       </c>
-      <c r="N23">
-        <v>100</v>
-      </c>
-      <c r="O23">
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>100</v>
+      </c>
+      <c r="R23">
         <v>87.5</v>
       </c>
-      <c r="P23">
+      <c r="S23">
         <v>86.7</v>
       </c>
-      <c r="Q23">
-        <v>100</v>
-      </c>
-      <c r="R23">
+      <c r="T23">
+        <v>100</v>
+      </c>
+      <c r="U23">
         <v>93.3</v>
       </c>
-      <c r="S23">
+      <c r="V23">
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:22">
       <c r="A24" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C24">
+        <v>100</v>
+      </c>
+      <c r="D24">
         <v>87.5</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>86.7</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>70</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>73.3</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>60</v>
       </c>
-      <c r="H24">
-        <v>100</v>
-      </c>
       <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>100</v>
+      </c>
+      <c r="K24">
         <v>87.5</v>
       </c>
-      <c r="J24">
+      <c r="L24">
         <v>86.7</v>
       </c>
-      <c r="K24">
+      <c r="M24">
         <v>70</v>
       </c>
-      <c r="L24">
+      <c r="N24">
         <v>73.3</v>
       </c>
-      <c r="M24">
+      <c r="O24">
         <v>60</v>
       </c>
-      <c r="N24">
-        <v>100</v>
-      </c>
-      <c r="O24">
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>100</v>
+      </c>
+      <c r="R24">
         <v>87.5</v>
       </c>
-      <c r="P24">
+      <c r="S24">
         <v>86.7</v>
       </c>
-      <c r="Q24">
+      <c r="T24">
         <v>70</v>
       </c>
-      <c r="R24">
+      <c r="U24">
         <v>73.3</v>
       </c>
-      <c r="S24">
+      <c r="V24">
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:22">
       <c r="A25" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C25">
+        <v>100</v>
+      </c>
+      <c r="D25">
         <v>95.8</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>86.7</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>70</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>80</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>75</v>
       </c>
-      <c r="H25">
-        <v>100</v>
-      </c>
       <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>100</v>
+      </c>
+      <c r="K25">
         <v>95.8</v>
       </c>
-      <c r="J25">
+      <c r="L25">
         <v>86.7</v>
       </c>
-      <c r="K25">
+      <c r="M25">
         <v>70</v>
       </c>
-      <c r="L25">
+      <c r="N25">
         <v>80</v>
       </c>
-      <c r="M25">
+      <c r="O25">
         <v>75</v>
       </c>
-      <c r="N25">
-        <v>100</v>
-      </c>
-      <c r="O25">
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>100</v>
+      </c>
+      <c r="R25">
         <v>95.8</v>
       </c>
-      <c r="P25">
+      <c r="S25">
         <v>86.7</v>
       </c>
-      <c r="Q25">
+      <c r="T25">
         <v>70</v>
       </c>
-      <c r="R25">
+      <c r="U25">
         <v>80</v>
       </c>
-      <c r="S25">
+      <c r="V25">
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:22">
       <c r="A26" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B26">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C26">
+        <v>100</v>
+      </c>
+      <c r="D26">
         <v>95.8</v>
       </c>
-      <c r="D26">
-        <v>100</v>
-      </c>
       <c r="E26">
         <v>100</v>
       </c>
@@ -5441,169 +5651,196 @@
         <v>100</v>
       </c>
       <c r="G26">
+        <v>100</v>
+      </c>
+      <c r="H26">
         <v>90</v>
       </c>
-      <c r="H26">
-        <v>100</v>
-      </c>
       <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>100</v>
+      </c>
+      <c r="K26">
         <v>95.8</v>
       </c>
-      <c r="J26">
-        <v>100</v>
-      </c>
-      <c r="K26">
-        <v>100</v>
-      </c>
       <c r="L26">
         <v>100</v>
       </c>
       <c r="M26">
+        <v>100</v>
+      </c>
+      <c r="N26">
+        <v>100</v>
+      </c>
+      <c r="O26">
         <v>90</v>
       </c>
-      <c r="N26">
-        <v>100</v>
-      </c>
-      <c r="O26">
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>100</v>
+      </c>
+      <c r="R26">
         <v>95.8</v>
       </c>
-      <c r="P26">
-        <v>100</v>
-      </c>
-      <c r="Q26">
-        <v>100</v>
-      </c>
-      <c r="R26">
-        <v>100</v>
-      </c>
       <c r="S26">
+        <v>100</v>
+      </c>
+      <c r="T26">
+        <v>100</v>
+      </c>
+      <c r="U26">
+        <v>100</v>
+      </c>
+      <c r="V26">
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:22">
       <c r="A27" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C27">
+        <v>100</v>
+      </c>
+      <c r="D27">
         <v>95.8</v>
       </c>
-      <c r="D27">
-        <v>100</v>
-      </c>
       <c r="E27">
+        <v>100</v>
+      </c>
+      <c r="F27">
         <v>90</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>93.3</v>
       </c>
-      <c r="G27">
-        <v>100</v>
-      </c>
       <c r="H27">
         <v>100</v>
       </c>
       <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>100</v>
+      </c>
+      <c r="K27">
         <v>95.8</v>
       </c>
-      <c r="J27">
-        <v>100</v>
-      </c>
-      <c r="K27">
+      <c r="L27">
+        <v>100</v>
+      </c>
+      <c r="M27">
         <v>90</v>
       </c>
-      <c r="L27">
+      <c r="N27">
         <v>93.3</v>
       </c>
-      <c r="M27">
-        <v>100</v>
-      </c>
-      <c r="N27">
-        <v>100</v>
-      </c>
       <c r="O27">
+        <v>100</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>100</v>
+      </c>
+      <c r="R27">
         <v>95.8</v>
       </c>
-      <c r="P27">
-        <v>100</v>
-      </c>
-      <c r="Q27">
+      <c r="S27">
+        <v>100</v>
+      </c>
+      <c r="T27">
         <v>90</v>
       </c>
-      <c r="R27">
+      <c r="U27">
         <v>93.3</v>
       </c>
-      <c r="S27">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19">
+      <c r="V27">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
       <c r="A28" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B28">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C28">
+        <v>100</v>
+      </c>
+      <c r="D28">
         <v>91.7</v>
       </c>
-      <c r="D28">
-        <v>100</v>
-      </c>
       <c r="E28">
         <v>100</v>
       </c>
       <c r="F28">
+        <v>100</v>
+      </c>
+      <c r="G28">
         <v>93.3</v>
       </c>
-      <c r="G28">
-        <v>100</v>
-      </c>
       <c r="H28">
         <v>100</v>
       </c>
       <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>100</v>
+      </c>
+      <c r="K28">
         <v>91.7</v>
       </c>
-      <c r="J28">
-        <v>100</v>
-      </c>
-      <c r="K28">
-        <v>100</v>
-      </c>
       <c r="L28">
+        <v>100</v>
+      </c>
+      <c r="M28">
+        <v>100</v>
+      </c>
+      <c r="N28">
         <v>93.3</v>
       </c>
-      <c r="M28">
-        <v>100</v>
-      </c>
-      <c r="N28">
-        <v>100</v>
-      </c>
       <c r="O28">
+        <v>100</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>100</v>
+      </c>
+      <c r="R28">
         <v>91.7</v>
       </c>
-      <c r="P28">
-        <v>100</v>
-      </c>
-      <c r="Q28">
-        <v>100</v>
-      </c>
-      <c r="R28">
+      <c r="S28">
+        <v>100</v>
+      </c>
+      <c r="T28">
+        <v>100</v>
+      </c>
+      <c r="U28">
         <v>93.3</v>
       </c>
-      <c r="S28">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19">
+      <c r="V28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
       <c r="A29" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B29">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C29">
         <v>100</v>
@@ -5612,57 +5849,66 @@
         <v>100</v>
       </c>
       <c r="E29">
+        <v>100</v>
+      </c>
+      <c r="F29">
         <v>80</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>93.3</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>95</v>
       </c>
-      <c r="H29">
-        <v>100</v>
-      </c>
       <c r="I29">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J29">
         <v>100</v>
       </c>
       <c r="K29">
+        <v>100</v>
+      </c>
+      <c r="L29">
+        <v>100</v>
+      </c>
+      <c r="M29">
         <v>80</v>
       </c>
-      <c r="L29">
+      <c r="N29">
         <v>93.3</v>
       </c>
-      <c r="M29">
+      <c r="O29">
         <v>95</v>
       </c>
-      <c r="N29">
-        <v>100</v>
-      </c>
-      <c r="O29">
-        <v>100</v>
-      </c>
       <c r="P29">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q29">
+        <v>100</v>
+      </c>
+      <c r="R29">
+        <v>100</v>
+      </c>
+      <c r="S29">
+        <v>100</v>
+      </c>
+      <c r="T29">
         <v>80</v>
       </c>
-      <c r="R29">
+      <c r="U29">
         <v>93.3</v>
       </c>
-      <c r="S29">
+      <c r="V29">
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:22">
       <c r="A30" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C30">
         <v>100</v>
@@ -5671,300 +5917,345 @@
         <v>100</v>
       </c>
       <c r="E30">
+        <v>100</v>
+      </c>
+      <c r="F30">
         <v>90</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>93.3</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>95</v>
       </c>
-      <c r="H30">
-        <v>100</v>
-      </c>
       <c r="I30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J30">
         <v>100</v>
       </c>
       <c r="K30">
+        <v>100</v>
+      </c>
+      <c r="L30">
+        <v>100</v>
+      </c>
+      <c r="M30">
         <v>90</v>
       </c>
-      <c r="L30">
+      <c r="N30">
         <v>93.3</v>
       </c>
-      <c r="M30">
+      <c r="O30">
         <v>95</v>
       </c>
-      <c r="N30">
-        <v>100</v>
-      </c>
-      <c r="O30">
-        <v>100</v>
-      </c>
       <c r="P30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q30">
+        <v>100</v>
+      </c>
+      <c r="R30">
+        <v>100</v>
+      </c>
+      <c r="S30">
+        <v>100</v>
+      </c>
+      <c r="T30">
         <v>90</v>
       </c>
-      <c r="R30">
+      <c r="U30">
         <v>93.3</v>
       </c>
-      <c r="S30">
+      <c r="V30">
         <v>95</v>
       </c>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:22">
       <c r="A31" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B31">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C31">
+        <v>100</v>
+      </c>
+      <c r="D31">
         <v>95.8</v>
       </c>
-      <c r="D31">
-        <v>100</v>
-      </c>
       <c r="E31">
         <v>100</v>
       </c>
       <c r="F31">
+        <v>100</v>
+      </c>
+      <c r="G31">
         <v>86.7</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>80</v>
       </c>
-      <c r="H31">
-        <v>100</v>
-      </c>
       <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>100</v>
+      </c>
+      <c r="K31">
         <v>95.8</v>
       </c>
-      <c r="J31">
-        <v>100</v>
-      </c>
-      <c r="K31">
-        <v>100</v>
-      </c>
       <c r="L31">
+        <v>100</v>
+      </c>
+      <c r="M31">
+        <v>100</v>
+      </c>
+      <c r="N31">
         <v>86.7</v>
       </c>
-      <c r="M31">
+      <c r="O31">
         <v>80</v>
       </c>
-      <c r="N31">
-        <v>100</v>
-      </c>
-      <c r="O31">
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>100</v>
+      </c>
+      <c r="R31">
         <v>95.8</v>
       </c>
-      <c r="P31">
-        <v>100</v>
-      </c>
-      <c r="Q31">
-        <v>100</v>
-      </c>
-      <c r="R31">
+      <c r="S31">
+        <v>100</v>
+      </c>
+      <c r="T31">
+        <v>100</v>
+      </c>
+      <c r="U31">
         <v>86.7</v>
       </c>
-      <c r="S31">
+      <c r="V31">
         <v>80</v>
       </c>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:22">
       <c r="A32" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B32">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C32">
+        <v>100</v>
+      </c>
+      <c r="D32">
         <v>95.8</v>
       </c>
-      <c r="D32">
-        <v>100</v>
-      </c>
       <c r="E32">
+        <v>100</v>
+      </c>
+      <c r="F32">
         <v>90</v>
       </c>
-      <c r="F32">
+      <c r="G32">
         <v>86.7</v>
       </c>
-      <c r="G32">
-        <v>100</v>
-      </c>
       <c r="H32">
         <v>100</v>
       </c>
       <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>100</v>
+      </c>
+      <c r="K32">
         <v>95.8</v>
       </c>
-      <c r="J32">
-        <v>100</v>
-      </c>
-      <c r="K32">
+      <c r="L32">
+        <v>100</v>
+      </c>
+      <c r="M32">
         <v>90</v>
       </c>
-      <c r="L32">
+      <c r="N32">
         <v>86.7</v>
       </c>
-      <c r="M32">
-        <v>100</v>
-      </c>
-      <c r="N32">
-        <v>100</v>
-      </c>
       <c r="O32">
+        <v>100</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>100</v>
+      </c>
+      <c r="R32">
         <v>95.8</v>
       </c>
-      <c r="P32">
-        <v>100</v>
-      </c>
-      <c r="Q32">
+      <c r="S32">
+        <v>100</v>
+      </c>
+      <c r="T32">
         <v>90</v>
       </c>
-      <c r="R32">
+      <c r="U32">
         <v>86.7</v>
       </c>
-      <c r="S32">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19">
+      <c r="V32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22">
       <c r="A33" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B33">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C33">
+        <v>100</v>
+      </c>
+      <c r="D33">
         <v>95.8</v>
       </c>
-      <c r="D33">
-        <v>100</v>
-      </c>
       <c r="E33">
+        <v>100</v>
+      </c>
+      <c r="F33">
         <v>80</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>86.7</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>90</v>
       </c>
-      <c r="H33">
-        <v>100</v>
-      </c>
       <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>100</v>
+      </c>
+      <c r="K33">
         <v>95.8</v>
       </c>
-      <c r="J33">
-        <v>100</v>
-      </c>
-      <c r="K33">
+      <c r="L33">
+        <v>100</v>
+      </c>
+      <c r="M33">
         <v>80</v>
       </c>
-      <c r="L33">
+      <c r="N33">
         <v>86.7</v>
       </c>
-      <c r="M33">
+      <c r="O33">
         <v>90</v>
       </c>
-      <c r="N33">
-        <v>100</v>
-      </c>
-      <c r="O33">
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>100</v>
+      </c>
+      <c r="R33">
         <v>95.8</v>
       </c>
-      <c r="P33">
-        <v>100</v>
-      </c>
-      <c r="Q33">
+      <c r="S33">
+        <v>100</v>
+      </c>
+      <c r="T33">
         <v>80</v>
       </c>
-      <c r="R33">
+      <c r="U33">
         <v>86.7</v>
       </c>
-      <c r="S33">
+      <c r="V33">
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:22">
       <c r="A34" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B34">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C34">
+        <v>100</v>
+      </c>
+      <c r="D34">
         <v>87.5</v>
       </c>
-      <c r="D34">
+      <c r="E34">
         <v>6.7</v>
       </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
       <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
         <v>80</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>45</v>
       </c>
-      <c r="H34">
-        <v>100</v>
-      </c>
       <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>100</v>
+      </c>
+      <c r="K34">
         <v>87.5</v>
       </c>
-      <c r="J34">
+      <c r="L34">
         <v>6.7</v>
       </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34">
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
         <v>80</v>
       </c>
-      <c r="M34">
+      <c r="O34">
         <v>45</v>
       </c>
-      <c r="N34">
-        <v>100</v>
-      </c>
-      <c r="O34">
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>100</v>
+      </c>
+      <c r="R34">
         <v>87.5</v>
       </c>
-      <c r="P34">
+      <c r="S34">
         <v>6.7</v>
       </c>
-      <c r="Q34">
-        <v>0</v>
-      </c>
-      <c r="R34">
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
         <v>80</v>
       </c>
-      <c r="S34">
+      <c r="V34">
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:22">
       <c r="A35" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B35">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C35">
+        <v>100</v>
+      </c>
+      <c r="D35">
         <v>95.8</v>
       </c>
-      <c r="D35">
-        <v>100</v>
-      </c>
       <c r="E35">
         <v>100</v>
       </c>
@@ -5978,14 +6269,14 @@
         <v>100</v>
       </c>
       <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>100</v>
+      </c>
+      <c r="K35">
         <v>95.8</v>
       </c>
-      <c r="J35">
-        <v>100</v>
-      </c>
-      <c r="K35">
-        <v>100</v>
-      </c>
       <c r="L35">
         <v>100</v>
       </c>
@@ -5996,86 +6287,104 @@
         <v>100</v>
       </c>
       <c r="O35">
+        <v>100</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>100</v>
+      </c>
+      <c r="R35">
         <v>95.8</v>
       </c>
-      <c r="P35">
-        <v>100</v>
-      </c>
-      <c r="Q35">
-        <v>100</v>
-      </c>
-      <c r="R35">
-        <v>100</v>
-      </c>
       <c r="S35">
         <v>100</v>
       </c>
-    </row>
-    <row r="36" spans="1:19">
+      <c r="T35">
+        <v>100</v>
+      </c>
+      <c r="U35">
+        <v>100</v>
+      </c>
+      <c r="V35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22">
       <c r="A36" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B36">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C36">
+        <v>100</v>
+      </c>
+      <c r="D36">
         <v>95.8</v>
       </c>
-      <c r="D36">
-        <v>100</v>
-      </c>
       <c r="E36">
+        <v>100</v>
+      </c>
+      <c r="F36">
         <v>90</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>93.3</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>85</v>
       </c>
-      <c r="H36">
-        <v>100</v>
-      </c>
       <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>100</v>
+      </c>
+      <c r="K36">
         <v>95.8</v>
       </c>
-      <c r="J36">
-        <v>100</v>
-      </c>
-      <c r="K36">
+      <c r="L36">
+        <v>100</v>
+      </c>
+      <c r="M36">
         <v>90</v>
       </c>
-      <c r="L36">
+      <c r="N36">
         <v>93.3</v>
       </c>
-      <c r="M36">
+      <c r="O36">
         <v>85</v>
       </c>
-      <c r="N36">
-        <v>100</v>
-      </c>
-      <c r="O36">
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>100</v>
+      </c>
+      <c r="R36">
         <v>95.8</v>
       </c>
-      <c r="P36">
-        <v>100</v>
-      </c>
-      <c r="Q36">
+      <c r="S36">
+        <v>100</v>
+      </c>
+      <c r="T36">
         <v>90</v>
       </c>
-      <c r="R36">
+      <c r="U36">
         <v>93.3</v>
       </c>
-      <c r="S36">
+      <c r="V36">
         <v>85</v>
       </c>
     </row>
-    <row r="37" spans="1:19">
+    <row r="37" spans="1:22">
       <c r="A37" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B37">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C37">
         <v>100</v>
@@ -6096,7 +6405,7 @@
         <v>100</v>
       </c>
       <c r="I37">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J37">
         <v>100</v>
@@ -6117,7 +6426,7 @@
         <v>100</v>
       </c>
       <c r="P37">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q37">
         <v>100</v>
@@ -6128,26 +6437,35 @@
       <c r="S37">
         <v>100</v>
       </c>
-    </row>
-    <row r="38" spans="1:19">
+      <c r="T37">
+        <v>100</v>
+      </c>
+      <c r="U37">
+        <v>100</v>
+      </c>
+      <c r="V37">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22">
       <c r="A38" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C38">
+        <v>100</v>
+      </c>
+      <c r="D38">
         <v>83.3</v>
       </c>
-      <c r="D38">
+      <c r="E38">
         <v>86.7</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <v>80</v>
       </c>
-      <c r="F38">
-        <v>100</v>
-      </c>
       <c r="G38">
         <v>100</v>
       </c>
@@ -6155,45 +6473,54 @@
         <v>100</v>
       </c>
       <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>100</v>
+      </c>
+      <c r="K38">
         <v>83.3</v>
       </c>
-      <c r="J38">
+      <c r="L38">
         <v>86.7</v>
       </c>
-      <c r="K38">
+      <c r="M38">
         <v>80</v>
       </c>
-      <c r="L38">
-        <v>100</v>
-      </c>
-      <c r="M38">
-        <v>100</v>
-      </c>
       <c r="N38">
         <v>100</v>
       </c>
       <c r="O38">
+        <v>100</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>100</v>
+      </c>
+      <c r="R38">
         <v>83.3</v>
       </c>
-      <c r="P38">
+      <c r="S38">
         <v>86.7</v>
       </c>
-      <c r="Q38">
+      <c r="T38">
         <v>80</v>
       </c>
-      <c r="R38">
-        <v>100</v>
-      </c>
-      <c r="S38">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19">
+      <c r="U38">
+        <v>100</v>
+      </c>
+      <c r="V38">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22">
       <c r="A39" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B39">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C39">
         <v>100</v>
@@ -6202,56 +6529,65 @@
         <v>100</v>
       </c>
       <c r="E39">
+        <v>100</v>
+      </c>
+      <c r="F39">
         <v>90</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <v>86.7</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <v>65</v>
       </c>
-      <c r="H39">
-        <v>100</v>
-      </c>
       <c r="I39">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J39">
         <v>100</v>
       </c>
       <c r="K39">
+        <v>100</v>
+      </c>
+      <c r="L39">
+        <v>100</v>
+      </c>
+      <c r="M39">
         <v>90</v>
       </c>
-      <c r="L39">
+      <c r="N39">
         <v>86.7</v>
       </c>
-      <c r="M39">
+      <c r="O39">
         <v>65</v>
       </c>
-      <c r="N39">
-        <v>100</v>
-      </c>
-      <c r="O39">
-        <v>100</v>
-      </c>
       <c r="P39">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q39">
+        <v>100</v>
+      </c>
+      <c r="R39">
+        <v>100</v>
+      </c>
+      <c r="S39">
+        <v>100</v>
+      </c>
+      <c r="T39">
         <v>90</v>
       </c>
-      <c r="R39">
+      <c r="U39">
         <v>86.7</v>
       </c>
-      <c r="S39">
+      <c r="V39">
         <v>65</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="N1:S1"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="P1:V1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/1AV - Estadisticos 20231.xlsx
+++ b/grupos/1AV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="97">
   <si>
     <t>Materia</t>
   </si>
@@ -212,21 +212,21 @@
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
     <t>Saucedo Rivalcoba Graciela</t>
   </si>
   <si>
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
+    <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
     <t>Rivera Serra Alma Lilian</t>
   </si>
   <si>
@@ -242,73 +242,73 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BUSTOS</t>
+  </si>
+  <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>LARA</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>BUSTOS</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DAMIAN</t>
   </si>
   <si>
     <t>GUEVARA</t>
   </si>
   <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DAMIAN</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>VILLA</t>
   </si>
   <si>
     <t>AUTRAN</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>JOSE EMILIANO</t>
+  </si>
+  <si>
+    <t>JESUS JAREF</t>
   </si>
   <si>
     <t>NATANAHEL</t>
   </si>
   <si>
-    <t>ROBBIE ALONSO</t>
-  </si>
-  <si>
-    <t>JOSE EMILIANO</t>
-  </si>
-  <si>
-    <t>JESUS JAREF</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>LUIS FABIAN</t>
+  </si>
+  <si>
+    <t>ALEX URIEL</t>
   </si>
   <si>
     <t>AXEL AARON</t>
   </si>
   <si>
-    <t>KEVYN DANIEL</t>
-  </si>
-  <si>
-    <t>LUIS FABIAN</t>
+    <t>SABDY</t>
   </si>
 </sst>
 </file>
@@ -835,22 +835,22 @@
         <v>5</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -880,19 +880,19 @@
         <v>5</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>5</v>
       </c>
       <c r="Z4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA4">
         <v>5</v>
       </c>
       <c r="AB4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC4">
         <v>5</v>
@@ -924,22 +924,22 @@
         <v>5</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -969,7 +969,7 @@
         <v>5</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -1013,22 +1013,22 @@
         <v>7</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -1058,13 +1058,13 @@
         <v>7</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y6">
         <v>6</v>
       </c>
       <c r="Z6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA6">
         <v>10</v>
@@ -1102,22 +1102,22 @@
         <v>6</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -1144,19 +1144,19 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>5</v>
       </c>
       <c r="Z7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB7">
         <v>9</v>
@@ -1191,22 +1191,22 @@
         <v>6</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -1233,13 +1233,13 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z8">
         <v>9</v>
@@ -1248,7 +1248,7 @@
         <v>5</v>
       </c>
       <c r="AB8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC8">
         <v>6</v>
@@ -1259,7 +1259,7 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C9">
         <v>6</v>
@@ -1283,19 +1283,19 @@
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -1322,7 +1322,7 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X9">
         <v>6</v>
@@ -1334,7 +1334,7 @@
         <v>5</v>
       </c>
       <c r="AA9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB9">
         <v>5</v>
@@ -1369,22 +1369,22 @@
         <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -1414,13 +1414,13 @@
         <v>8</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>6</v>
       </c>
       <c r="Z10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA10">
         <v>10</v>
@@ -1458,22 +1458,22 @@
         <v>5</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -1506,16 +1506,16 @@
         <v>7</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA11">
         <v>5</v>
       </c>
       <c r="AB11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC11">
         <v>5</v>
@@ -1547,22 +1547,22 @@
         <v>7</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -1595,13 +1595,13 @@
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB12">
         <v>5</v>
@@ -1636,22 +1636,22 @@
         <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -1678,16 +1678,16 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA13">
         <v>5</v>
@@ -1725,22 +1725,22 @@
         <v>7</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -1767,10 +1767,10 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>8</v>
@@ -1814,22 +1814,22 @@
         <v>5</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -1859,7 +1859,7 @@
         <v>5</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y15">
         <v>5</v>
@@ -1903,22 +1903,22 @@
         <v>5</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -1948,13 +1948,13 @@
         <v>5</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA16">
         <v>5</v>
@@ -1992,22 +1992,22 @@
         <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -2037,19 +2037,19 @@
         <v>5</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA17">
         <v>9</v>
       </c>
       <c r="AB17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC17">
         <v>6</v>
@@ -2081,22 +2081,22 @@
         <v>6</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -2126,16 +2126,16 @@
         <v>5</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z18">
         <v>5</v>
       </c>
       <c r="AA18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB18">
         <v>5</v>
@@ -2170,22 +2170,22 @@
         <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -2218,16 +2218,16 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA19">
         <v>5</v>
       </c>
       <c r="AB19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC19">
         <v>7</v>
@@ -2259,22 +2259,22 @@
         <v>7</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -2301,10 +2301,10 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -2313,10 +2313,10 @@
         <v>10</v>
       </c>
       <c r="AA20">
+        <v>10</v>
+      </c>
+      <c r="AB20">
         <v>9</v>
-      </c>
-      <c r="AB20">
-        <v>8</v>
       </c>
       <c r="AC20">
         <v>7</v>
@@ -2348,22 +2348,22 @@
         <v>5</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -2437,22 +2437,22 @@
         <v>5</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -2482,16 +2482,16 @@
         <v>5</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>5</v>
       </c>
       <c r="Z22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA22">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB22">
         <v>5</v>
@@ -2526,22 +2526,22 @@
         <v>5</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -2577,7 +2577,7 @@
         <v>5</v>
       </c>
       <c r="Z23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA23">
         <v>5</v>
@@ -2615,22 +2615,22 @@
         <v>5</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O24">
         <v>-1</v>
@@ -2660,7 +2660,7 @@
         <v>5</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -2704,22 +2704,22 @@
         <v>5</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O25">
         <v>-1</v>
@@ -2749,10 +2749,10 @@
         <v>5</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z25">
         <v>5</v>
@@ -2793,22 +2793,22 @@
         <v>7</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O26">
         <v>-1</v>
@@ -2835,7 +2835,7 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>7</v>
@@ -2844,10 +2844,10 @@
         <v>6</v>
       </c>
       <c r="Z26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB26">
         <v>9</v>
@@ -2882,22 +2882,22 @@
         <v>7</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
         <v>-1</v>
@@ -2927,13 +2927,13 @@
         <v>5</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA27">
         <v>5</v>
@@ -2971,22 +2971,22 @@
         <v>7</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
         <v>-1</v>
@@ -3013,16 +3013,16 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA28">
         <v>9</v>
@@ -3060,22 +3060,22 @@
         <v>6</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O29">
         <v>-1</v>
@@ -3105,13 +3105,13 @@
         <v>5</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA29">
         <v>5</v>
@@ -3149,22 +3149,22 @@
         <v>6</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
         <v>-1</v>
@@ -3194,19 +3194,19 @@
         <v>8</v>
       </c>
       <c r="X30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y30">
         <v>7</v>
       </c>
       <c r="Z30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AB30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC30">
         <v>6</v>
@@ -3238,22 +3238,22 @@
         <v>6</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O31">
         <v>-1</v>
@@ -3283,16 +3283,16 @@
         <v>5</v>
       </c>
       <c r="X31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB31">
         <v>5</v>
@@ -3327,22 +3327,22 @@
         <v>7</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O32">
         <v>-1</v>
@@ -3369,16 +3369,16 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X32">
         <v>7</v>
       </c>
       <c r="Y32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA32">
         <v>5</v>
@@ -3416,22 +3416,22 @@
         <v>7</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O33">
         <v>-1</v>
@@ -3461,19 +3461,19 @@
         <v>5</v>
       </c>
       <c r="X33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z33">
         <v>10</v>
       </c>
       <c r="AA33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC33">
         <v>7</v>
@@ -3505,22 +3505,22 @@
         <v>5</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O34">
         <v>-1</v>
@@ -3550,7 +3550,7 @@
         <v>5</v>
       </c>
       <c r="X34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y34">
         <v>5</v>
@@ -3594,22 +3594,22 @@
         <v>7</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
         <v>-1</v>
@@ -3636,7 +3636,7 @@
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X35">
         <v>7</v>
@@ -3648,7 +3648,7 @@
         <v>9</v>
       </c>
       <c r="AA35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB35">
         <v>10</v>
@@ -3683,22 +3683,22 @@
         <v>5</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O36">
         <v>-1</v>
@@ -3731,10 +3731,10 @@
         <v>7</v>
       </c>
       <c r="Y36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z36">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA36">
         <v>5</v>
@@ -3772,22 +3772,22 @@
         <v>8</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
         <v>-1</v>
@@ -3826,7 +3826,7 @@
         <v>9</v>
       </c>
       <c r="AA37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB37">
         <v>10</v>
@@ -3861,22 +3861,22 @@
         <v>6</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O38">
         <v>-1</v>
@@ -3912,7 +3912,7 @@
         <v>5</v>
       </c>
       <c r="Z38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA38">
         <v>5</v>
@@ -3950,22 +3950,22 @@
         <v>5</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O39">
         <v>-1</v>
@@ -3992,13 +3992,13 @@
         <v>-1</v>
       </c>
       <c r="W39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z39">
         <v>8</v>
@@ -4007,7 +4007,7 @@
         <v>5</v>
       </c>
       <c r="AB39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC39">
         <v>5</v>
@@ -4140,7 +4140,7 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -4161,43 +4161,43 @@
         <v>70</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="J4">
         <v>100</v>
       </c>
       <c r="K4">
-        <v>91.7</v>
+        <v>50</v>
       </c>
       <c r="L4">
-        <v>100</v>
+        <v>45.5</v>
       </c>
       <c r="M4">
-        <v>90</v>
+        <v>82.5</v>
       </c>
       <c r="N4">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O4">
         <v>70</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="Q4">
         <v>100</v>
       </c>
       <c r="R4">
-        <v>91.7</v>
+        <v>50</v>
       </c>
       <c r="S4">
-        <v>100</v>
+        <v>45.5</v>
       </c>
       <c r="T4">
-        <v>90</v>
+        <v>82.5</v>
       </c>
       <c r="U4">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="V4">
         <v>70</v>
@@ -4208,7 +4208,7 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -4229,43 +4229,43 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J5">
         <v>100</v>
       </c>
       <c r="K5">
-        <v>91.7</v>
+        <v>50</v>
       </c>
       <c r="L5">
-        <v>6.7</v>
+        <v>3</v>
       </c>
       <c r="M5">
         <v>0</v>
       </c>
       <c r="N5">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Q5">
         <v>100</v>
       </c>
       <c r="R5">
-        <v>91.7</v>
+        <v>50</v>
       </c>
       <c r="S5">
-        <v>6.7</v>
+        <v>3</v>
       </c>
       <c r="T5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V5">
         <v>0</v>
@@ -4276,7 +4276,7 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -4297,13 +4297,13 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J6">
         <v>100</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="L6">
         <v>100</v>
@@ -4318,13 +4318,13 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q6">
         <v>100</v>
       </c>
       <c r="R6">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -4344,7 +4344,7 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -4365,13 +4365,13 @@
         <v>85</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J7">
         <v>100</v>
       </c>
       <c r="K7">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L7">
         <v>100</v>
@@ -4386,13 +4386,13 @@
         <v>85</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q7">
         <v>100</v>
       </c>
       <c r="R7">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -4412,7 +4412,7 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -4433,13 +4433,13 @@
         <v>95</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J8">
         <v>100</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L8">
         <v>100</v>
@@ -4454,13 +4454,13 @@
         <v>95</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q8">
         <v>100</v>
       </c>
       <c r="R8">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -4480,7 +4480,7 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -4501,19 +4501,19 @@
         <v>70</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J9">
         <v>100</v>
       </c>
       <c r="K9">
-        <v>91.7</v>
+        <v>68.2</v>
       </c>
       <c r="L9">
-        <v>86.7</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="M9">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="N9">
         <v>80</v>
@@ -4522,19 +4522,19 @@
         <v>70</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="Q9">
         <v>100</v>
       </c>
       <c r="R9">
-        <v>91.7</v>
+        <v>68.2</v>
       </c>
       <c r="S9">
-        <v>86.7</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="T9">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="U9">
         <v>80</v>
@@ -4548,7 +4548,7 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C10">
         <v>100</v>
@@ -4569,7 +4569,7 @@
         <v>100</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J10">
         <v>100</v>
@@ -4590,7 +4590,7 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -4616,7 +4616,7 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -4637,43 +4637,43 @@
         <v>70</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J11">
         <v>100</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L11">
         <v>100</v>
       </c>
       <c r="M11">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N11">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="O11">
         <v>70</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q11">
         <v>100</v>
       </c>
       <c r="R11">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="S11">
         <v>100</v>
       </c>
       <c r="T11">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="U11">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="V11">
         <v>70</v>
@@ -4684,7 +4684,7 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C12">
         <v>100</v>
@@ -4705,43 +4705,43 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J12">
         <v>100</v>
       </c>
       <c r="K12">
-        <v>91.7</v>
+        <v>79.5</v>
       </c>
       <c r="L12">
         <v>100</v>
       </c>
       <c r="M12">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="N12">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="O12">
         <v>100</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q12">
         <v>100</v>
       </c>
       <c r="R12">
-        <v>91.7</v>
+        <v>79.5</v>
       </c>
       <c r="S12">
         <v>100</v>
       </c>
       <c r="T12">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="U12">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="V12">
         <v>100</v>
@@ -4752,7 +4752,7 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -4773,19 +4773,19 @@
         <v>95</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J13">
         <v>100</v>
       </c>
       <c r="K13">
-        <v>95.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L13">
         <v>100</v>
       </c>
       <c r="M13">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="N13">
         <v>100</v>
@@ -4794,19 +4794,19 @@
         <v>95</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q13">
         <v>100</v>
       </c>
       <c r="R13">
-        <v>95.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S13">
         <v>100</v>
       </c>
       <c r="T13">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="U13">
         <v>100</v>
@@ -4820,7 +4820,7 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C14">
         <v>100</v>
@@ -4841,43 +4841,43 @@
         <v>95</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J14">
         <v>100</v>
       </c>
       <c r="K14">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="L14">
         <v>100</v>
       </c>
       <c r="M14">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N14">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="O14">
         <v>95</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q14">
         <v>100</v>
       </c>
       <c r="R14">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="S14">
         <v>100</v>
       </c>
       <c r="T14">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="U14">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="V14">
         <v>95</v>
@@ -4888,7 +4888,7 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -4909,19 +4909,19 @@
         <v>20</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J15">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="K15">
-        <v>91.7</v>
+        <v>50</v>
       </c>
       <c r="L15">
-        <v>13.3</v>
+        <v>6.1</v>
       </c>
       <c r="M15">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -4930,19 +4930,19 @@
         <v>20</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="Q15">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="R15">
-        <v>91.7</v>
+        <v>50</v>
       </c>
       <c r="S15">
-        <v>13.3</v>
+        <v>6.1</v>
       </c>
       <c r="T15">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U15">
         <v>0</v>
@@ -4956,7 +4956,7 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -4977,43 +4977,43 @@
         <v>70</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J16">
         <v>100</v>
       </c>
       <c r="K16">
-        <v>100</v>
+        <v>81.8</v>
       </c>
       <c r="L16">
         <v>100</v>
       </c>
       <c r="M16">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="N16">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="O16">
         <v>70</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q16">
         <v>100</v>
       </c>
       <c r="R16">
-        <v>100</v>
+        <v>81.8</v>
       </c>
       <c r="S16">
         <v>100</v>
       </c>
       <c r="T16">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="U16">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="V16">
         <v>70</v>
@@ -5024,7 +5024,7 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C17">
         <v>100</v>
@@ -5045,13 +5045,13 @@
         <v>100</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J17">
         <v>100</v>
       </c>
       <c r="K17">
-        <v>100</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="L17">
         <v>100</v>
@@ -5066,13 +5066,13 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q17">
         <v>100</v>
       </c>
       <c r="R17">
-        <v>100</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -5092,7 +5092,7 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C18">
         <v>100</v>
@@ -5113,43 +5113,43 @@
         <v>70</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J18">
         <v>100</v>
       </c>
       <c r="K18">
-        <v>100</v>
+        <v>59.1</v>
       </c>
       <c r="L18">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="M18">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="N18">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="O18">
         <v>70</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="Q18">
         <v>100</v>
       </c>
       <c r="R18">
-        <v>100</v>
+        <v>59.1</v>
       </c>
       <c r="S18">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="T18">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="U18">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="V18">
         <v>70</v>
@@ -5160,7 +5160,7 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -5181,19 +5181,19 @@
         <v>100</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J19">
         <v>100</v>
       </c>
       <c r="K19">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="L19">
         <v>100</v>
       </c>
       <c r="M19">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N19">
         <v>100</v>
@@ -5202,19 +5202,19 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q19">
         <v>100</v>
       </c>
       <c r="R19">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S19">
         <v>100</v>
       </c>
       <c r="T19">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="U19">
         <v>100</v>
@@ -5228,7 +5228,7 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C20">
         <v>100</v>
@@ -5249,13 +5249,13 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J20">
         <v>100</v>
       </c>
       <c r="K20">
-        <v>95.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -5270,13 +5270,13 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q20">
         <v>100</v>
       </c>
       <c r="R20">
-        <v>95.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S20">
         <v>100</v>
@@ -5296,7 +5296,7 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C21">
         <v>100</v>
@@ -5317,43 +5317,43 @@
         <v>20</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J21">
         <v>100</v>
       </c>
       <c r="K21">
-        <v>91.7</v>
+        <v>75</v>
       </c>
       <c r="L21">
-        <v>86.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="M21">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N21">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="O21">
         <v>20</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="Q21">
         <v>100</v>
       </c>
       <c r="R21">
-        <v>91.7</v>
+        <v>75</v>
       </c>
       <c r="S21">
-        <v>86.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="T21">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="U21">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="V21">
         <v>20</v>
@@ -5364,7 +5364,7 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -5385,43 +5385,43 @@
         <v>60</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J22">
         <v>100</v>
       </c>
       <c r="K22">
-        <v>87.5</v>
+        <v>81.8</v>
       </c>
       <c r="L22">
-        <v>86.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="M22">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="N22">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="O22">
         <v>60</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q22">
         <v>100</v>
       </c>
       <c r="R22">
-        <v>87.5</v>
+        <v>81.8</v>
       </c>
       <c r="S22">
-        <v>86.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="T22">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="U22">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="V22">
         <v>60</v>
@@ -5432,7 +5432,7 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C23">
         <v>100</v>
@@ -5453,43 +5453,43 @@
         <v>60</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J23">
         <v>100</v>
       </c>
       <c r="K23">
-        <v>87.5</v>
+        <v>81.8</v>
       </c>
       <c r="L23">
-        <v>86.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="M23">
         <v>100</v>
       </c>
       <c r="N23">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="O23">
         <v>60</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="Q23">
         <v>100</v>
       </c>
       <c r="R23">
-        <v>87.5</v>
+        <v>81.8</v>
       </c>
       <c r="S23">
-        <v>86.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="T23">
         <v>100</v>
       </c>
       <c r="U23">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="V23">
         <v>60</v>
@@ -5500,7 +5500,7 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C24">
         <v>100</v>
@@ -5521,43 +5521,43 @@
         <v>60</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="J24">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="K24">
-        <v>87.5</v>
+        <v>47.7</v>
       </c>
       <c r="L24">
-        <v>86.7</v>
+        <v>39.4</v>
       </c>
       <c r="M24">
-        <v>70</v>
+        <v>77.5</v>
       </c>
       <c r="N24">
-        <v>73.3</v>
+        <v>80</v>
       </c>
       <c r="O24">
         <v>60</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="Q24">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="R24">
-        <v>87.5</v>
+        <v>47.7</v>
       </c>
       <c r="S24">
-        <v>86.7</v>
+        <v>39.4</v>
       </c>
       <c r="T24">
-        <v>70</v>
+        <v>77.5</v>
       </c>
       <c r="U24">
-        <v>73.3</v>
+        <v>80</v>
       </c>
       <c r="V24">
         <v>60</v>
@@ -5568,7 +5568,7 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C25">
         <v>100</v>
@@ -5589,43 +5589,43 @@
         <v>75</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J25">
         <v>100</v>
       </c>
       <c r="K25">
-        <v>95.8</v>
+        <v>52.3</v>
       </c>
       <c r="L25">
-        <v>86.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="M25">
-        <v>70</v>
+        <v>77.5</v>
       </c>
       <c r="N25">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="O25">
         <v>75</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q25">
         <v>100</v>
       </c>
       <c r="R25">
-        <v>95.8</v>
+        <v>52.3</v>
       </c>
       <c r="S25">
-        <v>86.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="T25">
-        <v>70</v>
+        <v>77.5</v>
       </c>
       <c r="U25">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="V25">
         <v>75</v>
@@ -5636,7 +5636,7 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C26">
         <v>100</v>
@@ -5657,19 +5657,19 @@
         <v>90</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J26">
         <v>100</v>
       </c>
       <c r="K26">
-        <v>95.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L26">
         <v>100</v>
       </c>
       <c r="M26">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N26">
         <v>100</v>
@@ -5678,19 +5678,19 @@
         <v>90</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q26">
         <v>100</v>
       </c>
       <c r="R26">
-        <v>95.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="S26">
         <v>100</v>
       </c>
       <c r="T26">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="U26">
         <v>100</v>
@@ -5704,7 +5704,7 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C27">
         <v>100</v>
@@ -5725,43 +5725,43 @@
         <v>100</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J27">
         <v>100</v>
       </c>
       <c r="K27">
-        <v>95.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L27">
         <v>100</v>
       </c>
       <c r="M27">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="N27">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="O27">
         <v>100</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="Q27">
         <v>100</v>
       </c>
       <c r="R27">
-        <v>95.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S27">
         <v>100</v>
       </c>
       <c r="T27">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="U27">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="V27">
         <v>100</v>
@@ -5772,7 +5772,7 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C28">
         <v>100</v>
@@ -5793,43 +5793,43 @@
         <v>100</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J28">
         <v>100</v>
       </c>
       <c r="K28">
-        <v>91.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L28">
         <v>100</v>
       </c>
       <c r="M28">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N28">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="O28">
         <v>100</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q28">
         <v>100</v>
       </c>
       <c r="R28">
-        <v>91.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="S28">
         <v>100</v>
       </c>
       <c r="T28">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="U28">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="V28">
         <v>100</v>
@@ -5840,7 +5840,7 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C29">
         <v>100</v>
@@ -5861,43 +5861,43 @@
         <v>95</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="J29">
         <v>100</v>
       </c>
       <c r="K29">
-        <v>100</v>
+        <v>81.8</v>
       </c>
       <c r="L29">
         <v>100</v>
       </c>
       <c r="M29">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="N29">
-        <v>93.3</v>
+        <v>90</v>
       </c>
       <c r="O29">
         <v>95</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="Q29">
         <v>100</v>
       </c>
       <c r="R29">
-        <v>100</v>
+        <v>81.8</v>
       </c>
       <c r="S29">
         <v>100</v>
       </c>
       <c r="T29">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="U29">
-        <v>93.3</v>
+        <v>90</v>
       </c>
       <c r="V29">
         <v>95</v>
@@ -5908,7 +5908,7 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C30">
         <v>100</v>
@@ -5929,43 +5929,43 @@
         <v>95</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J30">
         <v>100</v>
       </c>
       <c r="K30">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="L30">
         <v>100</v>
       </c>
       <c r="M30">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N30">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="O30">
         <v>95</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="Q30">
         <v>100</v>
       </c>
       <c r="R30">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="S30">
         <v>100</v>
       </c>
       <c r="T30">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="U30">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="V30">
         <v>95</v>
@@ -5976,7 +5976,7 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C31">
         <v>100</v>
@@ -5997,43 +5997,43 @@
         <v>80</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J31">
         <v>100</v>
       </c>
       <c r="K31">
-        <v>95.8</v>
+        <v>93.2</v>
       </c>
       <c r="L31">
         <v>100</v>
       </c>
       <c r="M31">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N31">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="O31">
         <v>80</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="Q31">
         <v>100</v>
       </c>
       <c r="R31">
-        <v>95.8</v>
+        <v>93.2</v>
       </c>
       <c r="S31">
         <v>100</v>
       </c>
       <c r="T31">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="U31">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="V31">
         <v>80</v>
@@ -6044,7 +6044,7 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C32">
         <v>100</v>
@@ -6065,43 +6065,43 @@
         <v>100</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J32">
         <v>100</v>
       </c>
       <c r="K32">
-        <v>95.8</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="L32">
         <v>100</v>
       </c>
       <c r="M32">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N32">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="O32">
         <v>100</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="Q32">
         <v>100</v>
       </c>
       <c r="R32">
-        <v>95.8</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="S32">
         <v>100</v>
       </c>
       <c r="T32">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="U32">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="V32">
         <v>100</v>
@@ -6112,7 +6112,7 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C33">
         <v>100</v>
@@ -6133,43 +6133,43 @@
         <v>90</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J33">
         <v>100</v>
       </c>
       <c r="K33">
-        <v>95.8</v>
+        <v>93.2</v>
       </c>
       <c r="L33">
         <v>100</v>
       </c>
       <c r="M33">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="N33">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="O33">
         <v>90</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q33">
         <v>100</v>
       </c>
       <c r="R33">
-        <v>95.8</v>
+        <v>93.2</v>
       </c>
       <c r="S33">
         <v>100</v>
       </c>
       <c r="T33">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="U33">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="V33">
         <v>90</v>
@@ -6180,7 +6180,7 @@
         <v>43</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="C34">
         <v>100</v>
@@ -6201,43 +6201,43 @@
         <v>45</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J34">
         <v>100</v>
       </c>
       <c r="K34">
-        <v>87.5</v>
+        <v>47.7</v>
       </c>
       <c r="L34">
-        <v>6.7</v>
+        <v>51.5</v>
       </c>
       <c r="M34">
         <v>0</v>
       </c>
       <c r="N34">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="O34">
         <v>45</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Q34">
         <v>100</v>
       </c>
       <c r="R34">
-        <v>87.5</v>
+        <v>47.7</v>
       </c>
       <c r="S34">
-        <v>6.7</v>
+        <v>51.5</v>
       </c>
       <c r="T34">
         <v>0</v>
       </c>
       <c r="U34">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="V34">
         <v>45</v>
@@ -6248,7 +6248,7 @@
         <v>44</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C35">
         <v>100</v>
@@ -6269,19 +6269,19 @@
         <v>100</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J35">
         <v>100</v>
       </c>
       <c r="K35">
-        <v>95.8</v>
+        <v>93.2</v>
       </c>
       <c r="L35">
         <v>100</v>
       </c>
       <c r="M35">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N35">
         <v>100</v>
@@ -6290,19 +6290,19 @@
         <v>100</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q35">
         <v>100</v>
       </c>
       <c r="R35">
-        <v>95.8</v>
+        <v>93.2</v>
       </c>
       <c r="S35">
         <v>100</v>
       </c>
       <c r="T35">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="U35">
         <v>100</v>
@@ -6316,7 +6316,7 @@
         <v>45</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C36">
         <v>100</v>
@@ -6337,13 +6337,13 @@
         <v>85</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J36">
         <v>100</v>
       </c>
       <c r="K36">
-        <v>95.8</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="L36">
         <v>100</v>
@@ -6352,19 +6352,19 @@
         <v>90</v>
       </c>
       <c r="N36">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="O36">
         <v>85</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="Q36">
         <v>100</v>
       </c>
       <c r="R36">
-        <v>95.8</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="S36">
         <v>100</v>
@@ -6373,7 +6373,7 @@
         <v>90</v>
       </c>
       <c r="U36">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="V36">
         <v>85</v>
@@ -6384,7 +6384,7 @@
         <v>46</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C37">
         <v>100</v>
@@ -6405,7 +6405,7 @@
         <v>100</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J37">
         <v>100</v>
@@ -6426,7 +6426,7 @@
         <v>100</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q37">
         <v>100</v>
@@ -6452,7 +6452,7 @@
         <v>47</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C38">
         <v>100</v>
@@ -6473,19 +6473,19 @@
         <v>100</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J38">
         <v>100</v>
       </c>
       <c r="K38">
-        <v>83.3</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="L38">
-        <v>86.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="M38">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="N38">
         <v>100</v>
@@ -6494,19 +6494,19 @@
         <v>100</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="Q38">
         <v>100</v>
       </c>
       <c r="R38">
-        <v>83.3</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="S38">
-        <v>86.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="T38">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="U38">
         <v>100</v>
@@ -6520,7 +6520,7 @@
         <v>48</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="C39">
         <v>100</v>
@@ -6541,43 +6541,43 @@
         <v>65</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J39">
         <v>100</v>
       </c>
       <c r="K39">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="L39">
         <v>100</v>
       </c>
       <c r="M39">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="N39">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="O39">
         <v>65</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q39">
         <v>100</v>
       </c>
       <c r="R39">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="S39">
         <v>100</v>
       </c>
       <c r="T39">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="U39">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="V39">
         <v>65</v>
@@ -6646,25 +6646,25 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2">
         <v>23</v>
       </c>
       <c r="F2" s="2">
-        <v>33.3</v>
+        <v>36.1</v>
       </c>
       <c r="G2" s="2">
         <v>63.9</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2">
-        <v>2.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6678,19 +6678,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" s="2">
-        <v>38.9</v>
+        <v>36.1</v>
       </c>
       <c r="G3" s="2">
-        <v>61.1</v>
+        <v>63.9</v>
       </c>
       <c r="H3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6701,7 +6701,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
@@ -6710,19 +6710,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F4" s="2">
-        <v>52.8</v>
+        <v>41.7</v>
       </c>
       <c r="G4" s="2">
-        <v>47.2</v>
+        <v>58.3</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>5.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6733,7 +6733,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
@@ -6742,19 +6742,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="2">
-        <v>61.1</v>
+        <v>58.3</v>
       </c>
       <c r="G5" s="2">
-        <v>38.9</v>
+        <v>41.7</v>
       </c>
       <c r="H5">
-        <v>6.1</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6765,7 +6765,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
@@ -6774,19 +6774,19 @@
         <v>36</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F6" s="2">
-        <v>69.40000000000001</v>
+        <v>61.1</v>
       </c>
       <c r="G6" s="2">
-        <v>30.6</v>
+        <v>38.9</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6797,7 +6797,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>67</v>
@@ -6806,19 +6806,19 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" s="2">
-        <v>77.8</v>
+        <v>75</v>
       </c>
       <c r="G7" s="2">
-        <v>22.2</v>
+        <v>25</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6829,7 +6829,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>68</v>
@@ -6838,19 +6838,19 @@
         <v>36</v>
       </c>
       <c r="D8">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F8" s="2">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="G8" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H8">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6886,7 +6886,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6913,26 +6913,6 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>23330051920349</v>
-      </c>
-      <c r="B2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>62</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6940,7 +6920,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6972,10 +6952,10 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920189</v>
+        <v>23330051920180</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
         <v>81</v>
@@ -6984,10 +6964,10 @@
         <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6995,10 +6975,10 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920189</v>
+        <v>23330051920180</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
         <v>81</v>
@@ -7018,10 +6998,10 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920204</v>
+        <v>23330051920181</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
         <v>82</v>
@@ -7030,10 +7010,10 @@
         <v>90</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7041,10 +7021,10 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920204</v>
+        <v>23330051920181</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
         <v>82</v>
@@ -7053,10 +7033,10 @@
         <v>90</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7064,10 +7044,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920180</v>
+        <v>23330051920189</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
         <v>83</v>
@@ -7076,10 +7056,10 @@
         <v>91</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7087,16 +7067,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920181</v>
+        <v>23330051920189</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -7110,22 +7090,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920185</v>
+        <v>23330051920199</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7133,22 +7113,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920190</v>
+        <v>23330051920199</v>
       </c>
       <c r="B9" t="s">
         <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7156,22 +7136,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920192</v>
+        <v>23330051920203</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7185,10 +7165,10 @@
         <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -7197,6 +7177,98 @@
         <v>63</v>
       </c>
       <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>23330051920212</v>
+      </c>
+      <c r="B12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" t="s">
+        <v>94</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>23330051920212</v>
+      </c>
+      <c r="B13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>23330051920190</v>
+      </c>
+      <c r="B14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" t="s">
+        <v>95</v>
+      </c>
+      <c r="E14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>23330051920329</v>
+      </c>
+      <c r="B15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" t="s">
+        <v>88</v>
+      </c>
+      <c r="D15" t="s">
+        <v>96</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>63</v>
+      </c>
+      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1AV - Estadisticos 20231.xlsx
+++ b/grupos/1AV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="97">
   <si>
     <t>Materia</t>
   </si>
@@ -215,12 +215,12 @@
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
     <t>Saucedo Rivalcoba Graciela</t>
   </si>
   <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
@@ -269,6 +269,9 @@
     <t>DAMIAN</t>
   </si>
   <si>
+    <t>AUTRAN</t>
+  </si>
+  <si>
     <t>GUEVARA</t>
   </si>
   <si>
@@ -281,9 +284,6 @@
     <t>VILLA</t>
   </si>
   <si>
-    <t>AUTRAN</t>
-  </si>
-  <si>
     <t>CIRUELO</t>
   </si>
   <si>
@@ -293,6 +293,9 @@
     <t>JESUS JAREF</t>
   </si>
   <si>
+    <t>AXEL AARON</t>
+  </si>
+  <si>
     <t>NATANAHEL</t>
   </si>
   <si>
@@ -303,9 +306,6 @@
   </si>
   <si>
     <t>ALEX URIEL</t>
-  </si>
-  <si>
-    <t>AXEL AARON</t>
   </si>
   <si>
     <t>SABDY</t>
@@ -853,7 +853,7 @@
         <v>5</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -942,7 +942,7 @@
         <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1031,7 +1031,7 @@
         <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1073,7 +1073,7 @@
         <v>10</v>
       </c>
       <c r="AC6">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1120,7 +1120,7 @@
         <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1209,7 +1209,7 @@
         <v>6</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1280,7 +1280,7 @@
         <v>5</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1298,7 +1298,7 @@
         <v>5</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1387,7 +1387,7 @@
         <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1429,7 +1429,7 @@
         <v>10</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1476,7 +1476,7 @@
         <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1565,7 +1565,7 @@
         <v>5</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1654,7 +1654,7 @@
         <v>7</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1696,7 +1696,7 @@
         <v>7</v>
       </c>
       <c r="AC13">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1743,7 +1743,7 @@
         <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1832,7 +1832,7 @@
         <v>5</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1921,7 +1921,7 @@
         <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -2010,7 +2010,7 @@
         <v>6</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2052,7 +2052,7 @@
         <v>8</v>
       </c>
       <c r="AC17">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2099,7 +2099,7 @@
         <v>5</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2141,7 +2141,7 @@
         <v>5</v>
       </c>
       <c r="AC18">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2188,7 +2188,7 @@
         <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2230,7 +2230,7 @@
         <v>10</v>
       </c>
       <c r="AC19">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2277,7 +2277,7 @@
         <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2366,7 +2366,7 @@
         <v>5</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2455,7 +2455,7 @@
         <v>5</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2544,7 +2544,7 @@
         <v>6</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2633,7 +2633,7 @@
         <v>5</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2722,7 +2722,7 @@
         <v>5</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2811,7 +2811,7 @@
         <v>9</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2853,7 +2853,7 @@
         <v>9</v>
       </c>
       <c r="AC26">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2900,7 +2900,7 @@
         <v>5</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2942,7 +2942,7 @@
         <v>5</v>
       </c>
       <c r="AC27">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -2989,7 +2989,7 @@
         <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3031,7 +3031,7 @@
         <v>10</v>
       </c>
       <c r="AC28">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3078,7 +3078,7 @@
         <v>5</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3120,7 +3120,7 @@
         <v>5</v>
       </c>
       <c r="AC29">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3167,7 +3167,7 @@
         <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3256,7 +3256,7 @@
         <v>6</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3298,7 +3298,7 @@
         <v>5</v>
       </c>
       <c r="AC31">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3345,7 +3345,7 @@
         <v>6</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3387,7 +3387,7 @@
         <v>7</v>
       </c>
       <c r="AC32">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3434,7 +3434,7 @@
         <v>8</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3476,7 +3476,7 @@
         <v>7</v>
       </c>
       <c r="AC33">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3523,7 +3523,7 @@
         <v>5</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3612,7 +3612,7 @@
         <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3701,7 +3701,7 @@
         <v>7</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3790,7 +3790,7 @@
         <v>10</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -3832,7 +3832,7 @@
         <v>10</v>
       </c>
       <c r="AC37">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:29">
@@ -3879,7 +3879,7 @@
         <v>6</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P38">
         <v>-1</v>
@@ -3921,7 +3921,7 @@
         <v>5</v>
       </c>
       <c r="AC38">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:29">
@@ -3968,7 +3968,7 @@
         <v>7</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P39">
         <v>-1</v>
@@ -4179,7 +4179,7 @@
         <v>50</v>
       </c>
       <c r="O4">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="P4">
         <v>65</v>
@@ -4200,7 +4200,7 @@
         <v>50</v>
       </c>
       <c r="V4">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -4315,7 +4315,7 @@
         <v>100</v>
       </c>
       <c r="O6">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P6">
         <v>95</v>
@@ -4336,7 +4336,7 @@
         <v>100</v>
       </c>
       <c r="V6">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -4451,7 +4451,7 @@
         <v>100</v>
       </c>
       <c r="O8">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="P8">
         <v>90</v>
@@ -4472,7 +4472,7 @@
         <v>100</v>
       </c>
       <c r="V8">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -4655,7 +4655,7 @@
         <v>93.3</v>
       </c>
       <c r="O11">
-        <v>70</v>
+        <v>82.5</v>
       </c>
       <c r="P11">
         <v>85</v>
@@ -4676,7 +4676,7 @@
         <v>93.3</v>
       </c>
       <c r="V11">
-        <v>70</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -4723,7 +4723,7 @@
         <v>96.7</v>
       </c>
       <c r="O12">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="P12">
         <v>85</v>
@@ -4744,7 +4744,7 @@
         <v>96.7</v>
       </c>
       <c r="V12">
-        <v>100</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -4791,7 +4791,7 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="P13">
         <v>85</v>
@@ -4812,7 +4812,7 @@
         <v>100</v>
       </c>
       <c r="V13">
-        <v>95</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -4859,7 +4859,7 @@
         <v>93.3</v>
       </c>
       <c r="O14">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -4880,7 +4880,7 @@
         <v>93.3</v>
       </c>
       <c r="V14">
-        <v>95</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -4927,7 +4927,7 @@
         <v>0</v>
       </c>
       <c r="O15">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>35</v>
@@ -4948,7 +4948,7 @@
         <v>0</v>
       </c>
       <c r="V15">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -4995,7 +4995,7 @@
         <v>93.3</v>
       </c>
       <c r="O16">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="P16">
         <v>90</v>
@@ -5016,7 +5016,7 @@
         <v>93.3</v>
       </c>
       <c r="V16">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -5063,7 +5063,7 @@
         <v>100</v>
       </c>
       <c r="O17">
-        <v>100</v>
+        <v>82.5</v>
       </c>
       <c r="P17">
         <v>90</v>
@@ -5084,7 +5084,7 @@
         <v>100</v>
       </c>
       <c r="V17">
-        <v>100</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -5131,7 +5131,7 @@
         <v>90</v>
       </c>
       <c r="O18">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="P18">
         <v>75</v>
@@ -5152,7 +5152,7 @@
         <v>90</v>
       </c>
       <c r="V18">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -5199,7 +5199,7 @@
         <v>100</v>
       </c>
       <c r="O19">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P19">
         <v>90</v>
@@ -5220,7 +5220,7 @@
         <v>100</v>
       </c>
       <c r="V19">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -5335,7 +5335,7 @@
         <v>83.3</v>
       </c>
       <c r="O21">
-        <v>20</v>
+        <v>47.5</v>
       </c>
       <c r="P21">
         <v>70</v>
@@ -5356,7 +5356,7 @@
         <v>83.3</v>
       </c>
       <c r="V21">
-        <v>20</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -5403,7 +5403,7 @@
         <v>83.3</v>
       </c>
       <c r="O22">
-        <v>60</v>
+        <v>72.5</v>
       </c>
       <c r="P22">
         <v>85</v>
@@ -5424,7 +5424,7 @@
         <v>83.3</v>
       </c>
       <c r="V22">
-        <v>60</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -5471,7 +5471,7 @@
         <v>96.7</v>
       </c>
       <c r="O23">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="P23">
         <v>70</v>
@@ -5492,7 +5492,7 @@
         <v>96.7</v>
       </c>
       <c r="V23">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -5539,7 +5539,7 @@
         <v>80</v>
       </c>
       <c r="O24">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P24">
         <v>55</v>
@@ -5560,7 +5560,7 @@
         <v>80</v>
       </c>
       <c r="V24">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -5607,7 +5607,7 @@
         <v>83.3</v>
       </c>
       <c r="O25">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="P25">
         <v>80</v>
@@ -5628,7 +5628,7 @@
         <v>83.3</v>
       </c>
       <c r="V25">
-        <v>75</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -5675,7 +5675,7 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P26">
         <v>80</v>
@@ -5696,7 +5696,7 @@
         <v>100</v>
       </c>
       <c r="V26">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -5743,7 +5743,7 @@
         <v>96.7</v>
       </c>
       <c r="O27">
-        <v>100</v>
+        <v>82.5</v>
       </c>
       <c r="P27">
         <v>75</v>
@@ -5764,7 +5764,7 @@
         <v>96.7</v>
       </c>
       <c r="V27">
-        <v>100</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -5811,7 +5811,7 @@
         <v>96.7</v>
       </c>
       <c r="O28">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P28">
         <v>95</v>
@@ -5832,7 +5832,7 @@
         <v>96.7</v>
       </c>
       <c r="V28">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -5879,7 +5879,7 @@
         <v>90</v>
       </c>
       <c r="O29">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="P29">
         <v>65</v>
@@ -5900,7 +5900,7 @@
         <v>90</v>
       </c>
       <c r="V29">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -5947,7 +5947,7 @@
         <v>96.7</v>
       </c>
       <c r="O30">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="P30">
         <v>75</v>
@@ -5968,7 +5968,7 @@
         <v>96.7</v>
       </c>
       <c r="V30">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -6015,7 +6015,7 @@
         <v>93.3</v>
       </c>
       <c r="O31">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="P31">
         <v>75</v>
@@ -6036,7 +6036,7 @@
         <v>93.3</v>
       </c>
       <c r="V31">
-        <v>80</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -6083,7 +6083,7 @@
         <v>93.3</v>
       </c>
       <c r="O32">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="P32">
         <v>75</v>
@@ -6104,7 +6104,7 @@
         <v>93.3</v>
       </c>
       <c r="V32">
-        <v>100</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -6151,7 +6151,7 @@
         <v>93.3</v>
       </c>
       <c r="O33">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="P33">
         <v>85</v>
@@ -6172,7 +6172,7 @@
         <v>93.3</v>
       </c>
       <c r="V33">
-        <v>90</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -6219,7 +6219,7 @@
         <v>83.3</v>
       </c>
       <c r="O34">
-        <v>45</v>
+        <v>22.5</v>
       </c>
       <c r="P34">
         <v>40</v>
@@ -6240,7 +6240,7 @@
         <v>83.3</v>
       </c>
       <c r="V34">
-        <v>45</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -6287,7 +6287,7 @@
         <v>100</v>
       </c>
       <c r="O35">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P35">
         <v>95</v>
@@ -6308,7 +6308,7 @@
         <v>100</v>
       </c>
       <c r="V35">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -6355,7 +6355,7 @@
         <v>96.7</v>
       </c>
       <c r="O36">
-        <v>85</v>
+        <v>72.5</v>
       </c>
       <c r="P36">
         <v>60</v>
@@ -6376,7 +6376,7 @@
         <v>96.7</v>
       </c>
       <c r="V36">
-        <v>85</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -6423,7 +6423,7 @@
         <v>100</v>
       </c>
       <c r="O37">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="P37">
         <v>100</v>
@@ -6444,7 +6444,7 @@
         <v>100</v>
       </c>
       <c r="V37">
-        <v>100</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -6491,7 +6491,7 @@
         <v>100</v>
       </c>
       <c r="O38">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="P38">
         <v>70</v>
@@ -6512,7 +6512,7 @@
         <v>100</v>
       </c>
       <c r="V38">
-        <v>100</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -6559,7 +6559,7 @@
         <v>93.3</v>
       </c>
       <c r="O39">
-        <v>65</v>
+        <v>77.5</v>
       </c>
       <c r="P39">
         <v>80</v>
@@ -6580,7 +6580,7 @@
         <v>93.3</v>
       </c>
       <c r="V39">
-        <v>65</v>
+        <v>77.5</v>
       </c>
     </row>
   </sheetData>
@@ -6733,7 +6733,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
@@ -6742,19 +6742,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F5" s="2">
-        <v>58.3</v>
+        <v>47.2</v>
       </c>
       <c r="G5" s="2">
-        <v>41.7</v>
+        <v>52.8</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6765,7 +6765,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
@@ -6774,19 +6774,19 @@
         <v>36</v>
       </c>
       <c r="D6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6" s="2">
-        <v>61.1</v>
+        <v>58.3</v>
       </c>
       <c r="G6" s="2">
-        <v>38.9</v>
+        <v>41.7</v>
       </c>
       <c r="H6">
-        <v>6.1</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6920,7 +6920,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7044,7 +7044,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920189</v>
+        <v>23330051920190</v>
       </c>
       <c r="B6" t="s">
         <v>76</v>
@@ -7067,7 +7067,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920189</v>
+        <v>23330051920190</v>
       </c>
       <c r="B7" t="s">
         <v>76</v>
@@ -7079,10 +7079,10 @@
         <v>91</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7090,10 +7090,10 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920199</v>
+        <v>23330051920189</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
         <v>84</v>
@@ -7102,10 +7102,10 @@
         <v>92</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7113,10 +7113,10 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920199</v>
+        <v>23330051920189</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
         <v>84</v>
@@ -7125,10 +7125,10 @@
         <v>92</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7136,10 +7136,10 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920203</v>
+        <v>23330051920199</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
         <v>85</v>
@@ -7148,10 +7148,10 @@
         <v>93</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7159,10 +7159,10 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920203</v>
+        <v>23330051920199</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
         <v>85</v>
@@ -7171,10 +7171,10 @@
         <v>93</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7182,10 +7182,10 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920212</v>
+        <v>23330051920203</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
         <v>86</v>
@@ -7194,10 +7194,10 @@
         <v>94</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -7205,10 +7205,10 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920212</v>
+        <v>23330051920203</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
         <v>86</v>
@@ -7217,10 +7217,10 @@
         <v>94</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7228,10 +7228,10 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920190</v>
+        <v>23330051920212</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
         <v>87</v>
@@ -7240,10 +7240,10 @@
         <v>95</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -7251,24 +7251,47 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
+        <v>23330051920212</v>
+      </c>
+      <c r="B15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" t="s">
+        <v>95</v>
+      </c>
+      <c r="E15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" t="s">
+        <v>65</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
         <v>23330051920329</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B16" t="s">
         <v>80</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C16" t="s">
         <v>88</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D16" t="s">
         <v>96</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E16" t="s">
         <v>9</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F16" t="s">
         <v>63</v>
       </c>
-      <c r="G15">
+      <c r="G16">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1AV - Estadisticos 20231.xlsx
+++ b/grupos/1AV - Estadisticos 20231.xlsx
@@ -5314,7 +5314,7 @@
         <v>80</v>
       </c>
       <c r="H21">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="I21">
         <v>70</v>
@@ -5335,7 +5335,7 @@
         <v>83.3</v>
       </c>
       <c r="O21">
-        <v>47.5</v>
+        <v>72.5</v>
       </c>
       <c r="P21">
         <v>70</v>
@@ -5356,7 +5356,7 @@
         <v>83.3</v>
       </c>
       <c r="V21">
-        <v>47.5</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="22" spans="1:22">

--- a/grupos/1AV - Estadisticos 20231.xlsx
+++ b/grupos/1AV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="102">
   <si>
     <t>Materia</t>
   </si>
@@ -209,24 +209,24 @@
     <t>Silva Villegas Mario</t>
   </si>
   <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Saucedo Rivalcoba Graciela</t>
+  </si>
+  <si>
+    <t>Zarate Amezcua Eladio Jorge</t>
+  </si>
+  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
-    <t>Saucedo Rivalcoba Graciela</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
     <t>Rivera Serra Alma Lilian</t>
   </si>
   <si>
@@ -242,73 +242,88 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>BUSTOS</t>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>VERA</t>
   </si>
   <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>LARA</t>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>AUTRAN</t>
+  </si>
+  <si>
+    <t>VILLA</t>
   </si>
   <si>
     <t>DAMIAN</t>
   </si>
   <si>
-    <t>AUTRAN</t>
+    <t>COCOTLE</t>
   </si>
   <si>
     <t>GUEVARA</t>
   </si>
   <si>
-    <t>MORALES</t>
+    <t>CARRERA</t>
   </si>
   <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>JOSE EMILIANO</t>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
+    <t>CRISTOPHER</t>
+  </si>
+  <si>
+    <t>AXEL AARON</t>
+  </si>
+  <si>
+    <t>ALEX URIEL</t>
   </si>
   <si>
     <t>JESUS JAREF</t>
   </si>
   <si>
-    <t>AXEL AARON</t>
+    <t>EMMANUEL</t>
   </si>
   <si>
     <t>NATANAHEL</t>
   </si>
   <si>
-    <t>DIEGO</t>
+    <t>KEVYN DANIEL</t>
   </si>
   <si>
     <t>LUIS FABIAN</t>
   </si>
   <si>
-    <t>ALEX URIEL</t>
-  </si>
-  <si>
-    <t>SABDY</t>
+    <t>ROBBIE ALONSO</t>
   </si>
 </sst>
 </file>
@@ -859,16 +874,16 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U4">
         <v>-1</v>
@@ -880,7 +895,7 @@
         <v>5</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y4">
         <v>5</v>
@@ -948,16 +963,16 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U5">
         <v>-1</v>
@@ -1037,16 +1052,16 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U6">
         <v>-1</v>
@@ -1126,16 +1141,16 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U7">
         <v>-1</v>
@@ -1150,13 +1165,13 @@
         <v>7</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z7">
         <v>9</v>
       </c>
       <c r="AA7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB7">
         <v>9</v>
@@ -1215,16 +1230,16 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>-1</v>
@@ -1236,16 +1251,16 @@
         <v>7</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y8">
         <v>5</v>
       </c>
       <c r="Z8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB8">
         <v>8</v>
@@ -1304,16 +1319,16 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U9">
         <v>-1</v>
@@ -1393,16 +1408,16 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U10">
         <v>-1</v>
@@ -1417,7 +1432,7 @@
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z10">
         <v>7</v>
@@ -1482,16 +1497,16 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U11">
         <v>-1</v>
@@ -1512,7 +1527,7 @@
         <v>8</v>
       </c>
       <c r="AA11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB11">
         <v>6</v>
@@ -1571,16 +1586,16 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U12">
         <v>-1</v>
@@ -1592,16 +1607,16 @@
         <v>5</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB12">
         <v>5</v>
@@ -1660,16 +1675,16 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>-1</v>
@@ -1681,16 +1696,16 @@
         <v>5</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z13">
         <v>7</v>
       </c>
       <c r="AA13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB13">
         <v>7</v>
@@ -1749,16 +1764,16 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U14">
         <v>-1</v>
@@ -1838,16 +1853,16 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U15">
         <v>-1</v>
@@ -1927,16 +1942,16 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U16">
         <v>-1</v>
@@ -1948,7 +1963,7 @@
         <v>5</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>6</v>
@@ -1957,7 +1972,7 @@
         <v>7</v>
       </c>
       <c r="AA16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB16">
         <v>5</v>
@@ -2016,16 +2031,16 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U17">
         <v>-1</v>
@@ -2105,16 +2120,16 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U18">
         <v>-1</v>
@@ -2126,13 +2141,13 @@
         <v>5</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA18">
         <v>5</v>
@@ -2194,16 +2209,16 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U19">
         <v>-1</v>
@@ -2224,7 +2239,7 @@
         <v>8</v>
       </c>
       <c r="AA19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB19">
         <v>10</v>
@@ -2283,16 +2298,16 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>-1</v>
@@ -2304,16 +2319,16 @@
         <v>6</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB20">
         <v>9</v>
@@ -2372,16 +2387,16 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U21">
         <v>-1</v>
@@ -2461,16 +2476,16 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U22">
         <v>-1</v>
@@ -2491,7 +2506,7 @@
         <v>5</v>
       </c>
       <c r="AA22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB22">
         <v>5</v>
@@ -2550,16 +2565,16 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U23">
         <v>-1</v>
@@ -2577,10 +2592,10 @@
         <v>5</v>
       </c>
       <c r="Z23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB23">
         <v>6</v>
@@ -2639,16 +2654,16 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U24">
         <v>-1</v>
@@ -2728,16 +2743,16 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U25">
         <v>-1</v>
@@ -2755,7 +2770,7 @@
         <v>5</v>
       </c>
       <c r="Z25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA25">
         <v>5</v>
@@ -2817,16 +2832,16 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U26">
         <v>-1</v>
@@ -2847,7 +2862,7 @@
         <v>8</v>
       </c>
       <c r="AA26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB26">
         <v>9</v>
@@ -2906,16 +2921,16 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U27">
         <v>-1</v>
@@ -2930,13 +2945,13 @@
         <v>6</v>
       </c>
       <c r="Y27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z27">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB27">
         <v>5</v>
@@ -2995,16 +3010,16 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U28">
         <v>-1</v>
@@ -3016,10 +3031,10 @@
         <v>7</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z28">
         <v>8</v>
@@ -3084,16 +3099,16 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U29">
         <v>-1</v>
@@ -3108,10 +3123,10 @@
         <v>5</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z29">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA29">
         <v>5</v>
@@ -3173,16 +3188,16 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U30">
         <v>-1</v>
@@ -3203,7 +3218,7 @@
         <v>7</v>
       </c>
       <c r="AA30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB30">
         <v>9</v>
@@ -3262,16 +3277,16 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U31">
         <v>-1</v>
@@ -3283,13 +3298,13 @@
         <v>5</v>
       </c>
       <c r="X31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z31">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA31">
         <v>6</v>
@@ -3351,16 +3366,16 @@
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U32">
         <v>-1</v>
@@ -3378,10 +3393,10 @@
         <v>5</v>
       </c>
       <c r="Z32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB32">
         <v>7</v>
@@ -3440,16 +3455,16 @@
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U33">
         <v>-1</v>
@@ -3461,10 +3476,10 @@
         <v>5</v>
       </c>
       <c r="X33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z33">
         <v>10</v>
@@ -3529,16 +3544,16 @@
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U34">
         <v>-1</v>
@@ -3618,16 +3633,16 @@
         <v>-1</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U35">
         <v>-1</v>
@@ -3642,13 +3657,13 @@
         <v>7</v>
       </c>
       <c r="Y35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z35">
         <v>9</v>
       </c>
       <c r="AA35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB35">
         <v>10</v>
@@ -3707,16 +3722,16 @@
         <v>-1</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U36">
         <v>-1</v>
@@ -3734,10 +3749,10 @@
         <v>5</v>
       </c>
       <c r="Z36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB36">
         <v>7</v>
@@ -3796,16 +3811,16 @@
         <v>-1</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U37">
         <v>-1</v>
@@ -3820,13 +3835,13 @@
         <v>7</v>
       </c>
       <c r="Y37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z37">
         <v>9</v>
       </c>
       <c r="AA37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB37">
         <v>10</v>
@@ -3885,16 +3900,16 @@
         <v>-1</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U38">
         <v>-1</v>
@@ -3906,16 +3921,16 @@
         <v>5</v>
       </c>
       <c r="X38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y38">
         <v>5</v>
       </c>
       <c r="Z38">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB38">
         <v>5</v>
@@ -3974,16 +3989,16 @@
         <v>-1</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U39">
         <v>-1</v>
@@ -3995,16 +4010,16 @@
         <v>6</v>
       </c>
       <c r="X39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z39">
         <v>8</v>
       </c>
       <c r="AA39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB39">
         <v>8</v>
@@ -4188,13 +4203,13 @@
         <v>100</v>
       </c>
       <c r="R4">
-        <v>50</v>
+        <v>34.4</v>
       </c>
       <c r="S4">
-        <v>45.5</v>
+        <v>31.3</v>
       </c>
       <c r="T4">
-        <v>82.5</v>
+        <v>55</v>
       </c>
       <c r="U4">
         <v>50</v>
@@ -4256,10 +4271,10 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>50</v>
+        <v>34.4</v>
       </c>
       <c r="S5">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -4324,7 +4339,7 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>93.2</v>
+        <v>87.5</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -4392,7 +4407,7 @@
         <v>100</v>
       </c>
       <c r="R7">
-        <v>90.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -4460,7 +4475,7 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -4528,13 +4543,13 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>68.2</v>
+        <v>57.8</v>
       </c>
       <c r="S9">
-        <v>87.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="T9">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="U9">
         <v>80</v>
@@ -4664,13 +4679,13 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>88.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="S11">
         <v>100</v>
       </c>
       <c r="T11">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U11">
         <v>93.3</v>
@@ -4732,13 +4747,13 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>79.5</v>
+        <v>81.3</v>
       </c>
       <c r="S12">
         <v>100</v>
       </c>
       <c r="T12">
-        <v>87.5</v>
+        <v>90</v>
       </c>
       <c r="U12">
         <v>96.7</v>
@@ -4800,13 +4815,13 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>90.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="S13">
         <v>100</v>
       </c>
       <c r="T13">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="U13">
         <v>100</v>
@@ -4868,13 +4883,13 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>93.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S14">
         <v>100</v>
       </c>
       <c r="T14">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U14">
         <v>93.3</v>
@@ -4933,16 +4948,16 @@
         <v>35</v>
       </c>
       <c r="Q15">
-        <v>83.3</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="R15">
-        <v>50</v>
+        <v>34.4</v>
       </c>
       <c r="S15">
-        <v>6.1</v>
+        <v>4.2</v>
       </c>
       <c r="T15">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="U15">
         <v>0</v>
@@ -5004,13 +5019,13 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>81.8</v>
+        <v>82.8</v>
       </c>
       <c r="S16">
         <v>100</v>
       </c>
       <c r="T16">
-        <v>87.5</v>
+        <v>90</v>
       </c>
       <c r="U16">
         <v>93.3</v>
@@ -5072,7 +5087,7 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>84.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -5140,13 +5155,13 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>59.1</v>
+        <v>40.6</v>
       </c>
       <c r="S18">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="T18">
-        <v>92.5</v>
+        <v>93.3</v>
       </c>
       <c r="U18">
         <v>90</v>
@@ -5208,13 +5223,13 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>97.7</v>
+        <v>93.8</v>
       </c>
       <c r="S19">
         <v>100</v>
       </c>
       <c r="T19">
-        <v>97.5</v>
+        <v>96.7</v>
       </c>
       <c r="U19">
         <v>100</v>
@@ -5276,7 +5291,7 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>90.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="S20">
         <v>100</v>
@@ -5344,10 +5359,10 @@
         <v>100</v>
       </c>
       <c r="R21">
-        <v>75</v>
+        <v>68.8</v>
       </c>
       <c r="S21">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="T21">
         <v>90</v>
@@ -5412,13 +5427,13 @@
         <v>100</v>
       </c>
       <c r="R22">
-        <v>81.8</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="S22">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="T22">
-        <v>82.5</v>
+        <v>86.7</v>
       </c>
       <c r="U22">
         <v>83.3</v>
@@ -5480,10 +5495,10 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>81.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="S23">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="T23">
         <v>100</v>
@@ -5545,16 +5560,16 @@
         <v>55</v>
       </c>
       <c r="Q24">
-        <v>83.3</v>
+        <v>77.8</v>
       </c>
       <c r="R24">
-        <v>47.7</v>
+        <v>32.8</v>
       </c>
       <c r="S24">
-        <v>39.4</v>
+        <v>27.1</v>
       </c>
       <c r="T24">
-        <v>77.5</v>
+        <v>51.7</v>
       </c>
       <c r="U24">
         <v>80</v>
@@ -5616,13 +5631,13 @@
         <v>100</v>
       </c>
       <c r="R25">
-        <v>52.3</v>
+        <v>57.8</v>
       </c>
       <c r="S25">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="T25">
-        <v>77.5</v>
+        <v>81.7</v>
       </c>
       <c r="U25">
         <v>83.3</v>
@@ -5684,13 +5699,13 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>88.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="S26">
         <v>100</v>
       </c>
       <c r="T26">
-        <v>97.5</v>
+        <v>96.7</v>
       </c>
       <c r="U26">
         <v>100</v>
@@ -5752,13 +5767,13 @@
         <v>100</v>
       </c>
       <c r="R27">
-        <v>90.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="S27">
         <v>100</v>
       </c>
       <c r="T27">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="U27">
         <v>96.7</v>
@@ -5820,13 +5835,13 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>88.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S28">
         <v>100</v>
       </c>
       <c r="T28">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="U28">
         <v>96.7</v>
@@ -5888,13 +5903,13 @@
         <v>100</v>
       </c>
       <c r="R29">
-        <v>81.8</v>
+        <v>56.3</v>
       </c>
       <c r="S29">
         <v>100</v>
       </c>
       <c r="T29">
-        <v>82.5</v>
+        <v>86.7</v>
       </c>
       <c r="U29">
         <v>90</v>
@@ -5956,13 +5971,13 @@
         <v>100</v>
       </c>
       <c r="R30">
-        <v>93.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S30">
         <v>100</v>
       </c>
       <c r="T30">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U30">
         <v>96.7</v>
@@ -6024,13 +6039,13 @@
         <v>100</v>
       </c>
       <c r="R31">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
       <c r="S31">
         <v>100</v>
       </c>
       <c r="T31">
-        <v>97.5</v>
+        <v>96.7</v>
       </c>
       <c r="U31">
         <v>93.3</v>
@@ -6092,13 +6107,13 @@
         <v>100</v>
       </c>
       <c r="R32">
-        <v>84.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="S32">
         <v>100</v>
       </c>
       <c r="T32">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U32">
         <v>93.3</v>
@@ -6160,13 +6175,13 @@
         <v>100</v>
       </c>
       <c r="R33">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
       <c r="S33">
         <v>100</v>
       </c>
       <c r="T33">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="U33">
         <v>93.3</v>
@@ -6228,10 +6243,10 @@
         <v>100</v>
       </c>
       <c r="R34">
-        <v>47.7</v>
+        <v>32.8</v>
       </c>
       <c r="S34">
-        <v>51.5</v>
+        <v>39.6</v>
       </c>
       <c r="T34">
         <v>0</v>
@@ -6296,13 +6311,13 @@
         <v>100</v>
       </c>
       <c r="R35">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="S35">
         <v>100</v>
       </c>
       <c r="T35">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="U35">
         <v>100</v>
@@ -6364,13 +6379,13 @@
         <v>100</v>
       </c>
       <c r="R36">
-        <v>84.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="S36">
         <v>100</v>
       </c>
       <c r="T36">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="U36">
         <v>96.7</v>
@@ -6500,13 +6515,13 @@
         <v>100</v>
       </c>
       <c r="R38">
-        <v>84.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="S38">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="T38">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="U38">
         <v>100</v>
@@ -6574,7 +6589,7 @@
         <v>100</v>
       </c>
       <c r="T39">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="U39">
         <v>93.3</v>
@@ -6669,7 +6684,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
@@ -6678,19 +6693,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F3" s="2">
-        <v>36.1</v>
+        <v>47.2</v>
       </c>
       <c r="G3" s="2">
-        <v>63.9</v>
+        <v>52.8</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6710,19 +6725,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F4" s="2">
-        <v>41.7</v>
+        <v>50</v>
       </c>
       <c r="G4" s="2">
-        <v>58.3</v>
+        <v>50</v>
       </c>
       <c r="H4">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6733,7 +6748,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
@@ -6742,19 +6757,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E5">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F5" s="2">
-        <v>47.2</v>
+        <v>58.3</v>
       </c>
       <c r="G5" s="2">
-        <v>52.8</v>
+        <v>41.7</v>
       </c>
       <c r="H5">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6765,7 +6780,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
@@ -6774,19 +6789,19 @@
         <v>36</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F6" s="2">
-        <v>58.3</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>41.7</v>
+        <v>30.6</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6797,7 +6812,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>67</v>
@@ -6806,19 +6821,19 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" s="2">
-        <v>75</v>
+        <v>72.2</v>
       </c>
       <c r="G7" s="2">
-        <v>25</v>
+        <v>27.8</v>
       </c>
       <c r="H7">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6829,7 +6844,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>68</v>
@@ -6838,19 +6853,19 @@
         <v>36</v>
       </c>
       <c r="D8">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E8">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F8" s="2">
-        <v>75</v>
+        <v>83.3</v>
       </c>
       <c r="G8" s="2">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="H8">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6920,7 +6935,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6952,22 +6967,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920180</v>
+        <v>23330051920183</v>
       </c>
       <c r="B2" t="s">
         <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6975,19 +6990,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920180</v>
+        <v>23330051920183</v>
       </c>
       <c r="B3" t="s">
         <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
         <v>63</v>
@@ -6998,22 +7013,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920181</v>
+        <v>23330051920184</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7021,22 +7036,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920181</v>
+        <v>23330051920184</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7050,10 +7065,10 @@
         <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -7073,16 +7088,16 @@
         <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7090,22 +7105,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920189</v>
+        <v>23330051920212</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7113,19 +7128,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920189</v>
+        <v>23330051920212</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
         <v>63</v>
@@ -7136,22 +7151,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920199</v>
+        <v>23330051920181</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7159,22 +7174,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920199</v>
+        <v>23330051920185</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7182,22 +7197,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920203</v>
+        <v>23330051920189</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -7205,22 +7220,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920203</v>
+        <v>23330051920192</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7228,22 +7243,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920212</v>
+        <v>23330051920203</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -7251,47 +7266,24 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920212</v>
+        <v>23330051920204</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D15" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>23330051920329</v>
-      </c>
-      <c r="B16" t="s">
-        <v>80</v>
-      </c>
-      <c r="C16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D16" t="s">
-        <v>96</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>63</v>
-      </c>
-      <c r="G16">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1AV - Estadisticos 20231.xlsx
+++ b/grupos/1AV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="107">
   <si>
     <t>Materia</t>
   </si>
@@ -215,15 +215,15 @@
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
+    <t>Zarate Amezcua Eladio Jorge</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Saucedo Rivalcoba Graciela</t>
   </si>
   <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
@@ -245,18 +245,24 @@
     <t>CHICO</t>
   </si>
   <si>
+    <t>ESPINOZA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>NARVAEZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>CORDOVA</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
     <t>CRUZ</t>
   </si>
   <si>
@@ -269,18 +275,21 @@
     <t>RIVERA</t>
   </si>
   <si>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>AUTRAN</t>
+  </si>
+  <si>
+    <t>LIBRADO</t>
+  </si>
+  <si>
+    <t>DAMIAN</t>
+  </si>
+  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
-    <t>AUTRAN</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>DAMIAN</t>
-  </si>
-  <si>
     <t>COCOTLE</t>
   </si>
   <si>
@@ -299,16 +308,22 @@
     <t>FERNANDO</t>
   </si>
   <si>
+    <t>JULIO CESAR</t>
+  </si>
+  <si>
+    <t>AXEL AARON</t>
+  </si>
+  <si>
+    <t>ARMANDO GABRIEL</t>
+  </si>
+  <si>
+    <t>LAZARO</t>
+  </si>
+  <si>
+    <t>JESUS JAREF</t>
+  </si>
+  <si>
     <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>AXEL AARON</t>
-  </si>
-  <si>
-    <t>ALEX URIEL</t>
-  </si>
-  <si>
-    <t>JESUS JAREF</t>
   </si>
   <si>
     <t>EMMANUEL</t>
@@ -871,7 +886,7 @@
         <v>5</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
         <v>5</v>
@@ -886,7 +901,7 @@
         <v>5</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V4">
         <v>-1</v>
@@ -907,7 +922,7 @@
         <v>5</v>
       </c>
       <c r="AB4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC4">
         <v>5</v>
@@ -960,7 +975,7 @@
         <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
         <v>5</v>
@@ -975,7 +990,7 @@
         <v>5</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V5">
         <v>-1</v>
@@ -1049,7 +1064,7 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
         <v>8</v>
@@ -1064,7 +1079,7 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>-1</v>
@@ -1085,7 +1100,7 @@
         <v>10</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC6">
         <v>6</v>
@@ -1138,7 +1153,7 @@
         <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
         <v>8</v>
@@ -1153,13 +1168,13 @@
         <v>7</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>7</v>
@@ -1227,7 +1242,7 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
         <v>5</v>
@@ -1242,13 +1257,13 @@
         <v>9</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V8">
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X8">
         <v>6</v>
@@ -1263,7 +1278,7 @@
         <v>7</v>
       </c>
       <c r="AB8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC8">
         <v>6</v>
@@ -1316,7 +1331,7 @@
         <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
         <v>7</v>
@@ -1331,7 +1346,7 @@
         <v>5</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V9">
         <v>-1</v>
@@ -1405,7 +1420,7 @@
         <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
         <v>8</v>
@@ -1420,7 +1435,7 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
         <v>-1</v>
@@ -1494,7 +1509,7 @@
         <v>5</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
         <v>6</v>
@@ -1509,7 +1524,7 @@
         <v>7</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>-1</v>
@@ -1583,7 +1598,7 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
         <v>6</v>
@@ -1598,7 +1613,7 @@
         <v>5</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>-1</v>
@@ -1619,7 +1634,7 @@
         <v>6</v>
       </c>
       <c r="AB12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC12">
         <v>7</v>
@@ -1672,7 +1687,7 @@
         <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
         <v>7</v>
@@ -1687,7 +1702,7 @@
         <v>8</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V13">
         <v>-1</v>
@@ -1708,7 +1723,7 @@
         <v>6</v>
       </c>
       <c r="AB13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC13">
         <v>7</v>
@@ -1761,7 +1776,7 @@
         <v>6</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
         <v>8</v>
@@ -1776,7 +1791,7 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
         <v>-1</v>
@@ -1850,7 +1865,7 @@
         <v>5</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -1865,7 +1880,7 @@
         <v>5</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V15">
         <v>-1</v>
@@ -1939,7 +1954,7 @@
         <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q16">
         <v>7</v>
@@ -1954,7 +1969,7 @@
         <v>8</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V16">
         <v>-1</v>
@@ -1975,7 +1990,7 @@
         <v>6</v>
       </c>
       <c r="AB16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC16">
         <v>5</v>
@@ -2028,7 +2043,7 @@
         <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -2043,7 +2058,7 @@
         <v>9</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>-1</v>
@@ -2117,7 +2132,7 @@
         <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
         <v>7</v>
@@ -2132,7 +2147,7 @@
         <v>5</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>-1</v>
@@ -2153,7 +2168,7 @@
         <v>5</v>
       </c>
       <c r="AB18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC18">
         <v>5</v>
@@ -2206,7 +2221,7 @@
         <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <v>7</v>
@@ -2221,7 +2236,7 @@
         <v>8</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>-1</v>
@@ -2242,7 +2257,7 @@
         <v>6</v>
       </c>
       <c r="AB19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC19">
         <v>6</v>
@@ -2295,7 +2310,7 @@
         <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
         <v>7</v>
@@ -2310,7 +2325,7 @@
         <v>9</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V20">
         <v>-1</v>
@@ -2384,7 +2399,7 @@
         <v>5</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
         <v>6</v>
@@ -2399,7 +2414,7 @@
         <v>5</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V21">
         <v>-1</v>
@@ -2473,7 +2488,7 @@
         <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
         <v>6</v>
@@ -2488,7 +2503,7 @@
         <v>5</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V22">
         <v>-1</v>
@@ -2562,7 +2577,7 @@
         <v>5</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
         <v>7</v>
@@ -2577,7 +2592,7 @@
         <v>8</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>-1</v>
@@ -2651,7 +2666,7 @@
         <v>5</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
         <v>5</v>
@@ -2666,7 +2681,7 @@
         <v>5</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V24">
         <v>-1</v>
@@ -2740,7 +2755,7 @@
         <v>5</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q25">
         <v>6</v>
@@ -2755,7 +2770,7 @@
         <v>5</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V25">
         <v>-1</v>
@@ -2829,7 +2844,7 @@
         <v>5</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q26">
         <v>7</v>
@@ -2844,13 +2859,13 @@
         <v>7</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V26">
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>7</v>
@@ -2918,7 +2933,7 @@
         <v>5</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
         <v>7</v>
@@ -2933,7 +2948,7 @@
         <v>7</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V27">
         <v>-1</v>
@@ -2954,7 +2969,7 @@
         <v>6</v>
       </c>
       <c r="AB27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC27">
         <v>6</v>
@@ -3007,7 +3022,7 @@
         <v>5</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q28">
         <v>7</v>
@@ -3022,7 +3037,7 @@
         <v>9</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
         <v>-1</v>
@@ -3096,7 +3111,7 @@
         <v>5</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q29">
         <v>5</v>
@@ -3111,7 +3126,7 @@
         <v>5</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V29">
         <v>-1</v>
@@ -3185,7 +3200,7 @@
         <v>6</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q30">
         <v>8</v>
@@ -3200,13 +3215,13 @@
         <v>8</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V30">
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X30">
         <v>8</v>
@@ -3274,7 +3289,7 @@
         <v>5</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q31">
         <v>7</v>
@@ -3289,7 +3304,7 @@
         <v>7</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>-1</v>
@@ -3310,7 +3325,7 @@
         <v>6</v>
       </c>
       <c r="AB31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC31">
         <v>5</v>
@@ -3363,7 +3378,7 @@
         <v>5</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -3378,13 +3393,13 @@
         <v>9</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V32">
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X32">
         <v>7</v>
@@ -3399,7 +3414,7 @@
         <v>7</v>
       </c>
       <c r="AB32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC32">
         <v>6</v>
@@ -3452,7 +3467,7 @@
         <v>5</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q33">
         <v>7</v>
@@ -3467,7 +3482,7 @@
         <v>7</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
         <v>-1</v>
@@ -3488,7 +3503,7 @@
         <v>7</v>
       </c>
       <c r="AB33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC33">
         <v>6</v>
@@ -3541,7 +3556,7 @@
         <v>5</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q34">
         <v>5</v>
@@ -3556,7 +3571,7 @@
         <v>5</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V34">
         <v>-1</v>
@@ -3630,7 +3645,7 @@
         <v>6</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q35">
         <v>7</v>
@@ -3645,7 +3660,7 @@
         <v>7</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V35">
         <v>-1</v>
@@ -3719,7 +3734,7 @@
         <v>5</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q36">
         <v>7</v>
@@ -3734,7 +3749,7 @@
         <v>8</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V36">
         <v>-1</v>
@@ -3808,7 +3823,7 @@
         <v>6</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q37">
         <v>7</v>
@@ -3823,7 +3838,7 @@
         <v>9</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V37">
         <v>-1</v>
@@ -3897,7 +3912,7 @@
         <v>5</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q38">
         <v>6</v>
@@ -3912,7 +3927,7 @@
         <v>7</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V38">
         <v>-1</v>
@@ -3933,7 +3948,7 @@
         <v>6</v>
       </c>
       <c r="AB38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC38">
         <v>5</v>
@@ -3986,7 +4001,7 @@
         <v>5</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q39">
         <v>7</v>
@@ -4001,13 +4016,13 @@
         <v>8</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V39">
         <v>-1</v>
       </c>
       <c r="W39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X39">
         <v>7</v>
@@ -4022,7 +4037,7 @@
         <v>6</v>
       </c>
       <c r="AB39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC39">
         <v>5</v>
@@ -4197,7 +4212,7 @@
         <v>35</v>
       </c>
       <c r="P4">
-        <v>65</v>
+        <v>41.9</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -4212,7 +4227,7 @@
         <v>55</v>
       </c>
       <c r="U4">
-        <v>50</v>
+        <v>31.3</v>
       </c>
       <c r="V4">
         <v>35</v>
@@ -4265,7 +4280,7 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>40</v>
+        <v>25.8</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -4280,7 +4295,7 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="V5">
         <v>0</v>
@@ -4333,7 +4348,7 @@
         <v>97.5</v>
       </c>
       <c r="P6">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -4401,7 +4416,7 @@
         <v>85</v>
       </c>
       <c r="P7">
-        <v>90</v>
+        <v>93.5</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -4469,7 +4484,7 @@
         <v>90</v>
       </c>
       <c r="P8">
-        <v>90</v>
+        <v>93.5</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -4484,7 +4499,7 @@
         <v>100</v>
       </c>
       <c r="U8">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="V8">
         <v>90</v>
@@ -4537,7 +4552,7 @@
         <v>70</v>
       </c>
       <c r="P9">
-        <v>60</v>
+        <v>45.2</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -4552,7 +4567,7 @@
         <v>91.7</v>
       </c>
       <c r="U9">
-        <v>80</v>
+        <v>60.4</v>
       </c>
       <c r="V9">
         <v>70</v>
@@ -4605,7 +4620,7 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>90</v>
+        <v>93.5</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -4673,7 +4688,7 @@
         <v>82.5</v>
       </c>
       <c r="P11">
-        <v>85</v>
+        <v>90.3</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -4688,7 +4703,7 @@
         <v>96.7</v>
       </c>
       <c r="U11">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="V11">
         <v>82.5</v>
@@ -4741,7 +4756,7 @@
         <v>92.5</v>
       </c>
       <c r="P12">
-        <v>85</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -4756,7 +4771,7 @@
         <v>90</v>
       </c>
       <c r="U12">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V12">
         <v>92.5</v>
@@ -4809,7 +4824,7 @@
         <v>92.5</v>
       </c>
       <c r="P13">
-        <v>85</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -4824,7 +4839,7 @@
         <v>91.7</v>
       </c>
       <c r="U13">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V13">
         <v>92.5</v>
@@ -4892,7 +4907,7 @@
         <v>96.7</v>
       </c>
       <c r="U14">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="V14">
         <v>97.5</v>
@@ -4945,7 +4960,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>35</v>
+        <v>22.6</v>
       </c>
       <c r="Q15">
         <v>75.59999999999999</v>
@@ -5013,7 +5028,7 @@
         <v>80</v>
       </c>
       <c r="P16">
-        <v>90</v>
+        <v>58.1</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -5028,7 +5043,7 @@
         <v>90</v>
       </c>
       <c r="U16">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="V16">
         <v>80</v>
@@ -5081,7 +5096,7 @@
         <v>82.5</v>
       </c>
       <c r="P17">
-        <v>90</v>
+        <v>93.5</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -5149,7 +5164,7 @@
         <v>75</v>
       </c>
       <c r="P18">
-        <v>75</v>
+        <v>48.4</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -5164,7 +5179,7 @@
         <v>93.3</v>
       </c>
       <c r="U18">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="V18">
         <v>75</v>
@@ -5217,7 +5232,7 @@
         <v>95</v>
       </c>
       <c r="P19">
-        <v>90</v>
+        <v>90.3</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -5285,7 +5300,7 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>95</v>
+        <v>93.5</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -5353,7 +5368,7 @@
         <v>72.5</v>
       </c>
       <c r="P21">
-        <v>70</v>
+        <v>45.2</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -5368,7 +5383,7 @@
         <v>90</v>
       </c>
       <c r="U21">
-        <v>83.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="V21">
         <v>72.5</v>
@@ -5421,7 +5436,7 @@
         <v>72.5</v>
       </c>
       <c r="P22">
-        <v>85</v>
+        <v>54.8</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -5436,7 +5451,7 @@
         <v>86.7</v>
       </c>
       <c r="U22">
-        <v>83.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="V22">
         <v>72.5</v>
@@ -5489,7 +5504,7 @@
         <v>65</v>
       </c>
       <c r="P23">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -5504,7 +5519,7 @@
         <v>100</v>
       </c>
       <c r="U23">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V23">
         <v>65</v>
@@ -5557,7 +5572,7 @@
         <v>30</v>
       </c>
       <c r="P24">
-        <v>55</v>
+        <v>35.5</v>
       </c>
       <c r="Q24">
         <v>77.8</v>
@@ -5572,7 +5587,7 @@
         <v>51.7</v>
       </c>
       <c r="U24">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="V24">
         <v>30</v>
@@ -5625,7 +5640,7 @@
         <v>37.5</v>
       </c>
       <c r="P25">
-        <v>80</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="Q25">
         <v>100</v>
@@ -5640,7 +5655,7 @@
         <v>81.7</v>
       </c>
       <c r="U25">
-        <v>83.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="V25">
         <v>37.5</v>
@@ -5693,7 +5708,7 @@
         <v>95</v>
       </c>
       <c r="P26">
-        <v>80</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -5761,7 +5776,7 @@
         <v>82.5</v>
       </c>
       <c r="P27">
-        <v>75</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -5776,7 +5791,7 @@
         <v>95</v>
       </c>
       <c r="U27">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V27">
         <v>82.5</v>
@@ -5829,7 +5844,7 @@
         <v>97.5</v>
       </c>
       <c r="P28">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -5844,7 +5859,7 @@
         <v>98.3</v>
       </c>
       <c r="U28">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V28">
         <v>97.5</v>
@@ -5897,7 +5912,7 @@
         <v>80</v>
       </c>
       <c r="P29">
-        <v>65</v>
+        <v>41.9</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -5912,7 +5927,7 @@
         <v>86.7</v>
       </c>
       <c r="U29">
-        <v>90</v>
+        <v>56.3</v>
       </c>
       <c r="V29">
         <v>80</v>
@@ -5965,7 +5980,7 @@
         <v>90</v>
       </c>
       <c r="P30">
-        <v>75</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -5980,7 +5995,7 @@
         <v>96.7</v>
       </c>
       <c r="U30">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V30">
         <v>90</v>
@@ -6033,7 +6048,7 @@
         <v>82.5</v>
       </c>
       <c r="P31">
-        <v>75</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="Q31">
         <v>100</v>
@@ -6048,7 +6063,7 @@
         <v>96.7</v>
       </c>
       <c r="U31">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="V31">
         <v>82.5</v>
@@ -6101,7 +6116,7 @@
         <v>92.5</v>
       </c>
       <c r="P32">
-        <v>75</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="Q32">
         <v>100</v>
@@ -6116,7 +6131,7 @@
         <v>96.7</v>
       </c>
       <c r="U32">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="V32">
         <v>92.5</v>
@@ -6169,7 +6184,7 @@
         <v>87.5</v>
       </c>
       <c r="P33">
-        <v>85</v>
+        <v>90.3</v>
       </c>
       <c r="Q33">
         <v>100</v>
@@ -6184,7 +6199,7 @@
         <v>91.7</v>
       </c>
       <c r="U33">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="V33">
         <v>87.5</v>
@@ -6237,7 +6252,7 @@
         <v>22.5</v>
       </c>
       <c r="P34">
-        <v>40</v>
+        <v>25.8</v>
       </c>
       <c r="Q34">
         <v>100</v>
@@ -6252,7 +6267,7 @@
         <v>0</v>
       </c>
       <c r="U34">
-        <v>83.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="V34">
         <v>22.5</v>
@@ -6305,7 +6320,7 @@
         <v>95</v>
       </c>
       <c r="P35">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="Q35">
         <v>100</v>
@@ -6373,7 +6388,7 @@
         <v>72.5</v>
       </c>
       <c r="P36">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="Q36">
         <v>100</v>
@@ -6388,7 +6403,7 @@
         <v>91.7</v>
       </c>
       <c r="U36">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V36">
         <v>72.5</v>
@@ -6509,7 +6524,7 @@
         <v>85</v>
       </c>
       <c r="P38">
-        <v>70</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="Q38">
         <v>100</v>
@@ -6577,7 +6592,7 @@
         <v>77.5</v>
       </c>
       <c r="P39">
-        <v>80</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="Q39">
         <v>100</v>
@@ -6592,7 +6607,7 @@
         <v>95</v>
       </c>
       <c r="U39">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="V39">
         <v>77.5</v>
@@ -6661,19 +6676,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="2">
-        <v>36.1</v>
+        <v>33.3</v>
       </c>
       <c r="G2" s="2">
-        <v>63.9</v>
+        <v>66.7</v>
       </c>
       <c r="H2">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6748,7 +6763,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
@@ -6757,19 +6772,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F5" s="2">
-        <v>58.3</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>41.7</v>
+        <v>30.6</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6780,7 +6795,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
@@ -6789,19 +6804,19 @@
         <v>36</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F6" s="2">
-        <v>69.40000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="G6" s="2">
-        <v>30.6</v>
+        <v>27.8</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6812,7 +6827,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>67</v>
@@ -6833,7 +6848,7 @@
         <v>27.8</v>
       </c>
       <c r="H7">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6935,7 +6950,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6973,10 +6988,10 @@
         <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -6996,10 +7011,10 @@
         <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -7013,16 +7028,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920184</v>
+        <v>23330051920188</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -7036,22 +7051,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920184</v>
+        <v>23330051920188</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7065,10 +7080,10 @@
         <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -7088,10 +7103,10 @@
         <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -7105,22 +7120,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920212</v>
+        <v>23330051920324</v>
       </c>
       <c r="B8" t="s">
         <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7128,22 +7143,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920212</v>
+        <v>23330051920324</v>
       </c>
       <c r="B9" t="s">
         <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7151,22 +7166,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920181</v>
+        <v>23330051920202</v>
       </c>
       <c r="B10" t="s">
         <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7174,22 +7189,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920185</v>
+        <v>23330051920202</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7197,22 +7212,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920189</v>
+        <v>23330051920181</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
         <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -7220,7 +7235,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920192</v>
+        <v>23330051920184</v>
       </c>
       <c r="B13" t="s">
         <v>80</v>
@@ -7229,13 +7244,13 @@
         <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7243,7 +7258,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920203</v>
+        <v>23330051920185</v>
       </c>
       <c r="B14" t="s">
         <v>81</v>
@@ -7252,13 +7267,13 @@
         <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -7266,16 +7281,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920204</v>
+        <v>23330051920189</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
         <v>91</v>
       </c>
       <c r="D15" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E15" t="s">
         <v>5</v>
@@ -7284,6 +7299,75 @@
         <v>62</v>
       </c>
       <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>23330051920192</v>
+      </c>
+      <c r="B16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" t="s">
+        <v>104</v>
+      </c>
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
+        <v>64</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>23330051920203</v>
+      </c>
+      <c r="B17" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D17" t="s">
+        <v>105</v>
+      </c>
+      <c r="E17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" t="s">
+        <v>64</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>23330051920204</v>
+      </c>
+      <c r="B18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E18" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" t="s">
+        <v>62</v>
+      </c>
+      <c r="G18">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1AV - Estadisticos 20231.xlsx
+++ b/grupos/1AV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="107">
   <si>
     <t>Materia</t>
   </si>
@@ -251,9 +251,6 @@
     <t>FLORES</t>
   </si>
   <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
     <t>NARVAEZ</t>
   </si>
   <si>
@@ -269,6 +266,9 @@
     <t>GARCIA</t>
   </si>
   <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
@@ -281,9 +281,6 @@
     <t>AUTRAN</t>
   </si>
   <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
     <t>DAMIAN</t>
   </si>
   <si>
@@ -299,6 +296,9 @@
     <t>CARRERA</t>
   </si>
   <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
@@ -314,9 +314,6 @@
     <t>AXEL AARON</t>
   </si>
   <si>
-    <t>ARMANDO GABRIEL</t>
-  </si>
-  <si>
     <t>LAZARO</t>
   </si>
   <si>
@@ -333,6 +330,9 @@
   </si>
   <si>
     <t>KEVYN DANIEL</t>
+  </si>
+  <si>
+    <t>SABDY</t>
   </si>
   <si>
     <t>LUIS FABIAN</t>
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W4">
         <v>5</v>
@@ -993,7 +993,7 @@
         <v>0</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W5">
         <v>5</v>
@@ -1082,7 +1082,7 @@
         <v>8</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>7</v>
@@ -1171,7 +1171,7 @@
         <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W7">
         <v>6</v>
@@ -1260,7 +1260,7 @@
         <v>5</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>6</v>
@@ -1349,7 +1349,7 @@
         <v>0</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W9">
         <v>5</v>
@@ -1438,7 +1438,7 @@
         <v>10</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W10">
         <v>8</v>
@@ -1527,7 +1527,7 @@
         <v>7</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W11">
         <v>5</v>
@@ -1616,7 +1616,7 @@
         <v>8</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>5</v>
@@ -1637,7 +1637,7 @@
         <v>6</v>
       </c>
       <c r="AC12">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1705,7 +1705,7 @@
         <v>5</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>5</v>
@@ -1794,7 +1794,7 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W14">
         <v>7</v>
@@ -1815,7 +1815,7 @@
         <v>10</v>
       </c>
       <c r="AC14">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W15">
         <v>5</v>
@@ -1972,7 +1972,7 @@
         <v>8</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W16">
         <v>5</v>
@@ -2061,7 +2061,7 @@
         <v>8</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W17">
         <v>5</v>
@@ -2150,7 +2150,7 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W18">
         <v>5</v>
@@ -2239,7 +2239,7 @@
         <v>8</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W19">
         <v>5</v>
@@ -2328,7 +2328,7 @@
         <v>10</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>6</v>
@@ -2349,7 +2349,7 @@
         <v>9</v>
       </c>
       <c r="AC20">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2417,7 +2417,7 @@
         <v>5</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W21">
         <v>5</v>
@@ -2506,7 +2506,7 @@
         <v>5</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W22">
         <v>5</v>
@@ -2595,7 +2595,7 @@
         <v>7</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W23">
         <v>5</v>
@@ -2684,7 +2684,7 @@
         <v>0</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W24">
         <v>5</v>
@@ -2773,7 +2773,7 @@
         <v>5</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W25">
         <v>5</v>
@@ -2862,7 +2862,7 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W26">
         <v>6</v>
@@ -2883,7 +2883,7 @@
         <v>9</v>
       </c>
       <c r="AC26">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2951,7 +2951,7 @@
         <v>8</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W27">
         <v>5</v>
@@ -2972,7 +2972,7 @@
         <v>6</v>
       </c>
       <c r="AC27">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3040,7 +3040,7 @@
         <v>10</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W28">
         <v>7</v>
@@ -3129,7 +3129,7 @@
         <v>0</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W29">
         <v>5</v>
@@ -3218,7 +3218,7 @@
         <v>10</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W30">
         <v>7</v>
@@ -3307,7 +3307,7 @@
         <v>7</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W31">
         <v>5</v>
@@ -3396,7 +3396,7 @@
         <v>10</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W32">
         <v>6</v>
@@ -3485,7 +3485,7 @@
         <v>10</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W33">
         <v>5</v>
@@ -3574,7 +3574,7 @@
         <v>5</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W34">
         <v>5</v>
@@ -3663,7 +3663,7 @@
         <v>10</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W35">
         <v>7</v>
@@ -3684,7 +3684,7 @@
         <v>10</v>
       </c>
       <c r="AC35">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -3752,7 +3752,7 @@
         <v>7</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W36">
         <v>5</v>
@@ -3841,7 +3841,7 @@
         <v>10</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W37">
         <v>8</v>
@@ -3930,7 +3930,7 @@
         <v>7</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W38">
         <v>5</v>
@@ -3951,7 +3951,7 @@
         <v>6</v>
       </c>
       <c r="AC38">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:29">
@@ -4019,7 +4019,7 @@
         <v>10</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W39">
         <v>5</v>
@@ -4230,7 +4230,7 @@
         <v>31.3</v>
       </c>
       <c r="V4">
-        <v>35</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -4366,7 +4366,7 @@
         <v>100</v>
       </c>
       <c r="V6">
-        <v>97.5</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -4434,7 +4434,7 @@
         <v>100</v>
       </c>
       <c r="V7">
-        <v>85</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -4502,7 +4502,7 @@
         <v>95.8</v>
       </c>
       <c r="V8">
-        <v>90</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -4570,7 +4570,7 @@
         <v>60.4</v>
       </c>
       <c r="V9">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -4706,7 +4706,7 @@
         <v>95.8</v>
       </c>
       <c r="V11">
-        <v>82.5</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -4774,7 +4774,7 @@
         <v>97.90000000000001</v>
       </c>
       <c r="V12">
-        <v>92.5</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -4842,7 +4842,7 @@
         <v>97.90000000000001</v>
       </c>
       <c r="V13">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -4910,7 +4910,7 @@
         <v>95.8</v>
       </c>
       <c r="V14">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -4978,7 +4978,7 @@
         <v>0</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -5046,7 +5046,7 @@
         <v>95.8</v>
       </c>
       <c r="V16">
-        <v>80</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -5114,7 +5114,7 @@
         <v>100</v>
       </c>
       <c r="V17">
-        <v>82.5</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -5182,7 +5182,7 @@
         <v>93.8</v>
       </c>
       <c r="V18">
-        <v>75</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -5250,7 +5250,7 @@
         <v>100</v>
       </c>
       <c r="V19">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -5318,7 +5318,7 @@
         <v>100</v>
       </c>
       <c r="V20">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -5386,7 +5386,7 @@
         <v>85.40000000000001</v>
       </c>
       <c r="V21">
-        <v>72.5</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -5454,7 +5454,7 @@
         <v>85.40000000000001</v>
       </c>
       <c r="V22">
-        <v>72.5</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -5522,7 +5522,7 @@
         <v>97.90000000000001</v>
       </c>
       <c r="V23">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -5590,7 +5590,7 @@
         <v>50</v>
       </c>
       <c r="V24">
-        <v>30</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -5658,7 +5658,7 @@
         <v>85.40000000000001</v>
       </c>
       <c r="V25">
-        <v>37.5</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -5726,7 +5726,7 @@
         <v>100</v>
       </c>
       <c r="V26">
-        <v>95</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -5794,7 +5794,7 @@
         <v>97.90000000000001</v>
       </c>
       <c r="V27">
-        <v>82.5</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -5862,7 +5862,7 @@
         <v>97.90000000000001</v>
       </c>
       <c r="V28">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -5930,7 +5930,7 @@
         <v>56.3</v>
       </c>
       <c r="V29">
-        <v>80</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -5998,7 +5998,7 @@
         <v>97.90000000000001</v>
       </c>
       <c r="V30">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -6066,7 +6066,7 @@
         <v>95.8</v>
       </c>
       <c r="V31">
-        <v>82.5</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -6134,7 +6134,7 @@
         <v>95.8</v>
       </c>
       <c r="V32">
-        <v>92.5</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -6202,7 +6202,7 @@
         <v>95.8</v>
       </c>
       <c r="V33">
-        <v>87.5</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -6270,7 +6270,7 @@
         <v>85.40000000000001</v>
       </c>
       <c r="V34">
-        <v>22.5</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -6338,7 +6338,7 @@
         <v>100</v>
       </c>
       <c r="V35">
-        <v>95</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -6406,7 +6406,7 @@
         <v>97.90000000000001</v>
       </c>
       <c r="V36">
-        <v>72.5</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -6474,7 +6474,7 @@
         <v>100</v>
       </c>
       <c r="V37">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -6542,7 +6542,7 @@
         <v>100</v>
       </c>
       <c r="V38">
-        <v>85</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -6610,7 +6610,7 @@
         <v>95.8</v>
       </c>
       <c r="V39">
-        <v>77.5</v>
+        <v>82.8</v>
       </c>
     </row>
   </sheetData>
@@ -6708,19 +6708,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="2">
-        <v>47.2</v>
+        <v>44.4</v>
       </c>
       <c r="G3" s="2">
-        <v>52.8</v>
+        <v>55.6</v>
       </c>
       <c r="H3">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6950,7 +6950,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7120,13 +7120,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920324</v>
+        <v>23330051920202</v>
       </c>
       <c r="B8" t="s">
         <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
         <v>98</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920324</v>
+        <v>23330051920202</v>
       </c>
       <c r="B9" t="s">
         <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
         <v>98</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7166,22 +7166,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920202</v>
+        <v>23330051920181</v>
       </c>
       <c r="B10" t="s">
         <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
         <v>99</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7189,22 +7189,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920202</v>
+        <v>23330051920184</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7212,22 +7212,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920181</v>
+        <v>23330051920185</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -7235,16 +7235,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920184</v>
+        <v>23330051920189</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E13" t="s">
         <v>5</v>
@@ -7258,22 +7258,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920185</v>
+        <v>23330051920192</v>
       </c>
       <c r="B14" t="s">
         <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -7281,22 +7281,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920189</v>
+        <v>23330051920329</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -7304,16 +7304,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920192</v>
+        <v>23330051920203</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
@@ -7327,47 +7327,24 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920203</v>
+        <v>23330051920204</v>
       </c>
       <c r="B17" t="s">
         <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F17" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>23330051920204</v>
-      </c>
-      <c r="B18" t="s">
-        <v>83</v>
-      </c>
-      <c r="C18" t="s">
-        <v>94</v>
-      </c>
-      <c r="D18" t="s">
-        <v>106</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>62</v>
-      </c>
-      <c r="G18">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1AV - Estadisticos 20231.xlsx
+++ b/grupos/1AV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="107">
   <si>
     <t>Materia</t>
   </si>
@@ -56,6 +56,9 @@
     <t>Pensamiento matemático I</t>
   </si>
   <si>
+    <t>Recursos socioemocionales I</t>
+  </si>
+  <si>
     <t>Nombre</t>
   </si>
   <si>
@@ -201,9 +204,6 @@
   </si>
   <si>
     <t>Por_Blancos</t>
-  </si>
-  <si>
-    <t>Recursos socioemocionales I</t>
   </si>
   <si>
     <t>Silva Villegas Mario</t>
@@ -700,13 +700,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AG39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:33">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -717,35 +717,39 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="1"/>
+      <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-      <c r="W1" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
+      <c r="Z1" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
-    </row>
-    <row r="2" spans="1:29">
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+    </row>
+    <row r="2" spans="1:33">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -771,77 +775,89 @@
         <v>11</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="O2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="U2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="V2" s="1" t="s">
+      <c r="W2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="W2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="Y2" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AE2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:29">
+      <c r="AG2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33">
       <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>5</v>
@@ -865,17 +881,17 @@
         <v>5</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J4">
         <v>5</v>
       </c>
       <c r="K4">
+        <v>5</v>
+      </c>
+      <c r="L4">
         <v>4</v>
       </c>
-      <c r="L4">
-        <v>5</v>
-      </c>
       <c r="M4">
         <v>5</v>
       </c>
@@ -889,31 +905,31 @@
         <v>5</v>
       </c>
       <c r="Q4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R4">
+        <v>5</v>
+      </c>
+      <c r="S4">
+        <v>5</v>
+      </c>
+      <c r="T4">
         <v>0</v>
       </c>
-      <c r="S4">
-        <v>5</v>
-      </c>
-      <c r="T4">
-        <v>5</v>
-      </c>
       <c r="U4">
+        <v>5</v>
+      </c>
+      <c r="V4">
+        <v>5</v>
+      </c>
+      <c r="W4">
         <v>0</v>
       </c>
-      <c r="V4">
-        <v>5</v>
-      </c>
-      <c r="W4">
-        <v>5</v>
-      </c>
       <c r="X4">
         <v>5</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z4">
         <v>5</v>
@@ -927,10 +943,22 @@
       <c r="AC4">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:29">
+      <c r="AD4">
+        <v>5</v>
+      </c>
+      <c r="AE4">
+        <v>5</v>
+      </c>
+      <c r="AF4">
+        <v>5</v>
+      </c>
+      <c r="AG4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>5</v>
@@ -954,17 +982,17 @@
         <v>5</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J5">
         <v>5</v>
       </c>
       <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="L5">
         <v>4</v>
       </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
       <c r="M5">
         <v>5</v>
       </c>
@@ -978,31 +1006,31 @@
         <v>5</v>
       </c>
       <c r="Q5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R5">
+        <v>5</v>
+      </c>
+      <c r="S5">
+        <v>5</v>
+      </c>
+      <c r="T5">
         <v>0</v>
       </c>
-      <c r="S5">
-        <v>5</v>
-      </c>
-      <c r="T5">
-        <v>5</v>
-      </c>
       <c r="U5">
+        <v>5</v>
+      </c>
+      <c r="V5">
+        <v>5</v>
+      </c>
+      <c r="W5">
         <v>0</v>
       </c>
-      <c r="V5">
-        <v>5</v>
-      </c>
-      <c r="W5">
-        <v>5</v>
-      </c>
       <c r="X5">
         <v>5</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z5">
         <v>5</v>
@@ -1016,10 +1044,22 @@
       <c r="AC5">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:29">
+      <c r="AD5">
+        <v>5</v>
+      </c>
+      <c r="AE5">
+        <v>5</v>
+      </c>
+      <c r="AF5">
+        <v>5</v>
+      </c>
+      <c r="AG5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>7</v>
@@ -1043,72 +1083,84 @@
         <v>7</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N6">
         <v>10</v>
       </c>
       <c r="O6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S6">
         <v>8</v>
       </c>
       <c r="T6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U6">
         <v>8</v>
       </c>
       <c r="V6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB6">
+        <v>6</v>
+      </c>
+      <c r="AC6">
+        <v>8</v>
+      </c>
+      <c r="AD6">
+        <v>10</v>
+      </c>
+      <c r="AE6">
         <v>9</v>
       </c>
-      <c r="AC6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29">
+      <c r="AF6">
+        <v>6</v>
+      </c>
+      <c r="AG6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>8</v>
@@ -1132,72 +1184,84 @@
         <v>6</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N7">
+        <v>5</v>
+      </c>
+      <c r="O7">
         <v>9</v>
       </c>
-      <c r="O7">
-        <v>6</v>
-      </c>
       <c r="P7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="S7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U7">
         <v>10</v>
       </c>
       <c r="V7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z7">
+        <v>6</v>
+      </c>
+      <c r="AA7">
+        <v>7</v>
+      </c>
+      <c r="AB7">
+        <v>6</v>
+      </c>
+      <c r="AC7">
         <v>9</v>
       </c>
-      <c r="AA7">
-        <v>6</v>
-      </c>
-      <c r="AB7">
+      <c r="AD7">
+        <v>6</v>
+      </c>
+      <c r="AE7">
         <v>9</v>
       </c>
-      <c r="AC7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29">
+      <c r="AF7">
+        <v>6</v>
+      </c>
+      <c r="AG7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>8</v>
@@ -1221,20 +1285,20 @@
         <v>6</v>
       </c>
       <c r="I8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J8">
         <v>6</v>
       </c>
       <c r="K8">
+        <v>6</v>
+      </c>
+      <c r="L8">
         <v>4</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>9</v>
       </c>
-      <c r="M8">
-        <v>6</v>
-      </c>
       <c r="N8">
         <v>6</v>
       </c>
@@ -1242,51 +1306,63 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R8">
+        <v>5</v>
+      </c>
+      <c r="S8">
+        <v>5</v>
+      </c>
+      <c r="T8">
         <v>4</v>
       </c>
-      <c r="S8">
+      <c r="U8">
         <v>4</v>
       </c>
-      <c r="T8">
+      <c r="V8">
         <v>9</v>
       </c>
-      <c r="U8">
-        <v>5</v>
-      </c>
-      <c r="V8">
-        <v>6</v>
-      </c>
       <c r="W8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X8">
         <v>6</v>
       </c>
       <c r="Y8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD8">
+        <v>7</v>
+      </c>
+      <c r="AE8">
+        <v>7</v>
+      </c>
+      <c r="AF8">
+        <v>6</v>
+      </c>
+      <c r="AG8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>5</v>
@@ -1310,13 +1386,13 @@
         <v>5</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L9">
         <v>5</v>
@@ -1334,37 +1410,37 @@
         <v>5</v>
       </c>
       <c r="Q9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R9">
+        <v>5</v>
+      </c>
+      <c r="S9">
+        <v>7</v>
+      </c>
+      <c r="T9">
         <v>4</v>
       </c>
-      <c r="S9">
-        <v>6</v>
-      </c>
-      <c r="T9">
-        <v>5</v>
-      </c>
       <c r="U9">
+        <v>6</v>
+      </c>
+      <c r="V9">
+        <v>5</v>
+      </c>
+      <c r="W9">
         <v>0</v>
       </c>
-      <c r="V9">
-        <v>5</v>
-      </c>
-      <c r="W9">
-        <v>5</v>
-      </c>
       <c r="X9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z9">
         <v>5</v>
       </c>
       <c r="AA9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB9">
         <v>5</v>
@@ -1372,10 +1448,22 @@
       <c r="AC9">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:29">
+      <c r="AD9">
+        <v>5</v>
+      </c>
+      <c r="AE9">
+        <v>5</v>
+      </c>
+      <c r="AF9">
+        <v>5</v>
+      </c>
+      <c r="AG9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>8</v>
@@ -1399,34 +1487,34 @@
         <v>8</v>
       </c>
       <c r="I10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M10">
+        <v>7</v>
+      </c>
+      <c r="N10">
         <v>9</v>
       </c>
-      <c r="N10">
-        <v>10</v>
-      </c>
       <c r="O10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="S10">
         <v>8</v>
@@ -1435,36 +1523,48 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC10">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:29">
+      <c r="AD10">
+        <v>10</v>
+      </c>
+      <c r="AE10">
+        <v>10</v>
+      </c>
+      <c r="AF10">
+        <v>7</v>
+      </c>
+      <c r="AG10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>5</v>
@@ -1488,72 +1588,84 @@
         <v>5</v>
       </c>
       <c r="I11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>6</v>
       </c>
       <c r="S11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB11">
         <v>6</v>
       </c>
       <c r="AC11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD11">
+        <v>6</v>
+      </c>
+      <c r="AE11">
+        <v>6</v>
+      </c>
+      <c r="AF11">
+        <v>5</v>
+      </c>
+      <c r="AG11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>5</v>
@@ -1577,58 +1689,58 @@
         <v>7</v>
       </c>
       <c r="I12">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>9</v>
       </c>
       <c r="N12">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S12">
+        <v>6</v>
+      </c>
+      <c r="T12">
+        <v>7</v>
+      </c>
+      <c r="U12">
         <v>3</v>
       </c>
-      <c r="T12">
-        <v>5</v>
-      </c>
-      <c r="U12">
-        <v>8</v>
-      </c>
       <c r="V12">
         <v>5</v>
       </c>
       <c r="W12">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA12">
         <v>6</v>
@@ -1637,12 +1749,24 @@
         <v>6</v>
       </c>
       <c r="AC12">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD12">
+        <v>6</v>
+      </c>
+      <c r="AE12">
+        <v>6</v>
+      </c>
+      <c r="AF12">
+        <v>6</v>
+      </c>
+      <c r="AG12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>6</v>
@@ -1666,61 +1790,61 @@
         <v>8</v>
       </c>
       <c r="I13">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P13">
         <v>6</v>
       </c>
       <c r="Q13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U13">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>5</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB13">
         <v>6</v>
@@ -1728,10 +1852,22 @@
       <c r="AC13">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:29">
+      <c r="AD13">
+        <v>6</v>
+      </c>
+      <c r="AE13">
+        <v>6</v>
+      </c>
+      <c r="AF13">
+        <v>7</v>
+      </c>
+      <c r="AG13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>8</v>
@@ -1755,34 +1891,34 @@
         <v>7</v>
       </c>
       <c r="I14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J14">
+        <v>6</v>
+      </c>
+      <c r="K14">
         <v>9</v>
       </c>
-      <c r="K14">
-        <v>7</v>
-      </c>
       <c r="L14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>10</v>
       </c>
       <c r="O14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="S14">
         <v>8</v>
@@ -1791,36 +1927,48 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC14">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD14">
+        <v>10</v>
+      </c>
+      <c r="AE14">
+        <v>10</v>
+      </c>
+      <c r="AF14">
+        <v>6</v>
+      </c>
+      <c r="AG14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>5</v>
@@ -1844,17 +1992,17 @@
         <v>5</v>
       </c>
       <c r="I15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J15">
         <v>5</v>
       </c>
       <c r="K15">
+        <v>5</v>
+      </c>
+      <c r="L15">
         <v>0</v>
       </c>
-      <c r="L15">
-        <v>5</v>
-      </c>
       <c r="M15">
         <v>5</v>
       </c>
@@ -1868,31 +2016,31 @@
         <v>5</v>
       </c>
       <c r="Q15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R15">
+        <v>5</v>
+      </c>
+      <c r="S15">
+        <v>5</v>
+      </c>
+      <c r="T15">
         <v>0</v>
       </c>
-      <c r="S15">
-        <v>5</v>
-      </c>
-      <c r="T15">
-        <v>5</v>
-      </c>
       <c r="U15">
+        <v>5</v>
+      </c>
+      <c r="V15">
+        <v>5</v>
+      </c>
+      <c r="W15">
         <v>0</v>
       </c>
-      <c r="V15">
-        <v>5</v>
-      </c>
-      <c r="W15">
-        <v>5</v>
-      </c>
       <c r="X15">
         <v>5</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z15">
         <v>5</v>
@@ -1906,10 +2054,22 @@
       <c r="AC15">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:29">
+      <c r="AD15">
+        <v>5</v>
+      </c>
+      <c r="AE15">
+        <v>5</v>
+      </c>
+      <c r="AF15">
+        <v>5</v>
+      </c>
+      <c r="AG15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>5</v>
@@ -1933,72 +2093,84 @@
         <v>5</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P16">
         <v>5</v>
       </c>
       <c r="Q16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>8</v>
       </c>
       <c r="V16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z16">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB16">
         <v>6</v>
       </c>
       <c r="AC16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD16">
+        <v>6</v>
+      </c>
+      <c r="AE16">
+        <v>6</v>
+      </c>
+      <c r="AF16">
+        <v>5</v>
+      </c>
+      <c r="AG16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>5</v>
@@ -2022,72 +2194,84 @@
         <v>6</v>
       </c>
       <c r="I17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M17">
+        <v>6</v>
+      </c>
+      <c r="N17">
         <v>9</v>
       </c>
-      <c r="N17">
-        <v>6</v>
-      </c>
       <c r="O17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P17">
         <v>5</v>
       </c>
       <c r="Q17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T17">
+        <v>6</v>
+      </c>
+      <c r="U17">
+        <v>8</v>
+      </c>
+      <c r="V17">
         <v>9</v>
       </c>
-      <c r="U17">
-        <v>8</v>
-      </c>
-      <c r="V17">
-        <v>5</v>
-      </c>
       <c r="W17">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA17">
+        <v>7</v>
+      </c>
+      <c r="AB17">
+        <v>6</v>
+      </c>
+      <c r="AC17">
+        <v>8</v>
+      </c>
+      <c r="AD17">
         <v>9</v>
       </c>
-      <c r="AB17">
-        <v>8</v>
-      </c>
-      <c r="AC17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:29">
+      <c r="AE17">
+        <v>8</v>
+      </c>
+      <c r="AF17">
+        <v>5</v>
+      </c>
+      <c r="AG17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>5</v>
@@ -2111,10 +2295,10 @@
         <v>6</v>
       </c>
       <c r="I18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K18">
         <v>5</v>
@@ -2135,17 +2319,17 @@
         <v>5</v>
       </c>
       <c r="Q18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R18">
+        <v>5</v>
+      </c>
+      <c r="S18">
+        <v>7</v>
+      </c>
+      <c r="T18">
         <v>0</v>
       </c>
-      <c r="S18">
-        <v>8</v>
-      </c>
-      <c r="T18">
-        <v>5</v>
-      </c>
       <c r="U18">
         <v>8</v>
       </c>
@@ -2153,30 +2337,42 @@
         <v>5</v>
       </c>
       <c r="W18">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD18">
+        <v>5</v>
+      </c>
+      <c r="AE18">
+        <v>6</v>
+      </c>
+      <c r="AF18">
+        <v>5</v>
+      </c>
+      <c r="AG18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>5</v>
@@ -2200,72 +2396,84 @@
         <v>7</v>
       </c>
       <c r="I19">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N19">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O19">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P19">
         <v>5</v>
       </c>
       <c r="Q19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U19">
         <v>8</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z19">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB19">
+        <v>6</v>
+      </c>
+      <c r="AC19">
+        <v>8</v>
+      </c>
+      <c r="AD19">
+        <v>6</v>
+      </c>
+      <c r="AE19">
         <v>9</v>
       </c>
-      <c r="AC19">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:29">
+      <c r="AF19">
+        <v>6</v>
+      </c>
+      <c r="AG19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>5</v>
@@ -2289,72 +2497,84 @@
         <v>7</v>
       </c>
       <c r="I20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L20">
+        <v>6</v>
+      </c>
+      <c r="M20">
         <v>9</v>
       </c>
-      <c r="M20">
-        <v>10</v>
-      </c>
       <c r="N20">
         <v>10</v>
       </c>
       <c r="O20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P20">
         <v>6</v>
       </c>
       <c r="Q20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S20">
+        <v>7</v>
+      </c>
+      <c r="T20">
+        <v>5</v>
+      </c>
+      <c r="U20">
         <v>9</v>
       </c>
-      <c r="T20">
+      <c r="V20">
         <v>9</v>
       </c>
-      <c r="U20">
-        <v>10</v>
-      </c>
-      <c r="V20">
-        <v>6</v>
-      </c>
       <c r="W20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z20">
+        <v>6</v>
+      </c>
+      <c r="AA20">
+        <v>7</v>
+      </c>
+      <c r="AB20">
+        <v>5</v>
+      </c>
+      <c r="AC20">
         <v>9</v>
       </c>
-      <c r="AA20">
+      <c r="AD20">
         <v>9</v>
       </c>
-      <c r="AB20">
+      <c r="AE20">
         <v>9</v>
       </c>
-      <c r="AC20">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:29">
+      <c r="AF20">
+        <v>6</v>
+      </c>
+      <c r="AG20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>5</v>
@@ -2378,19 +2598,19 @@
         <v>5</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N21">
         <v>5</v>
@@ -2402,19 +2622,19 @@
         <v>5</v>
       </c>
       <c r="Q21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R21">
+        <v>5</v>
+      </c>
+      <c r="S21">
+        <v>6</v>
+      </c>
+      <c r="T21">
         <v>4</v>
       </c>
-      <c r="S21">
-        <v>6</v>
-      </c>
-      <c r="T21">
-        <v>5</v>
-      </c>
       <c r="U21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V21">
         <v>5</v>
@@ -2423,27 +2643,39 @@
         <v>5</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y21">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB21">
         <v>5</v>
       </c>
       <c r="AC21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD21">
+        <v>5</v>
+      </c>
+      <c r="AE21">
+        <v>5</v>
+      </c>
+      <c r="AF21">
+        <v>5</v>
+      </c>
+      <c r="AG21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22">
         <v>5</v>
@@ -2467,22 +2699,22 @@
         <v>5</v>
       </c>
       <c r="I22">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J22">
         <v>5</v>
       </c>
       <c r="K22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N22">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O22">
         <v>5</v>
@@ -2491,17 +2723,17 @@
         <v>5</v>
       </c>
       <c r="Q22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R22">
+        <v>5</v>
+      </c>
+      <c r="S22">
+        <v>6</v>
+      </c>
+      <c r="T22">
         <v>4</v>
       </c>
-      <c r="S22">
-        <v>5</v>
-      </c>
-      <c r="T22">
-        <v>5</v>
-      </c>
       <c r="U22">
         <v>5</v>
       </c>
@@ -2512,16 +2744,16 @@
         <v>5</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y22">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z22">
         <v>5</v>
       </c>
       <c r="AA22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB22">
         <v>5</v>
@@ -2529,10 +2761,22 @@
       <c r="AC22">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:29">
+      <c r="AD22">
+        <v>7</v>
+      </c>
+      <c r="AE22">
+        <v>5</v>
+      </c>
+      <c r="AF22">
+        <v>5</v>
+      </c>
+      <c r="AG22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23">
         <v>5</v>
@@ -2556,55 +2800,55 @@
         <v>5</v>
       </c>
       <c r="I23">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N23">
         <v>6</v>
       </c>
       <c r="O23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P23">
         <v>5</v>
       </c>
       <c r="Q23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R23">
+        <v>5</v>
+      </c>
+      <c r="S23">
+        <v>7</v>
+      </c>
+      <c r="T23">
         <v>4</v>
       </c>
-      <c r="S23">
+      <c r="U23">
         <v>3</v>
       </c>
-      <c r="T23">
-        <v>8</v>
-      </c>
-      <c r="U23">
-        <v>7</v>
-      </c>
       <c r="V23">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y23">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z23">
         <v>5</v>
@@ -2613,15 +2857,27 @@
         <v>6</v>
       </c>
       <c r="AB23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC23">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:29">
+      <c r="AD23">
+        <v>6</v>
+      </c>
+      <c r="AE23">
+        <v>6</v>
+      </c>
+      <c r="AF23">
+        <v>5</v>
+      </c>
+      <c r="AG23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24">
         <v>5</v>
@@ -2645,17 +2901,17 @@
         <v>5</v>
       </c>
       <c r="I24">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J24">
         <v>5</v>
       </c>
       <c r="K24">
+        <v>5</v>
+      </c>
+      <c r="L24">
         <v>0</v>
       </c>
-      <c r="L24">
-        <v>5</v>
-      </c>
       <c r="M24">
         <v>5</v>
       </c>
@@ -2669,31 +2925,31 @@
         <v>5</v>
       </c>
       <c r="Q24">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R24">
+        <v>5</v>
+      </c>
+      <c r="S24">
+        <v>5</v>
+      </c>
+      <c r="T24">
         <v>0</v>
       </c>
-      <c r="S24">
-        <v>5</v>
-      </c>
-      <c r="T24">
-        <v>5</v>
-      </c>
       <c r="U24">
+        <v>5</v>
+      </c>
+      <c r="V24">
+        <v>5</v>
+      </c>
+      <c r="W24">
         <v>0</v>
       </c>
-      <c r="V24">
-        <v>5</v>
-      </c>
-      <c r="W24">
-        <v>5</v>
-      </c>
       <c r="X24">
         <v>5</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z24">
         <v>5</v>
@@ -2707,10 +2963,22 @@
       <c r="AC24">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:29">
+      <c r="AD24">
+        <v>5</v>
+      </c>
+      <c r="AE24">
+        <v>5</v>
+      </c>
+      <c r="AF24">
+        <v>5</v>
+      </c>
+      <c r="AG24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25">
         <v>5</v>
@@ -2734,19 +3002,19 @@
         <v>5</v>
       </c>
       <c r="I25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K25">
+        <v>5</v>
+      </c>
+      <c r="L25">
         <v>0</v>
       </c>
-      <c r="L25">
-        <v>6</v>
-      </c>
       <c r="M25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>5</v>
@@ -2758,19 +3026,19 @@
         <v>5</v>
       </c>
       <c r="Q25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R25">
+        <v>5</v>
+      </c>
+      <c r="S25">
+        <v>6</v>
+      </c>
+      <c r="T25">
         <v>4</v>
       </c>
-      <c r="S25">
-        <v>8</v>
-      </c>
-      <c r="T25">
-        <v>5</v>
-      </c>
       <c r="U25">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V25">
         <v>5</v>
@@ -2779,27 +3047,39 @@
         <v>5</v>
       </c>
       <c r="X25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y25">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB25">
         <v>5</v>
       </c>
       <c r="AC25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD25">
+        <v>5</v>
+      </c>
+      <c r="AE25">
+        <v>5</v>
+      </c>
+      <c r="AF25">
+        <v>5</v>
+      </c>
+      <c r="AG25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26">
         <v>8</v>
@@ -2823,7 +3103,7 @@
         <v>7</v>
       </c>
       <c r="I26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J26">
         <v>6</v>
@@ -2832,63 +3112,75 @@
         <v>6</v>
       </c>
       <c r="L26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M26">
         <v>5</v>
       </c>
       <c r="N26">
+        <v>5</v>
+      </c>
+      <c r="O26">
         <v>9</v>
       </c>
-      <c r="O26">
-        <v>5</v>
-      </c>
       <c r="P26">
         <v>5</v>
       </c>
       <c r="Q26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z26">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB26">
+        <v>6</v>
+      </c>
+      <c r="AC26">
+        <v>8</v>
+      </c>
+      <c r="AD26">
+        <v>6</v>
+      </c>
+      <c r="AE26">
         <v>9</v>
       </c>
-      <c r="AC26">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:29">
+      <c r="AF26">
+        <v>5</v>
+      </c>
+      <c r="AG26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27">
         <v>5</v>
@@ -2912,7 +3204,7 @@
         <v>7</v>
       </c>
       <c r="I27">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J27">
         <v>5</v>
@@ -2921,13 +3213,13 @@
         <v>5</v>
       </c>
       <c r="L27">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O27">
         <v>5</v>
@@ -2936,31 +3228,31 @@
         <v>5</v>
       </c>
       <c r="Q27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S27">
+        <v>7</v>
+      </c>
+      <c r="T27">
+        <v>7</v>
+      </c>
+      <c r="U27">
         <v>3</v>
       </c>
-      <c r="T27">
-        <v>7</v>
-      </c>
-      <c r="U27">
-        <v>8</v>
-      </c>
       <c r="V27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W27">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z27">
         <v>5</v>
@@ -2974,10 +3266,22 @@
       <c r="AC27">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:29">
+      <c r="AD27">
+        <v>6</v>
+      </c>
+      <c r="AE27">
+        <v>6</v>
+      </c>
+      <c r="AF27">
+        <v>5</v>
+      </c>
+      <c r="AG27">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:33">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28">
         <v>8</v>
@@ -3001,72 +3305,84 @@
         <v>7</v>
       </c>
       <c r="I28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K28">
+        <v>5</v>
+      </c>
+      <c r="L28">
         <v>4</v>
       </c>
-      <c r="L28">
-        <v>7</v>
-      </c>
       <c r="M28">
+        <v>7</v>
+      </c>
+      <c r="N28">
         <v>9</v>
       </c>
-      <c r="N28">
-        <v>10</v>
-      </c>
       <c r="O28">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P28">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T28">
         <v>9</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V28">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X28">
         <v>6</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA28">
+        <v>6</v>
+      </c>
+      <c r="AB28">
+        <v>6</v>
+      </c>
+      <c r="AC28">
+        <v>8</v>
+      </c>
+      <c r="AD28">
         <v>9</v>
       </c>
-      <c r="AB28">
-        <v>10</v>
-      </c>
-      <c r="AC28">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:29">
+      <c r="AE28">
+        <v>10</v>
+      </c>
+      <c r="AF28">
+        <v>6</v>
+      </c>
+      <c r="AG28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29">
         <v>5</v>
@@ -3090,7 +3406,7 @@
         <v>6</v>
       </c>
       <c r="I29">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J29">
         <v>5</v>
@@ -3114,31 +3430,31 @@
         <v>5</v>
       </c>
       <c r="Q29">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R29">
+        <v>5</v>
+      </c>
+      <c r="S29">
+        <v>5</v>
+      </c>
+      <c r="T29">
         <v>0</v>
       </c>
-      <c r="S29">
+      <c r="U29">
         <v>3</v>
       </c>
-      <c r="T29">
-        <v>5</v>
-      </c>
-      <c r="U29">
+      <c r="V29">
+        <v>5</v>
+      </c>
+      <c r="W29">
         <v>0</v>
       </c>
-      <c r="V29">
-        <v>5</v>
-      </c>
-      <c r="W29">
-        <v>5</v>
-      </c>
       <c r="X29">
         <v>5</v>
       </c>
       <c r="Y29">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z29">
         <v>5</v>
@@ -3152,10 +3468,22 @@
       <c r="AC29">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="1:29">
+      <c r="AD29">
+        <v>5</v>
+      </c>
+      <c r="AE29">
+        <v>5</v>
+      </c>
+      <c r="AF29">
+        <v>5</v>
+      </c>
+      <c r="AG29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30">
         <v>8</v>
@@ -3179,55 +3507,55 @@
         <v>6</v>
       </c>
       <c r="I30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L30">
         <v>6</v>
       </c>
       <c r="M30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N30">
         <v>10</v>
       </c>
       <c r="O30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R30">
+        <v>7</v>
+      </c>
+      <c r="S30">
+        <v>8</v>
+      </c>
+      <c r="T30">
         <v>9</v>
       </c>
-      <c r="S30">
-        <v>8</v>
-      </c>
-      <c r="T30">
-        <v>8</v>
-      </c>
       <c r="U30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z30">
         <v>7</v>
@@ -3236,15 +3564,27 @@
         <v>8</v>
       </c>
       <c r="AB30">
+        <v>7</v>
+      </c>
+      <c r="AC30">
+        <v>7</v>
+      </c>
+      <c r="AD30">
+        <v>8</v>
+      </c>
+      <c r="AE30">
         <v>9</v>
       </c>
-      <c r="AC30">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:29">
+      <c r="AF30">
+        <v>6</v>
+      </c>
+      <c r="AG30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31">
         <v>5</v>
@@ -3268,7 +3608,7 @@
         <v>6</v>
       </c>
       <c r="I31">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J31">
         <v>5</v>
@@ -3277,49 +3617,49 @@
         <v>5</v>
       </c>
       <c r="L31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M31">
         <v>7</v>
       </c>
       <c r="N31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P31">
         <v>5</v>
       </c>
       <c r="Q31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S31">
+        <v>7</v>
+      </c>
+      <c r="T31">
+        <v>7</v>
+      </c>
+      <c r="U31">
         <v>3</v>
       </c>
-      <c r="T31">
-        <v>7</v>
-      </c>
-      <c r="U31">
-        <v>7</v>
-      </c>
       <c r="V31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA31">
         <v>6</v>
@@ -3328,12 +3668,24 @@
         <v>6</v>
       </c>
       <c r="AC31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD31">
+        <v>6</v>
+      </c>
+      <c r="AE31">
+        <v>6</v>
+      </c>
+      <c r="AF31">
+        <v>5</v>
+      </c>
+      <c r="AG31">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33">
       <c r="A32" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B32">
         <v>8</v>
@@ -3357,17 +3709,17 @@
         <v>7</v>
       </c>
       <c r="I32">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K32">
+        <v>7</v>
+      </c>
+      <c r="L32">
         <v>4</v>
       </c>
-      <c r="L32">
-        <v>6</v>
-      </c>
       <c r="M32">
         <v>6</v>
       </c>
@@ -3375,54 +3727,66 @@
         <v>6</v>
       </c>
       <c r="O32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T32">
+        <v>5</v>
+      </c>
+      <c r="U32">
+        <v>7</v>
+      </c>
+      <c r="V32">
         <v>9</v>
       </c>
-      <c r="U32">
-        <v>10</v>
-      </c>
-      <c r="V32">
-        <v>6</v>
-      </c>
       <c r="W32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y32">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA32">
         <v>7</v>
       </c>
       <c r="AB32">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC32">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD32">
+        <v>7</v>
+      </c>
+      <c r="AE32">
+        <v>8</v>
+      </c>
+      <c r="AF32">
+        <v>6</v>
+      </c>
+      <c r="AG32">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:33">
       <c r="A33" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B33">
         <v>5</v>
@@ -3446,72 +3810,84 @@
         <v>7</v>
       </c>
       <c r="I33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K33">
         <v>5</v>
       </c>
       <c r="L33">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O33">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S33">
+        <v>7</v>
+      </c>
+      <c r="T33">
+        <v>7</v>
+      </c>
+      <c r="U33">
         <v>9</v>
       </c>
-      <c r="T33">
-        <v>7</v>
-      </c>
-      <c r="U33">
-        <v>10</v>
-      </c>
       <c r="V33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W33">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="X33">
         <v>6</v>
       </c>
       <c r="Y33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z33">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AA33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB33">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC33">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:29">
+        <v>10</v>
+      </c>
+      <c r="AD33">
+        <v>7</v>
+      </c>
+      <c r="AE33">
+        <v>8</v>
+      </c>
+      <c r="AF33">
+        <v>6</v>
+      </c>
+      <c r="AG33">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33">
       <c r="A34" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B34">
         <v>5</v>
@@ -3535,17 +3911,17 @@
         <v>5</v>
       </c>
       <c r="I34">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J34">
         <v>5</v>
       </c>
       <c r="K34">
+        <v>5</v>
+      </c>
+      <c r="L34">
         <v>0</v>
       </c>
-      <c r="L34">
-        <v>5</v>
-      </c>
       <c r="M34">
         <v>5</v>
       </c>
@@ -3559,17 +3935,17 @@
         <v>5</v>
       </c>
       <c r="Q34">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R34">
+        <v>5</v>
+      </c>
+      <c r="S34">
+        <v>5</v>
+      </c>
+      <c r="T34">
         <v>0</v>
       </c>
-      <c r="S34">
-        <v>5</v>
-      </c>
-      <c r="T34">
-        <v>5</v>
-      </c>
       <c r="U34">
         <v>5</v>
       </c>
@@ -3583,7 +3959,7 @@
         <v>5</v>
       </c>
       <c r="Y34">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z34">
         <v>5</v>
@@ -3597,10 +3973,22 @@
       <c r="AC34">
         <v>5</v>
       </c>
-    </row>
-    <row r="35" spans="1:29">
+      <c r="AD34">
+        <v>5</v>
+      </c>
+      <c r="AE34">
+        <v>5</v>
+      </c>
+      <c r="AF34">
+        <v>5</v>
+      </c>
+      <c r="AG34">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:33">
       <c r="A35" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B35">
         <v>8</v>
@@ -3624,72 +4012,84 @@
         <v>7</v>
       </c>
       <c r="I35">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L35">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N35">
         <v>10</v>
       </c>
       <c r="O35">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q35">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="S35">
+        <v>7</v>
+      </c>
+      <c r="T35">
+        <v>10</v>
+      </c>
+      <c r="U35">
         <v>9</v>
       </c>
-      <c r="T35">
-        <v>7</v>
-      </c>
-      <c r="U35">
-        <v>10</v>
-      </c>
       <c r="V35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W35">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y35">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z35">
+        <v>7</v>
+      </c>
+      <c r="AA35">
+        <v>7</v>
+      </c>
+      <c r="AB35">
+        <v>7</v>
+      </c>
+      <c r="AC35">
         <v>9</v>
       </c>
-      <c r="AA35">
+      <c r="AD35">
         <v>9</v>
       </c>
-      <c r="AB35">
-        <v>10</v>
-      </c>
-      <c r="AC35">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:29">
+      <c r="AE35">
+        <v>10</v>
+      </c>
+      <c r="AF35">
+        <v>6</v>
+      </c>
+      <c r="AG35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33">
       <c r="A36" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B36">
         <v>5</v>
@@ -3713,72 +4113,84 @@
         <v>5</v>
       </c>
       <c r="I36">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K36">
+        <v>7</v>
+      </c>
+      <c r="L36">
         <v>4</v>
       </c>
-      <c r="L36">
-        <v>5</v>
-      </c>
       <c r="M36">
         <v>5</v>
       </c>
       <c r="N36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P36">
         <v>5</v>
       </c>
       <c r="Q36">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R36">
+        <v>5</v>
+      </c>
+      <c r="S36">
+        <v>7</v>
+      </c>
+      <c r="T36">
         <v>4</v>
       </c>
-      <c r="S36">
-        <v>7</v>
-      </c>
-      <c r="T36">
-        <v>8</v>
-      </c>
       <c r="U36">
         <v>7</v>
       </c>
       <c r="V36">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y36">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC36">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD36">
+        <v>6</v>
+      </c>
+      <c r="AE36">
+        <v>7</v>
+      </c>
+      <c r="AF36">
+        <v>5</v>
+      </c>
+      <c r="AG36">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:33">
       <c r="A37" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B37">
         <v>8</v>
@@ -3802,72 +4214,84 @@
         <v>8</v>
       </c>
       <c r="I37">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J37">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K37">
         <v>6</v>
       </c>
       <c r="L37">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N37">
         <v>10</v>
       </c>
       <c r="O37">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P37">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q37">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="S37">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T37">
+        <v>10</v>
+      </c>
+      <c r="U37">
+        <v>10</v>
+      </c>
+      <c r="V37">
         <v>9</v>
       </c>
-      <c r="U37">
-        <v>10</v>
-      </c>
-      <c r="V37">
-        <v>6</v>
-      </c>
       <c r="W37">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y37">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z37">
+        <v>8</v>
+      </c>
+      <c r="AA37">
+        <v>7</v>
+      </c>
+      <c r="AB37">
+        <v>8</v>
+      </c>
+      <c r="AC37">
         <v>9</v>
       </c>
-      <c r="AA37">
+      <c r="AD37">
         <v>9</v>
       </c>
-      <c r="AB37">
-        <v>10</v>
-      </c>
-      <c r="AC37">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:29">
+      <c r="AE37">
+        <v>10</v>
+      </c>
+      <c r="AF37">
+        <v>7</v>
+      </c>
+      <c r="AG37">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:33">
       <c r="A38" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B38">
         <v>5</v>
@@ -3891,55 +4315,55 @@
         <v>6</v>
       </c>
       <c r="I38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J38">
         <v>6</v>
       </c>
       <c r="K38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L38">
         <v>5</v>
       </c>
       <c r="M38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N38">
         <v>6</v>
       </c>
       <c r="O38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P38">
         <v>5</v>
       </c>
       <c r="Q38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R38">
+        <v>5</v>
+      </c>
+      <c r="S38">
+        <v>6</v>
+      </c>
+      <c r="T38">
         <v>4</v>
       </c>
-      <c r="S38">
+      <c r="U38">
         <v>3</v>
       </c>
-      <c r="T38">
-        <v>7</v>
-      </c>
-      <c r="U38">
-        <v>7</v>
-      </c>
       <c r="V38">
         <v>7</v>
       </c>
       <c r="W38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y38">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z38">
         <v>5</v>
@@ -3948,15 +4372,27 @@
         <v>6</v>
       </c>
       <c r="AB38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC38">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:29">
+        <v>5</v>
+      </c>
+      <c r="AD38">
+        <v>6</v>
+      </c>
+      <c r="AE38">
+        <v>6</v>
+      </c>
+      <c r="AF38">
+        <v>6</v>
+      </c>
+      <c r="AG38">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:33">
       <c r="A39" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B39">
         <v>5</v>
@@ -3980,75 +4416,87 @@
         <v>5</v>
       </c>
       <c r="I39">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K39">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L39">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M39">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P39">
         <v>5</v>
       </c>
       <c r="Q39">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T39">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V39">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W39">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="X39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y39">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z39">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB39">
+        <v>5</v>
+      </c>
+      <c r="AC39">
+        <v>8</v>
+      </c>
+      <c r="AD39">
+        <v>6</v>
+      </c>
+      <c r="AE39">
         <v>9</v>
       </c>
-      <c r="AC39">
-        <v>5</v>
+      <c r="AF39">
+        <v>5</v>
+      </c>
+      <c r="AG39">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="P1:V1"/>
-    <mergeCell ref="W1:AC1"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="R1:Y1"/>
+    <mergeCell ref="Z1:AG1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4056,16 +4504,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V39"/>
+  <dimension ref="A1:Y39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:25">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -4073,26 +4521,29 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="J1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
+      <c r="R1" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:22">
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+    </row>
+    <row r="2" spans="1:25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -4118,56 +4569,65 @@
         <v>11</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="O2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="U2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="V2" s="1" t="s">
+      <c r="W2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:22">
+      <c r="Y2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
       <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>80</v>
@@ -4191,51 +4651,60 @@
         <v>70</v>
       </c>
       <c r="I4">
+        <v>100</v>
+      </c>
+      <c r="J4">
         <v>65</v>
       </c>
-      <c r="J4">
-        <v>100</v>
-      </c>
       <c r="K4">
+        <v>100</v>
+      </c>
+      <c r="L4">
         <v>50</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>45.5</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>82.5</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>50</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>35</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
+        <v>100</v>
+      </c>
+      <c r="R4">
         <v>41.9</v>
       </c>
-      <c r="Q4">
-        <v>100</v>
-      </c>
-      <c r="R4">
+      <c r="S4">
+        <v>100</v>
+      </c>
+      <c r="T4">
         <v>34.4</v>
-      </c>
-      <c r="S4">
-        <v>31.3</v>
-      </c>
-      <c r="T4">
-        <v>55</v>
       </c>
       <c r="U4">
         <v>31.3</v>
       </c>
       <c r="V4">
+        <v>55</v>
+      </c>
+      <c r="W4">
+        <v>31.3</v>
+      </c>
+      <c r="X4">
         <v>21.9</v>
       </c>
-    </row>
-    <row r="5" spans="1:22">
+      <c r="Y4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>60</v>
@@ -4259,51 +4728,60 @@
         <v>0</v>
       </c>
       <c r="I5">
+        <v>100</v>
+      </c>
+      <c r="J5">
         <v>40</v>
       </c>
-      <c r="J5">
-        <v>100</v>
-      </c>
       <c r="K5">
+        <v>100</v>
+      </c>
+      <c r="L5">
         <v>50</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>3</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>0</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>40</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>0</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
+        <v>100</v>
+      </c>
+      <c r="R5">
         <v>25.8</v>
       </c>
-      <c r="Q5">
-        <v>100</v>
-      </c>
-      <c r="R5">
+      <c r="S5">
+        <v>100</v>
+      </c>
+      <c r="T5">
         <v>34.4</v>
       </c>
-      <c r="S5">
+      <c r="U5">
         <v>2.1</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>25</v>
       </c>
       <c r="V5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:22">
+      <c r="W5">
+        <v>25</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>90</v>
@@ -4327,17 +4805,17 @@
         <v>100</v>
       </c>
       <c r="I6">
+        <v>100</v>
+      </c>
+      <c r="J6">
         <v>95</v>
       </c>
-      <c r="J6">
-        <v>100</v>
-      </c>
       <c r="K6">
+        <v>100</v>
+      </c>
+      <c r="L6">
         <v>93.2</v>
       </c>
-      <c r="L6">
-        <v>100</v>
-      </c>
       <c r="M6">
         <v>100</v>
       </c>
@@ -4345,33 +4823,42 @@
         <v>100</v>
       </c>
       <c r="O6">
+        <v>100</v>
+      </c>
+      <c r="P6">
         <v>97.5</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
+        <v>100</v>
+      </c>
+      <c r="R6">
         <v>96.8</v>
       </c>
-      <c r="Q6">
-        <v>100</v>
-      </c>
-      <c r="R6">
+      <c r="S6">
+        <v>100</v>
+      </c>
+      <c r="T6">
         <v>87.5</v>
       </c>
-      <c r="S6">
-        <v>100</v>
-      </c>
-      <c r="T6">
-        <v>100</v>
-      </c>
       <c r="U6">
         <v>100</v>
       </c>
       <c r="V6">
+        <v>100</v>
+      </c>
+      <c r="W6">
+        <v>100</v>
+      </c>
+      <c r="X6">
         <v>89.09999999999999</v>
       </c>
-    </row>
-    <row r="7" spans="1:22">
+      <c r="Y6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>100</v>
@@ -4395,17 +4882,17 @@
         <v>85</v>
       </c>
       <c r="I7">
+        <v>100</v>
+      </c>
+      <c r="J7">
         <v>90</v>
       </c>
-      <c r="J7">
-        <v>100</v>
-      </c>
       <c r="K7">
+        <v>100</v>
+      </c>
+      <c r="L7">
         <v>90.90000000000001</v>
       </c>
-      <c r="L7">
-        <v>100</v>
-      </c>
       <c r="M7">
         <v>100</v>
       </c>
@@ -4413,33 +4900,42 @@
         <v>100</v>
       </c>
       <c r="O7">
+        <v>100</v>
+      </c>
+      <c r="P7">
         <v>85</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
+        <v>100</v>
+      </c>
+      <c r="R7">
         <v>93.5</v>
       </c>
-      <c r="Q7">
-        <v>100</v>
-      </c>
-      <c r="R7">
+      <c r="S7">
+        <v>100</v>
+      </c>
+      <c r="T7">
         <v>89.09999999999999</v>
       </c>
-      <c r="S7">
-        <v>100</v>
-      </c>
-      <c r="T7">
-        <v>100</v>
-      </c>
       <c r="U7">
         <v>100</v>
       </c>
       <c r="V7">
+        <v>100</v>
+      </c>
+      <c r="W7">
+        <v>100</v>
+      </c>
+      <c r="X7">
         <v>84.40000000000001</v>
       </c>
-    </row>
-    <row r="8" spans="1:22">
+      <c r="Y7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>100</v>
@@ -4463,17 +4959,17 @@
         <v>95</v>
       </c>
       <c r="I8">
+        <v>100</v>
+      </c>
+      <c r="J8">
         <v>90</v>
       </c>
-      <c r="J8">
-        <v>100</v>
-      </c>
       <c r="K8">
+        <v>100</v>
+      </c>
+      <c r="L8">
         <v>95.5</v>
       </c>
-      <c r="L8">
-        <v>100</v>
-      </c>
       <c r="M8">
         <v>100</v>
       </c>
@@ -4481,33 +4977,42 @@
         <v>100</v>
       </c>
       <c r="O8">
+        <v>100</v>
+      </c>
+      <c r="P8">
         <v>90</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
+        <v>100</v>
+      </c>
+      <c r="R8">
         <v>93.5</v>
       </c>
-      <c r="Q8">
-        <v>100</v>
-      </c>
-      <c r="R8">
+      <c r="S8">
+        <v>100</v>
+      </c>
+      <c r="T8">
         <v>95.3</v>
       </c>
-      <c r="S8">
-        <v>100</v>
-      </c>
-      <c r="T8">
-        <v>100</v>
-      </c>
       <c r="U8">
+        <v>100</v>
+      </c>
+      <c r="V8">
+        <v>100</v>
+      </c>
+      <c r="W8">
         <v>95.8</v>
       </c>
-      <c r="V8">
+      <c r="X8">
         <v>87.5</v>
       </c>
-    </row>
-    <row r="9" spans="1:22">
+      <c r="Y8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>60</v>
@@ -4531,51 +5036,60 @@
         <v>70</v>
       </c>
       <c r="I9">
+        <v>100</v>
+      </c>
+      <c r="J9">
         <v>60</v>
       </c>
-      <c r="J9">
-        <v>100</v>
-      </c>
       <c r="K9">
+        <v>100</v>
+      </c>
+      <c r="L9">
         <v>68.2</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>87.90000000000001</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>87.5</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>80</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>70</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
+        <v>100</v>
+      </c>
+      <c r="R9">
         <v>45.2</v>
       </c>
-      <c r="Q9">
-        <v>100</v>
-      </c>
-      <c r="R9">
+      <c r="S9">
+        <v>100</v>
+      </c>
+      <c r="T9">
         <v>57.8</v>
       </c>
-      <c r="S9">
+      <c r="U9">
         <v>91.7</v>
       </c>
-      <c r="T9">
+      <c r="V9">
         <v>91.7</v>
       </c>
-      <c r="U9">
+      <c r="W9">
         <v>60.4</v>
       </c>
-      <c r="V9">
+      <c r="X9">
         <v>50</v>
       </c>
-    </row>
-    <row r="10" spans="1:22">
+      <c r="Y9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>80</v>
@@ -4599,11 +5113,11 @@
         <v>100</v>
       </c>
       <c r="I10">
+        <v>100</v>
+      </c>
+      <c r="J10">
         <v>90</v>
       </c>
-      <c r="J10">
-        <v>100</v>
-      </c>
       <c r="K10">
         <v>100</v>
       </c>
@@ -4620,14 +5134,14 @@
         <v>100</v>
       </c>
       <c r="P10">
+        <v>100</v>
+      </c>
+      <c r="Q10">
+        <v>100</v>
+      </c>
+      <c r="R10">
         <v>93.5</v>
       </c>
-      <c r="Q10">
-        <v>100</v>
-      </c>
-      <c r="R10">
-        <v>100</v>
-      </c>
       <c r="S10">
         <v>100</v>
       </c>
@@ -4640,10 +5154,19 @@
       <c r="V10">
         <v>100</v>
       </c>
-    </row>
-    <row r="11" spans="1:22">
+      <c r="W10">
+        <v>100</v>
+      </c>
+      <c r="X10">
+        <v>100</v>
+      </c>
+      <c r="Y10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>90</v>
@@ -4667,51 +5190,60 @@
         <v>70</v>
       </c>
       <c r="I11">
+        <v>100</v>
+      </c>
+      <c r="J11">
         <v>85</v>
       </c>
-      <c r="J11">
-        <v>100</v>
-      </c>
       <c r="K11">
+        <v>100</v>
+      </c>
+      <c r="L11">
         <v>88.59999999999999</v>
       </c>
-      <c r="L11">
-        <v>100</v>
-      </c>
       <c r="M11">
+        <v>100</v>
+      </c>
+      <c r="N11">
         <v>95</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>93.3</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>82.5</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
+        <v>100</v>
+      </c>
+      <c r="R11">
         <v>90.3</v>
       </c>
-      <c r="Q11">
-        <v>100</v>
-      </c>
-      <c r="R11">
+      <c r="S11">
+        <v>100</v>
+      </c>
+      <c r="T11">
         <v>87.5</v>
       </c>
-      <c r="S11">
-        <v>100</v>
-      </c>
-      <c r="T11">
+      <c r="U11">
+        <v>100</v>
+      </c>
+      <c r="V11">
         <v>96.7</v>
       </c>
-      <c r="U11">
+      <c r="W11">
         <v>95.8</v>
       </c>
-      <c r="V11">
+      <c r="X11">
         <v>85.90000000000001</v>
       </c>
-    </row>
-    <row r="12" spans="1:22">
+      <c r="Y11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>90</v>
@@ -4735,51 +5267,60 @@
         <v>100</v>
       </c>
       <c r="I12">
+        <v>100</v>
+      </c>
+      <c r="J12">
         <v>85</v>
       </c>
-      <c r="J12">
-        <v>100</v>
-      </c>
       <c r="K12">
+        <v>100</v>
+      </c>
+      <c r="L12">
         <v>79.5</v>
       </c>
-      <c r="L12">
-        <v>100</v>
-      </c>
       <c r="M12">
+        <v>100</v>
+      </c>
+      <c r="N12">
         <v>87.5</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>96.7</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>92.5</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
+        <v>100</v>
+      </c>
+      <c r="R12">
         <v>87.09999999999999</v>
       </c>
-      <c r="Q12">
-        <v>100</v>
-      </c>
-      <c r="R12">
+      <c r="S12">
+        <v>100</v>
+      </c>
+      <c r="T12">
         <v>81.3</v>
       </c>
-      <c r="S12">
-        <v>100</v>
-      </c>
-      <c r="T12">
+      <c r="U12">
+        <v>100</v>
+      </c>
+      <c r="V12">
         <v>90</v>
       </c>
-      <c r="U12">
+      <c r="W12">
         <v>97.90000000000001</v>
       </c>
-      <c r="V12">
+      <c r="X12">
         <v>85.90000000000001</v>
       </c>
-    </row>
-    <row r="13" spans="1:22">
+      <c r="Y12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>100</v>
@@ -4803,51 +5344,60 @@
         <v>95</v>
       </c>
       <c r="I13">
+        <v>100</v>
+      </c>
+      <c r="J13">
         <v>85</v>
       </c>
-      <c r="J13">
-        <v>100</v>
-      </c>
       <c r="K13">
+        <v>100</v>
+      </c>
+      <c r="L13">
         <v>90.90000000000001</v>
       </c>
-      <c r="L13">
-        <v>100</v>
-      </c>
       <c r="M13">
+        <v>100</v>
+      </c>
+      <c r="N13">
         <v>87.5</v>
       </c>
-      <c r="N13">
-        <v>100</v>
-      </c>
       <c r="O13">
+        <v>100</v>
+      </c>
+      <c r="P13">
         <v>92.5</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
+        <v>100</v>
+      </c>
+      <c r="R13">
         <v>87.09999999999999</v>
       </c>
-      <c r="Q13">
-        <v>100</v>
-      </c>
-      <c r="R13">
+      <c r="S13">
+        <v>100</v>
+      </c>
+      <c r="T13">
         <v>92.2</v>
       </c>
-      <c r="S13">
-        <v>100</v>
-      </c>
-      <c r="T13">
+      <c r="U13">
+        <v>100</v>
+      </c>
+      <c r="V13">
         <v>91.7</v>
       </c>
-      <c r="U13">
+      <c r="W13">
         <v>97.90000000000001</v>
       </c>
-      <c r="V13">
+      <c r="X13">
         <v>95.3</v>
       </c>
-    </row>
-    <row r="14" spans="1:22">
+      <c r="Y13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>100</v>
@@ -4877,45 +5427,54 @@
         <v>100</v>
       </c>
       <c r="K14">
+        <v>100</v>
+      </c>
+      <c r="L14">
         <v>93.2</v>
       </c>
-      <c r="L14">
-        <v>100</v>
-      </c>
       <c r="M14">
+        <v>100</v>
+      </c>
+      <c r="N14">
         <v>95</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>93.3</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>97.5</v>
       </c>
-      <c r="P14">
-        <v>100</v>
-      </c>
       <c r="Q14">
         <v>100</v>
       </c>
       <c r="R14">
+        <v>100</v>
+      </c>
+      <c r="S14">
+        <v>100</v>
+      </c>
+      <c r="T14">
         <v>90.59999999999999</v>
       </c>
-      <c r="S14">
-        <v>100</v>
-      </c>
-      <c r="T14">
+      <c r="U14">
+        <v>100</v>
+      </c>
+      <c r="V14">
         <v>96.7</v>
       </c>
-      <c r="U14">
+      <c r="W14">
         <v>95.8</v>
       </c>
-      <c r="V14">
+      <c r="X14">
         <v>98.40000000000001</v>
       </c>
-    </row>
-    <row r="15" spans="1:22">
+      <c r="Y14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>50</v>
@@ -4939,51 +5498,60 @@
         <v>20</v>
       </c>
       <c r="I15">
+        <v>100</v>
+      </c>
+      <c r="J15">
         <v>35</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>83.3</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>50</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>6.1</v>
       </c>
-      <c r="M15">
-        <v>5</v>
-      </c>
       <c r="N15">
+        <v>5</v>
+      </c>
+      <c r="O15">
         <v>0</v>
       </c>
-      <c r="O15">
-        <v>10</v>
-      </c>
       <c r="P15">
+        <v>10</v>
+      </c>
+      <c r="Q15">
+        <v>100</v>
+      </c>
+      <c r="R15">
         <v>22.6</v>
       </c>
-      <c r="Q15">
+      <c r="S15">
         <v>75.59999999999999</v>
       </c>
-      <c r="R15">
+      <c r="T15">
         <v>34.4</v>
       </c>
-      <c r="S15">
+      <c r="U15">
         <v>4.2</v>
       </c>
-      <c r="T15">
+      <c r="V15">
         <v>3.3</v>
       </c>
-      <c r="U15">
+      <c r="W15">
         <v>0</v>
       </c>
-      <c r="V15">
+      <c r="X15">
         <v>6.3</v>
       </c>
-    </row>
-    <row r="16" spans="1:22">
+      <c r="Y15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>100</v>
@@ -5007,51 +5575,60 @@
         <v>70</v>
       </c>
       <c r="I16">
+        <v>100</v>
+      </c>
+      <c r="J16">
         <v>90</v>
       </c>
-      <c r="J16">
-        <v>100</v>
-      </c>
       <c r="K16">
+        <v>100</v>
+      </c>
+      <c r="L16">
         <v>81.8</v>
       </c>
-      <c r="L16">
-        <v>100</v>
-      </c>
       <c r="M16">
+        <v>100</v>
+      </c>
+      <c r="N16">
         <v>87.5</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>93.3</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>80</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
+        <v>100</v>
+      </c>
+      <c r="R16">
         <v>58.1</v>
       </c>
-      <c r="Q16">
-        <v>100</v>
-      </c>
-      <c r="R16">
+      <c r="S16">
+        <v>100</v>
+      </c>
+      <c r="T16">
         <v>82.8</v>
       </c>
-      <c r="S16">
-        <v>100</v>
-      </c>
-      <c r="T16">
+      <c r="U16">
+        <v>100</v>
+      </c>
+      <c r="V16">
         <v>90</v>
       </c>
-      <c r="U16">
+      <c r="W16">
         <v>95.8</v>
       </c>
-      <c r="V16">
+      <c r="X16">
         <v>68.8</v>
       </c>
-    </row>
-    <row r="17" spans="1:22">
+      <c r="Y16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>100</v>
@@ -5075,17 +5652,17 @@
         <v>100</v>
       </c>
       <c r="I17">
+        <v>100</v>
+      </c>
+      <c r="J17">
         <v>90</v>
       </c>
-      <c r="J17">
-        <v>100</v>
-      </c>
       <c r="K17">
+        <v>100</v>
+      </c>
+      <c r="L17">
         <v>84.09999999999999</v>
       </c>
-      <c r="L17">
-        <v>100</v>
-      </c>
       <c r="M17">
         <v>100</v>
       </c>
@@ -5093,33 +5670,42 @@
         <v>100</v>
       </c>
       <c r="O17">
+        <v>100</v>
+      </c>
+      <c r="P17">
         <v>82.5</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
+        <v>100</v>
+      </c>
+      <c r="R17">
         <v>93.5</v>
       </c>
-      <c r="Q17">
-        <v>100</v>
-      </c>
-      <c r="R17">
+      <c r="S17">
+        <v>100</v>
+      </c>
+      <c r="T17">
         <v>81.3</v>
       </c>
-      <c r="S17">
-        <v>100</v>
-      </c>
-      <c r="T17">
-        <v>100</v>
-      </c>
       <c r="U17">
         <v>100</v>
       </c>
       <c r="V17">
+        <v>100</v>
+      </c>
+      <c r="W17">
+        <v>100</v>
+      </c>
+      <c r="X17">
         <v>82.8</v>
       </c>
-    </row>
-    <row r="18" spans="1:22">
+      <c r="Y17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>100</v>
@@ -5143,51 +5729,60 @@
         <v>70</v>
       </c>
       <c r="I18">
+        <v>100</v>
+      </c>
+      <c r="J18">
         <v>75</v>
       </c>
-      <c r="J18">
-        <v>100</v>
-      </c>
       <c r="K18">
+        <v>100</v>
+      </c>
+      <c r="L18">
         <v>59.1</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>93.90000000000001</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>92.5</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>90</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>75</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
+        <v>100</v>
+      </c>
+      <c r="R18">
         <v>48.4</v>
       </c>
-      <c r="Q18">
-        <v>100</v>
-      </c>
-      <c r="R18">
+      <c r="S18">
+        <v>100</v>
+      </c>
+      <c r="T18">
         <v>40.6</v>
       </c>
-      <c r="S18">
+      <c r="U18">
         <v>95.8</v>
       </c>
-      <c r="T18">
+      <c r="V18">
         <v>93.3</v>
       </c>
-      <c r="U18">
+      <c r="W18">
         <v>93.8</v>
       </c>
-      <c r="V18">
+      <c r="X18">
         <v>73.40000000000001</v>
       </c>
-    </row>
-    <row r="19" spans="1:22">
+      <c r="Y18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>100</v>
@@ -5211,51 +5806,60 @@
         <v>100</v>
       </c>
       <c r="I19">
+        <v>100</v>
+      </c>
+      <c r="J19">
         <v>90</v>
       </c>
-      <c r="J19">
-        <v>100</v>
-      </c>
       <c r="K19">
+        <v>100</v>
+      </c>
+      <c r="L19">
         <v>97.7</v>
       </c>
-      <c r="L19">
-        <v>100</v>
-      </c>
       <c r="M19">
+        <v>100</v>
+      </c>
+      <c r="N19">
         <v>97.5</v>
       </c>
-      <c r="N19">
-        <v>100</v>
-      </c>
       <c r="O19">
+        <v>100</v>
+      </c>
+      <c r="P19">
         <v>95</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
+        <v>100</v>
+      </c>
+      <c r="R19">
         <v>90.3</v>
       </c>
-      <c r="Q19">
-        <v>100</v>
-      </c>
-      <c r="R19">
+      <c r="S19">
+        <v>100</v>
+      </c>
+      <c r="T19">
         <v>93.8</v>
       </c>
-      <c r="S19">
-        <v>100</v>
-      </c>
-      <c r="T19">
+      <c r="U19">
+        <v>100</v>
+      </c>
+      <c r="V19">
         <v>96.7</v>
       </c>
-      <c r="U19">
-        <v>100</v>
-      </c>
-      <c r="V19">
+      <c r="W19">
+        <v>100</v>
+      </c>
+      <c r="X19">
         <v>96.90000000000001</v>
       </c>
-    </row>
-    <row r="20" spans="1:22">
+      <c r="Y19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>100</v>
@@ -5279,17 +5883,17 @@
         <v>100</v>
       </c>
       <c r="I20">
+        <v>100</v>
+      </c>
+      <c r="J20">
         <v>95</v>
       </c>
-      <c r="J20">
-        <v>100</v>
-      </c>
       <c r="K20">
+        <v>100</v>
+      </c>
+      <c r="L20">
         <v>90.90000000000001</v>
       </c>
-      <c r="L20">
-        <v>100</v>
-      </c>
       <c r="M20">
         <v>100</v>
       </c>
@@ -5300,30 +5904,39 @@
         <v>100</v>
       </c>
       <c r="P20">
+        <v>100</v>
+      </c>
+      <c r="Q20">
+        <v>100</v>
+      </c>
+      <c r="R20">
         <v>93.5</v>
       </c>
-      <c r="Q20">
-        <v>100</v>
-      </c>
-      <c r="R20">
+      <c r="S20">
+        <v>100</v>
+      </c>
+      <c r="T20">
         <v>78.09999999999999</v>
       </c>
-      <c r="S20">
-        <v>100</v>
-      </c>
-      <c r="T20">
-        <v>100</v>
-      </c>
       <c r="U20">
         <v>100</v>
       </c>
       <c r="V20">
+        <v>100</v>
+      </c>
+      <c r="W20">
+        <v>100</v>
+      </c>
+      <c r="X20">
         <v>96.90000000000001</v>
       </c>
-    </row>
-    <row r="21" spans="1:22">
+      <c r="Y20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>80</v>
@@ -5347,51 +5960,60 @@
         <v>70</v>
       </c>
       <c r="I21">
+        <v>100</v>
+      </c>
+      <c r="J21">
         <v>70</v>
       </c>
-      <c r="J21">
-        <v>100</v>
-      </c>
       <c r="K21">
+        <v>100</v>
+      </c>
+      <c r="L21">
         <v>75</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>93.90000000000001</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>90</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>83.3</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>72.5</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
+        <v>100</v>
+      </c>
+      <c r="R21">
         <v>45.2</v>
       </c>
-      <c r="Q21">
-        <v>100</v>
-      </c>
-      <c r="R21">
+      <c r="S21">
+        <v>100</v>
+      </c>
+      <c r="T21">
         <v>68.8</v>
       </c>
-      <c r="S21">
+      <c r="U21">
         <v>95.8</v>
       </c>
-      <c r="T21">
+      <c r="V21">
         <v>90</v>
       </c>
-      <c r="U21">
+      <c r="W21">
         <v>85.40000000000001</v>
       </c>
-      <c r="V21">
+      <c r="X21">
         <v>64.09999999999999</v>
       </c>
-    </row>
-    <row r="22" spans="1:22">
+      <c r="Y21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22">
         <v>80</v>
@@ -5415,51 +6037,60 @@
         <v>60</v>
       </c>
       <c r="I22">
+        <v>100</v>
+      </c>
+      <c r="J22">
         <v>85</v>
       </c>
-      <c r="J22">
-        <v>100</v>
-      </c>
       <c r="K22">
+        <v>100</v>
+      </c>
+      <c r="L22">
         <v>81.8</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>93.90000000000001</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>82.5</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>83.3</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>72.5</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
+        <v>100</v>
+      </c>
+      <c r="R22">
         <v>54.8</v>
       </c>
-      <c r="Q22">
-        <v>100</v>
-      </c>
-      <c r="R22">
+      <c r="S22">
+        <v>100</v>
+      </c>
+      <c r="T22">
         <v>64.09999999999999</v>
       </c>
-      <c r="S22">
+      <c r="U22">
         <v>95.8</v>
       </c>
-      <c r="T22">
+      <c r="V22">
         <v>86.7</v>
       </c>
-      <c r="U22">
+      <c r="W22">
         <v>85.40000000000001</v>
       </c>
-      <c r="V22">
+      <c r="X22">
         <v>73.40000000000001</v>
       </c>
-    </row>
-    <row r="23" spans="1:22">
+      <c r="Y22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23">
         <v>90</v>
@@ -5483,51 +6114,60 @@
         <v>60</v>
       </c>
       <c r="I23">
+        <v>100</v>
+      </c>
+      <c r="J23">
         <v>70</v>
       </c>
-      <c r="J23">
-        <v>100</v>
-      </c>
       <c r="K23">
+        <v>100</v>
+      </c>
+      <c r="L23">
         <v>81.8</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>93.90000000000001</v>
       </c>
-      <c r="M23">
-        <v>100</v>
-      </c>
       <c r="N23">
+        <v>100</v>
+      </c>
+      <c r="O23">
         <v>96.7</v>
       </c>
-      <c r="O23">
+      <c r="P23">
         <v>65</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
+        <v>100</v>
+      </c>
+      <c r="R23">
         <v>71</v>
       </c>
-      <c r="Q23">
-        <v>100</v>
-      </c>
-      <c r="R23">
+      <c r="S23">
+        <v>100</v>
+      </c>
+      <c r="T23">
         <v>76.59999999999999</v>
       </c>
-      <c r="S23">
+      <c r="U23">
         <v>95.8</v>
       </c>
-      <c r="T23">
-        <v>100</v>
-      </c>
-      <c r="U23">
+      <c r="V23">
+        <v>100</v>
+      </c>
+      <c r="W23">
         <v>97.90000000000001</v>
       </c>
-      <c r="V23">
+      <c r="X23">
         <v>75</v>
       </c>
-    </row>
-    <row r="24" spans="1:22">
+      <c r="Y23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24">
         <v>90</v>
@@ -5551,51 +6191,60 @@
         <v>60</v>
       </c>
       <c r="I24">
+        <v>100</v>
+      </c>
+      <c r="J24">
         <v>55</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>83.3</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>47.7</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>39.4</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>77.5</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>80</v>
       </c>
-      <c r="O24">
+      <c r="P24">
         <v>30</v>
       </c>
-      <c r="P24">
+      <c r="Q24">
+        <v>100</v>
+      </c>
+      <c r="R24">
         <v>35.5</v>
       </c>
-      <c r="Q24">
+      <c r="S24">
         <v>77.8</v>
       </c>
-      <c r="R24">
+      <c r="T24">
         <v>32.8</v>
       </c>
-      <c r="S24">
+      <c r="U24">
         <v>27.1</v>
       </c>
-      <c r="T24">
+      <c r="V24">
         <v>51.7</v>
       </c>
-      <c r="U24">
+      <c r="W24">
         <v>50</v>
       </c>
-      <c r="V24">
+      <c r="X24">
         <v>18.8</v>
       </c>
-    </row>
-    <row r="25" spans="1:22">
+      <c r="Y24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25">
         <v>80</v>
@@ -5619,51 +6268,60 @@
         <v>75</v>
       </c>
       <c r="I25">
+        <v>100</v>
+      </c>
+      <c r="J25">
         <v>80</v>
       </c>
-      <c r="J25">
-        <v>100</v>
-      </c>
       <c r="K25">
+        <v>100</v>
+      </c>
+      <c r="L25">
         <v>52.3</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>93.90000000000001</v>
       </c>
-      <c r="M25">
+      <c r="N25">
         <v>77.5</v>
       </c>
-      <c r="N25">
+      <c r="O25">
         <v>83.3</v>
       </c>
-      <c r="O25">
+      <c r="P25">
         <v>37.5</v>
       </c>
-      <c r="P25">
+      <c r="Q25">
+        <v>100</v>
+      </c>
+      <c r="R25">
         <v>83.90000000000001</v>
       </c>
-      <c r="Q25">
-        <v>100</v>
-      </c>
-      <c r="R25">
+      <c r="S25">
+        <v>100</v>
+      </c>
+      <c r="T25">
         <v>57.8</v>
       </c>
-      <c r="S25">
+      <c r="U25">
         <v>95.8</v>
       </c>
-      <c r="T25">
+      <c r="V25">
         <v>81.7</v>
       </c>
-      <c r="U25">
+      <c r="W25">
         <v>85.40000000000001</v>
       </c>
-      <c r="V25">
+      <c r="X25">
         <v>54.7</v>
       </c>
-    </row>
-    <row r="26" spans="1:22">
+      <c r="Y25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26">
         <v>90</v>
@@ -5687,51 +6345,60 @@
         <v>90</v>
       </c>
       <c r="I26">
+        <v>100</v>
+      </c>
+      <c r="J26">
         <v>80</v>
       </c>
-      <c r="J26">
-        <v>100</v>
-      </c>
       <c r="K26">
+        <v>100</v>
+      </c>
+      <c r="L26">
         <v>88.59999999999999</v>
       </c>
-      <c r="L26">
-        <v>100</v>
-      </c>
       <c r="M26">
+        <v>100</v>
+      </c>
+      <c r="N26">
         <v>97.5</v>
       </c>
-      <c r="N26">
-        <v>100</v>
-      </c>
       <c r="O26">
+        <v>100</v>
+      </c>
+      <c r="P26">
         <v>95</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
+        <v>100</v>
+      </c>
+      <c r="R26">
         <v>83.90000000000001</v>
       </c>
-      <c r="Q26">
-        <v>100</v>
-      </c>
-      <c r="R26">
+      <c r="S26">
+        <v>100</v>
+      </c>
+      <c r="T26">
         <v>87.5</v>
       </c>
-      <c r="S26">
-        <v>100</v>
-      </c>
-      <c r="T26">
+      <c r="U26">
+        <v>100</v>
+      </c>
+      <c r="V26">
         <v>96.7</v>
       </c>
-      <c r="U26">
-        <v>100</v>
-      </c>
-      <c r="V26">
+      <c r="W26">
+        <v>100</v>
+      </c>
+      <c r="X26">
         <v>87.5</v>
       </c>
-    </row>
-    <row r="27" spans="1:22">
+      <c r="Y26">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27">
         <v>100</v>
@@ -5755,51 +6422,60 @@
         <v>100</v>
       </c>
       <c r="I27">
+        <v>100</v>
+      </c>
+      <c r="J27">
         <v>75</v>
       </c>
-      <c r="J27">
-        <v>100</v>
-      </c>
       <c r="K27">
+        <v>100</v>
+      </c>
+      <c r="L27">
         <v>90.90000000000001</v>
       </c>
-      <c r="L27">
-        <v>100</v>
-      </c>
       <c r="M27">
+        <v>100</v>
+      </c>
+      <c r="N27">
         <v>92.5</v>
       </c>
-      <c r="N27">
+      <c r="O27">
         <v>96.7</v>
       </c>
-      <c r="O27">
+      <c r="P27">
         <v>82.5</v>
       </c>
-      <c r="P27">
+      <c r="Q27">
+        <v>100</v>
+      </c>
+      <c r="R27">
         <v>83.90000000000001</v>
       </c>
-      <c r="Q27">
-        <v>100</v>
-      </c>
-      <c r="R27">
+      <c r="S27">
+        <v>100</v>
+      </c>
+      <c r="T27">
         <v>92.2</v>
       </c>
-      <c r="S27">
-        <v>100</v>
-      </c>
-      <c r="T27">
+      <c r="U27">
+        <v>100</v>
+      </c>
+      <c r="V27">
         <v>95</v>
       </c>
-      <c r="U27">
+      <c r="W27">
         <v>97.90000000000001</v>
       </c>
-      <c r="V27">
+      <c r="X27">
         <v>82.8</v>
       </c>
-    </row>
-    <row r="28" spans="1:22">
+      <c r="Y27">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28">
         <v>100</v>
@@ -5823,51 +6499,60 @@
         <v>100</v>
       </c>
       <c r="I28">
+        <v>100</v>
+      </c>
+      <c r="J28">
         <v>95</v>
       </c>
-      <c r="J28">
-        <v>100</v>
-      </c>
       <c r="K28">
+        <v>100</v>
+      </c>
+      <c r="L28">
         <v>88.59999999999999</v>
       </c>
-      <c r="L28">
-        <v>100</v>
-      </c>
       <c r="M28">
+        <v>100</v>
+      </c>
+      <c r="N28">
         <v>97.5</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>96.7</v>
       </c>
-      <c r="O28">
+      <c r="P28">
         <v>97.5</v>
       </c>
-      <c r="P28">
+      <c r="Q28">
+        <v>100</v>
+      </c>
+      <c r="R28">
         <v>96.8</v>
       </c>
-      <c r="Q28">
-        <v>100</v>
-      </c>
-      <c r="R28">
+      <c r="S28">
+        <v>100</v>
+      </c>
+      <c r="T28">
         <v>89.09999999999999</v>
       </c>
-      <c r="S28">
-        <v>100</v>
-      </c>
-      <c r="T28">
+      <c r="U28">
+        <v>100</v>
+      </c>
+      <c r="V28">
         <v>98.3</v>
       </c>
-      <c r="U28">
+      <c r="W28">
         <v>97.90000000000001</v>
       </c>
-      <c r="V28">
+      <c r="X28">
         <v>98.40000000000001</v>
       </c>
-    </row>
-    <row r="29" spans="1:22">
+      <c r="Y28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29">
         <v>80</v>
@@ -5891,51 +6576,60 @@
         <v>95</v>
       </c>
       <c r="I29">
+        <v>100</v>
+      </c>
+      <c r="J29">
         <v>65</v>
       </c>
-      <c r="J29">
-        <v>100</v>
-      </c>
       <c r="K29">
+        <v>100</v>
+      </c>
+      <c r="L29">
         <v>81.8</v>
       </c>
-      <c r="L29">
-        <v>100</v>
-      </c>
       <c r="M29">
+        <v>100</v>
+      </c>
+      <c r="N29">
         <v>82.5</v>
       </c>
-      <c r="N29">
+      <c r="O29">
         <v>90</v>
       </c>
-      <c r="O29">
+      <c r="P29">
         <v>80</v>
       </c>
-      <c r="P29">
+      <c r="Q29">
+        <v>100</v>
+      </c>
+      <c r="R29">
         <v>41.9</v>
       </c>
-      <c r="Q29">
-        <v>100</v>
-      </c>
-      <c r="R29">
+      <c r="S29">
+        <v>100</v>
+      </c>
+      <c r="T29">
         <v>56.3</v>
       </c>
-      <c r="S29">
-        <v>100</v>
-      </c>
-      <c r="T29">
+      <c r="U29">
+        <v>100</v>
+      </c>
+      <c r="V29">
         <v>86.7</v>
       </c>
-      <c r="U29">
+      <c r="W29">
         <v>56.3</v>
       </c>
-      <c r="V29">
+      <c r="X29">
         <v>50</v>
       </c>
-    </row>
-    <row r="30" spans="1:22">
+      <c r="Y29">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30">
         <v>90</v>
@@ -5959,51 +6653,60 @@
         <v>95</v>
       </c>
       <c r="I30">
+        <v>100</v>
+      </c>
+      <c r="J30">
         <v>75</v>
       </c>
-      <c r="J30">
-        <v>100</v>
-      </c>
       <c r="K30">
+        <v>100</v>
+      </c>
+      <c r="L30">
         <v>93.2</v>
       </c>
-      <c r="L30">
-        <v>100</v>
-      </c>
       <c r="M30">
+        <v>100</v>
+      </c>
+      <c r="N30">
         <v>95</v>
       </c>
-      <c r="N30">
+      <c r="O30">
         <v>96.7</v>
       </c>
-      <c r="O30">
+      <c r="P30">
         <v>90</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
+        <v>100</v>
+      </c>
+      <c r="R30">
         <v>83.90000000000001</v>
       </c>
-      <c r="Q30">
-        <v>100</v>
-      </c>
-      <c r="R30">
+      <c r="S30">
+        <v>100</v>
+      </c>
+      <c r="T30">
         <v>90.59999999999999</v>
       </c>
-      <c r="S30">
-        <v>100</v>
-      </c>
-      <c r="T30">
+      <c r="U30">
+        <v>100</v>
+      </c>
+      <c r="V30">
         <v>96.7</v>
       </c>
-      <c r="U30">
+      <c r="W30">
         <v>97.90000000000001</v>
       </c>
-      <c r="V30">
+      <c r="X30">
         <v>93.8</v>
       </c>
-    </row>
-    <row r="31" spans="1:22">
+      <c r="Y30">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31">
         <v>90</v>
@@ -6027,51 +6730,60 @@
         <v>80</v>
       </c>
       <c r="I31">
+        <v>100</v>
+      </c>
+      <c r="J31">
         <v>75</v>
       </c>
-      <c r="J31">
-        <v>100</v>
-      </c>
       <c r="K31">
+        <v>100</v>
+      </c>
+      <c r="L31">
         <v>93.2</v>
       </c>
-      <c r="L31">
-        <v>100</v>
-      </c>
       <c r="M31">
+        <v>100</v>
+      </c>
+      <c r="N31">
         <v>97.5</v>
       </c>
-      <c r="N31">
+      <c r="O31">
         <v>93.3</v>
       </c>
-      <c r="O31">
+      <c r="P31">
         <v>82.5</v>
       </c>
-      <c r="P31">
+      <c r="Q31">
+        <v>100</v>
+      </c>
+      <c r="R31">
         <v>80.59999999999999</v>
       </c>
-      <c r="Q31">
-        <v>100</v>
-      </c>
-      <c r="R31">
+      <c r="S31">
+        <v>100</v>
+      </c>
+      <c r="T31">
         <v>92.2</v>
       </c>
-      <c r="S31">
-        <v>100</v>
-      </c>
-      <c r="T31">
+      <c r="U31">
+        <v>100</v>
+      </c>
+      <c r="V31">
         <v>96.7</v>
       </c>
-      <c r="U31">
+      <c r="W31">
         <v>95.8</v>
       </c>
-      <c r="V31">
+      <c r="X31">
         <v>85.90000000000001</v>
       </c>
-    </row>
-    <row r="32" spans="1:22">
+      <c r="Y31">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25">
       <c r="A32" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B32">
         <v>90</v>
@@ -6095,51 +6807,60 @@
         <v>100</v>
       </c>
       <c r="I32">
+        <v>100</v>
+      </c>
+      <c r="J32">
         <v>75</v>
       </c>
-      <c r="J32">
-        <v>100</v>
-      </c>
       <c r="K32">
+        <v>100</v>
+      </c>
+      <c r="L32">
         <v>84.09999999999999</v>
       </c>
-      <c r="L32">
-        <v>100</v>
-      </c>
       <c r="M32">
+        <v>100</v>
+      </c>
+      <c r="N32">
         <v>95</v>
       </c>
-      <c r="N32">
+      <c r="O32">
         <v>93.3</v>
       </c>
-      <c r="O32">
+      <c r="P32">
         <v>92.5</v>
       </c>
-      <c r="P32">
+      <c r="Q32">
+        <v>100</v>
+      </c>
+      <c r="R32">
         <v>87.09999999999999</v>
       </c>
-      <c r="Q32">
-        <v>100</v>
-      </c>
-      <c r="R32">
+      <c r="S32">
+        <v>100</v>
+      </c>
+      <c r="T32">
         <v>82.8</v>
       </c>
-      <c r="S32">
-        <v>100</v>
-      </c>
-      <c r="T32">
+      <c r="U32">
+        <v>100</v>
+      </c>
+      <c r="V32">
         <v>96.7</v>
       </c>
-      <c r="U32">
+      <c r="W32">
         <v>95.8</v>
       </c>
-      <c r="V32">
+      <c r="X32">
         <v>92.2</v>
       </c>
-    </row>
-    <row r="33" spans="1:22">
+      <c r="Y32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25">
       <c r="A33" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B33">
         <v>80</v>
@@ -6163,51 +6884,60 @@
         <v>90</v>
       </c>
       <c r="I33">
+        <v>100</v>
+      </c>
+      <c r="J33">
         <v>85</v>
       </c>
-      <c r="J33">
-        <v>100</v>
-      </c>
       <c r="K33">
+        <v>100</v>
+      </c>
+      <c r="L33">
         <v>93.2</v>
       </c>
-      <c r="L33">
-        <v>100</v>
-      </c>
       <c r="M33">
+        <v>100</v>
+      </c>
+      <c r="N33">
         <v>87.5</v>
       </c>
-      <c r="N33">
+      <c r="O33">
         <v>93.3</v>
       </c>
-      <c r="O33">
+      <c r="P33">
         <v>87.5</v>
       </c>
-      <c r="P33">
+      <c r="Q33">
+        <v>100</v>
+      </c>
+      <c r="R33">
         <v>90.3</v>
       </c>
-      <c r="Q33">
-        <v>100</v>
-      </c>
-      <c r="R33">
+      <c r="S33">
+        <v>100</v>
+      </c>
+      <c r="T33">
         <v>92.2</v>
       </c>
-      <c r="S33">
-        <v>100</v>
-      </c>
-      <c r="T33">
+      <c r="U33">
+        <v>100</v>
+      </c>
+      <c r="V33">
         <v>91.7</v>
       </c>
-      <c r="U33">
+      <c r="W33">
         <v>95.8</v>
       </c>
-      <c r="V33">
+      <c r="X33">
         <v>89.09999999999999</v>
       </c>
-    </row>
-    <row r="34" spans="1:22">
+      <c r="Y33">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25">
       <c r="A34" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B34">
         <v>60</v>
@@ -6231,51 +6961,60 @@
         <v>45</v>
       </c>
       <c r="I34">
+        <v>100</v>
+      </c>
+      <c r="J34">
         <v>40</v>
       </c>
-      <c r="J34">
-        <v>100</v>
-      </c>
       <c r="K34">
+        <v>100</v>
+      </c>
+      <c r="L34">
         <v>47.7</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>51.5</v>
       </c>
-      <c r="M34">
+      <c r="N34">
         <v>0</v>
       </c>
-      <c r="N34">
+      <c r="O34">
         <v>83.3</v>
       </c>
-      <c r="O34">
+      <c r="P34">
         <v>22.5</v>
       </c>
-      <c r="P34">
+      <c r="Q34">
+        <v>100</v>
+      </c>
+      <c r="R34">
         <v>25.8</v>
       </c>
-      <c r="Q34">
-        <v>100</v>
-      </c>
-      <c r="R34">
+      <c r="S34">
+        <v>100</v>
+      </c>
+      <c r="T34">
         <v>32.8</v>
       </c>
-      <c r="S34">
+      <c r="U34">
         <v>39.6</v>
       </c>
-      <c r="T34">
+      <c r="V34">
         <v>0</v>
       </c>
-      <c r="U34">
+      <c r="W34">
         <v>85.40000000000001</v>
       </c>
-      <c r="V34">
+      <c r="X34">
         <v>14.1</v>
       </c>
-    </row>
-    <row r="35" spans="1:22">
+      <c r="Y34">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25">
       <c r="A35" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B35">
         <v>100</v>
@@ -6299,51 +7038,60 @@
         <v>100</v>
       </c>
       <c r="I35">
+        <v>100</v>
+      </c>
+      <c r="J35">
         <v>95</v>
       </c>
-      <c r="J35">
-        <v>100</v>
-      </c>
       <c r="K35">
+        <v>100</v>
+      </c>
+      <c r="L35">
         <v>93.2</v>
       </c>
-      <c r="L35">
-        <v>100</v>
-      </c>
       <c r="M35">
+        <v>100</v>
+      </c>
+      <c r="N35">
         <v>97.5</v>
       </c>
-      <c r="N35">
-        <v>100</v>
-      </c>
       <c r="O35">
+        <v>100</v>
+      </c>
+      <c r="P35">
         <v>95</v>
       </c>
-      <c r="P35">
+      <c r="Q35">
+        <v>100</v>
+      </c>
+      <c r="R35">
         <v>96.8</v>
       </c>
-      <c r="Q35">
-        <v>100</v>
-      </c>
-      <c r="R35">
+      <c r="S35">
+        <v>100</v>
+      </c>
+      <c r="T35">
         <v>95.3</v>
       </c>
-      <c r="S35">
-        <v>100</v>
-      </c>
-      <c r="T35">
+      <c r="U35">
+        <v>100</v>
+      </c>
+      <c r="V35">
         <v>98.3</v>
       </c>
-      <c r="U35">
-        <v>100</v>
-      </c>
-      <c r="V35">
+      <c r="W35">
+        <v>100</v>
+      </c>
+      <c r="X35">
         <v>93.8</v>
       </c>
-    </row>
-    <row r="36" spans="1:22">
+      <c r="Y35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25">
       <c r="A36" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B36">
         <v>100</v>
@@ -6367,51 +7115,60 @@
         <v>85</v>
       </c>
       <c r="I36">
+        <v>100</v>
+      </c>
+      <c r="J36">
         <v>60</v>
       </c>
-      <c r="J36">
-        <v>100</v>
-      </c>
       <c r="K36">
+        <v>100</v>
+      </c>
+      <c r="L36">
         <v>84.09999999999999</v>
       </c>
-      <c r="L36">
-        <v>100</v>
-      </c>
       <c r="M36">
+        <v>100</v>
+      </c>
+      <c r="N36">
         <v>90</v>
       </c>
-      <c r="N36">
+      <c r="O36">
         <v>96.7</v>
       </c>
-      <c r="O36">
+      <c r="P36">
         <v>72.5</v>
       </c>
-      <c r="P36">
+      <c r="Q36">
+        <v>100</v>
+      </c>
+      <c r="R36">
         <v>71</v>
       </c>
-      <c r="Q36">
-        <v>100</v>
-      </c>
-      <c r="R36">
+      <c r="S36">
+        <v>100</v>
+      </c>
+      <c r="T36">
         <v>76.59999999999999</v>
       </c>
-      <c r="S36">
-        <v>100</v>
-      </c>
-      <c r="T36">
+      <c r="U36">
+        <v>100</v>
+      </c>
+      <c r="V36">
         <v>91.7</v>
       </c>
-      <c r="U36">
+      <c r="W36">
         <v>97.90000000000001</v>
       </c>
-      <c r="V36">
+      <c r="X36">
         <v>64.09999999999999</v>
       </c>
-    </row>
-    <row r="37" spans="1:22">
+      <c r="Y36">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25">
       <c r="A37" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B37">
         <v>100</v>
@@ -6453,11 +7210,11 @@
         <v>100</v>
       </c>
       <c r="O37">
+        <v>100</v>
+      </c>
+      <c r="P37">
         <v>92.5</v>
       </c>
-      <c r="P37">
-        <v>100</v>
-      </c>
       <c r="Q37">
         <v>100</v>
       </c>
@@ -6474,12 +7231,21 @@
         <v>100</v>
       </c>
       <c r="V37">
+        <v>100</v>
+      </c>
+      <c r="W37">
+        <v>100</v>
+      </c>
+      <c r="X37">
         <v>95.3</v>
       </c>
-    </row>
-    <row r="38" spans="1:22">
+      <c r="Y37">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25">
       <c r="A38" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B38">
         <v>80</v>
@@ -6503,51 +7269,60 @@
         <v>100</v>
       </c>
       <c r="I38">
+        <v>100</v>
+      </c>
+      <c r="J38">
         <v>70</v>
       </c>
-      <c r="J38">
-        <v>100</v>
-      </c>
       <c r="K38">
+        <v>100</v>
+      </c>
+      <c r="L38">
         <v>84.09999999999999</v>
       </c>
-      <c r="L38">
+      <c r="M38">
         <v>93.90000000000001</v>
       </c>
-      <c r="M38">
+      <c r="N38">
         <v>87.5</v>
       </c>
-      <c r="N38">
-        <v>100</v>
-      </c>
       <c r="O38">
+        <v>100</v>
+      </c>
+      <c r="P38">
         <v>85</v>
       </c>
-      <c r="P38">
+      <c r="Q38">
+        <v>100</v>
+      </c>
+      <c r="R38">
         <v>77.40000000000001</v>
       </c>
-      <c r="Q38">
-        <v>100</v>
-      </c>
-      <c r="R38">
+      <c r="S38">
+        <v>100</v>
+      </c>
+      <c r="T38">
         <v>82.8</v>
       </c>
-      <c r="S38">
+      <c r="U38">
         <v>95.8</v>
       </c>
-      <c r="T38">
+      <c r="V38">
         <v>91.7</v>
       </c>
-      <c r="U38">
-        <v>100</v>
-      </c>
-      <c r="V38">
+      <c r="W38">
+        <v>100</v>
+      </c>
+      <c r="X38">
         <v>84.40000000000001</v>
       </c>
-    </row>
-    <row r="39" spans="1:22">
+      <c r="Y38">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25">
       <c r="A39" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B39">
         <v>70</v>
@@ -6571,53 +7346,62 @@
         <v>65</v>
       </c>
       <c r="I39">
+        <v>100</v>
+      </c>
+      <c r="J39">
         <v>80</v>
       </c>
-      <c r="J39">
-        <v>100</v>
-      </c>
       <c r="K39">
+        <v>100</v>
+      </c>
+      <c r="L39">
         <v>75</v>
       </c>
-      <c r="L39">
-        <v>100</v>
-      </c>
       <c r="M39">
+        <v>100</v>
+      </c>
+      <c r="N39">
         <v>92.5</v>
       </c>
-      <c r="N39">
+      <c r="O39">
         <v>93.3</v>
       </c>
-      <c r="O39">
+      <c r="P39">
         <v>77.5</v>
       </c>
-      <c r="P39">
+      <c r="Q39">
+        <v>100</v>
+      </c>
+      <c r="R39">
         <v>87.09999999999999</v>
       </c>
-      <c r="Q39">
-        <v>100</v>
-      </c>
-      <c r="R39">
+      <c r="S39">
+        <v>100</v>
+      </c>
+      <c r="T39">
         <v>75</v>
       </c>
-      <c r="S39">
-        <v>100</v>
-      </c>
-      <c r="T39">
+      <c r="U39">
+        <v>100</v>
+      </c>
+      <c r="V39">
         <v>95</v>
       </c>
-      <c r="U39">
+      <c r="W39">
         <v>95.8</v>
       </c>
-      <c r="V39">
+      <c r="X39">
         <v>82.8</v>
+      </c>
+      <c r="Y39">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="P1:V1"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="R1:Y1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6638,31 +7422,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -6891,21 +7675,33 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>69</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
+      <c r="F9" s="2">
+        <v>100</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>10</v>
+      </c>
       <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6940,7 +7736,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -6974,7 +7770,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>

--- a/grupos/1AV - Estadisticos 20231.xlsx
+++ b/grupos/1AV - Estadisticos 20231.xlsx
@@ -1134,25 +1134,25 @@
         <v>10</v>
       </c>
       <c r="Z6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD6">
         <v>10</v>
       </c>
       <c r="AE6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG6">
         <v>10</v>
@@ -1235,25 +1235,25 @@
         <v>10</v>
       </c>
       <c r="Z7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG7">
         <v>10</v>
@@ -1336,25 +1336,25 @@
         <v>10</v>
       </c>
       <c r="Z8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB8">
         <v>5</v>
       </c>
       <c r="AC8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG8">
         <v>10</v>
@@ -1440,7 +1440,7 @@
         <v>5</v>
       </c>
       <c r="AA9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB9">
         <v>5</v>
@@ -1538,16 +1538,16 @@
         <v>10</v>
       </c>
       <c r="Z10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD10">
         <v>10</v>
@@ -1556,7 +1556,7 @@
         <v>10</v>
       </c>
       <c r="AF10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG10">
         <v>10</v>
@@ -1642,19 +1642,19 @@
         <v>5</v>
       </c>
       <c r="AA11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF11">
         <v>5</v>
@@ -1743,22 +1743,22 @@
         <v>5</v>
       </c>
       <c r="AA12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG12">
         <v>10</v>
@@ -1844,22 +1844,22 @@
         <v>5</v>
       </c>
       <c r="AA13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG13">
         <v>10</v>
@@ -1942,16 +1942,16 @@
         <v>10</v>
       </c>
       <c r="Z14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD14">
         <v>10</v>
@@ -1960,7 +1960,7 @@
         <v>10</v>
       </c>
       <c r="AF14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG14">
         <v>10</v>
@@ -2147,19 +2147,19 @@
         <v>5</v>
       </c>
       <c r="AA16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF16">
         <v>5</v>
@@ -2248,19 +2248,19 @@
         <v>5</v>
       </c>
       <c r="AA17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF17">
         <v>5</v>
@@ -2349,19 +2349,19 @@
         <v>5</v>
       </c>
       <c r="AA18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB18">
         <v>5</v>
       </c>
       <c r="AC18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD18">
         <v>5</v>
       </c>
       <c r="AE18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF18">
         <v>5</v>
@@ -2450,22 +2450,22 @@
         <v>5</v>
       </c>
       <c r="AA19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG19">
         <v>10</v>
@@ -2548,25 +2548,25 @@
         <v>10</v>
       </c>
       <c r="Z20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB20">
         <v>5</v>
       </c>
       <c r="AC20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG20">
         <v>10</v>
@@ -2652,13 +2652,13 @@
         <v>5</v>
       </c>
       <c r="AA21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB21">
         <v>5</v>
       </c>
       <c r="AC21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD21">
         <v>5</v>
@@ -2753,7 +2753,7 @@
         <v>5</v>
       </c>
       <c r="AA22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB22">
         <v>5</v>
@@ -2762,7 +2762,7 @@
         <v>5</v>
       </c>
       <c r="AD22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE22">
         <v>5</v>
@@ -2854,7 +2854,7 @@
         <v>5</v>
       </c>
       <c r="AA23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB23">
         <v>5</v>
@@ -2863,10 +2863,10 @@
         <v>5</v>
       </c>
       <c r="AD23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF23">
         <v>5</v>
@@ -3056,13 +3056,13 @@
         <v>5</v>
       </c>
       <c r="AA25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB25">
         <v>5</v>
       </c>
       <c r="AC25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD25">
         <v>5</v>
@@ -3154,22 +3154,22 @@
         <v>10</v>
       </c>
       <c r="Z26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF26">
         <v>5</v>
@@ -3258,19 +3258,19 @@
         <v>5</v>
       </c>
       <c r="AA27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC27">
         <v>5</v>
       </c>
       <c r="AD27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF27">
         <v>5</v>
@@ -3356,25 +3356,25 @@
         <v>10</v>
       </c>
       <c r="Z28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE28">
         <v>10</v>
       </c>
       <c r="AF28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG28">
         <v>10</v>
@@ -3558,25 +3558,25 @@
         <v>10</v>
       </c>
       <c r="Z30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG30">
         <v>10</v>
@@ -3662,19 +3662,19 @@
         <v>5</v>
       </c>
       <c r="AA31">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB31">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC31">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD31">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE31">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF31">
         <v>5</v>
@@ -3760,25 +3760,25 @@
         <v>10</v>
       </c>
       <c r="Z32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB32">
         <v>5</v>
       </c>
       <c r="AC32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG32">
         <v>10</v>
@@ -3864,22 +3864,22 @@
         <v>5</v>
       </c>
       <c r="AA33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC33">
         <v>10</v>
       </c>
       <c r="AD33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG33">
         <v>10</v>
@@ -4063,25 +4063,25 @@
         <v>10</v>
       </c>
       <c r="Z35">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA35">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB35">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE35">
         <v>10</v>
       </c>
       <c r="AF35">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG35">
         <v>10</v>
@@ -4167,19 +4167,19 @@
         <v>5</v>
       </c>
       <c r="AA36">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB36">
         <v>5</v>
       </c>
       <c r="AC36">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD36">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE36">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF36">
         <v>5</v>
@@ -4265,25 +4265,25 @@
         <v>10</v>
       </c>
       <c r="Z37">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA37">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB37">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE37">
         <v>10</v>
       </c>
       <c r="AF37">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG37">
         <v>10</v>
@@ -4369,7 +4369,7 @@
         <v>5</v>
       </c>
       <c r="AA38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB38">
         <v>5</v>
@@ -4378,13 +4378,13 @@
         <v>5</v>
       </c>
       <c r="AD38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG38">
         <v>10</v>
@@ -4470,19 +4470,19 @@
         <v>5</v>
       </c>
       <c r="AA39">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB39">
         <v>5</v>
       </c>
       <c r="AC39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF39">
         <v>5</v>
@@ -7472,7 +7472,7 @@
         <v>66.7</v>
       </c>
       <c r="H2">
-        <v>5.6</v>
+        <v>6.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7504,7 +7504,7 @@
         <v>55.6</v>
       </c>
       <c r="H3">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7536,7 +7536,7 @@
         <v>50</v>
       </c>
       <c r="H4">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7568,7 +7568,7 @@
         <v>30.6</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7600,7 +7600,7 @@
         <v>27.8</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7632,7 +7632,7 @@
         <v>27.8</v>
       </c>
       <c r="H7">
-        <v>7.1</v>
+        <v>8.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7664,7 +7664,7 @@
         <v>16.7</v>
       </c>
       <c r="H8">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I8">
         <v>0</v>

--- a/grupos/1AV - Estadisticos 20231.xlsx
+++ b/grupos/1AV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="110">
   <si>
     <t>Materia</t>
   </si>
@@ -254,6 +254,9 @@
     <t>NARVAEZ</t>
   </si>
   <si>
+    <t>VERA</t>
+  </si>
+  <si>
     <t>CASTILLO</t>
   </si>
   <si>
@@ -281,6 +284,9 @@
     <t>AUTRAN</t>
   </si>
   <si>
+    <t>VILLA</t>
+  </si>
+  <si>
     <t>DAMIAN</t>
   </si>
   <si>
@@ -315,6 +321,9 @@
   </si>
   <si>
     <t>LAZARO</t>
+  </si>
+  <si>
+    <t>ALEX URIEL</t>
   </si>
   <si>
     <t>JESUS JAREF</t>
@@ -1134,25 +1143,25 @@
         <v>10</v>
       </c>
       <c r="Z6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD6">
         <v>10</v>
       </c>
       <c r="AE6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG6">
         <v>10</v>
@@ -1235,25 +1244,25 @@
         <v>10</v>
       </c>
       <c r="Z7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG7">
         <v>10</v>
@@ -1336,25 +1345,25 @@
         <v>10</v>
       </c>
       <c r="Z8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB8">
         <v>5</v>
       </c>
       <c r="AC8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG8">
         <v>10</v>
@@ -1440,7 +1449,7 @@
         <v>5</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB9">
         <v>5</v>
@@ -1538,16 +1547,16 @@
         <v>10</v>
       </c>
       <c r="Z10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD10">
         <v>10</v>
@@ -1556,7 +1565,7 @@
         <v>10</v>
       </c>
       <c r="AF10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG10">
         <v>10</v>
@@ -1642,19 +1651,19 @@
         <v>5</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF11">
         <v>5</v>
@@ -1743,22 +1752,22 @@
         <v>5</v>
       </c>
       <c r="AA12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG12">
         <v>10</v>
@@ -1844,22 +1853,22 @@
         <v>5</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG13">
         <v>10</v>
@@ -1942,16 +1951,16 @@
         <v>10</v>
       </c>
       <c r="Z14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD14">
         <v>10</v>
@@ -1960,7 +1969,7 @@
         <v>10</v>
       </c>
       <c r="AF14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG14">
         <v>10</v>
@@ -2147,19 +2156,19 @@
         <v>5</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF16">
         <v>5</v>
@@ -2248,19 +2257,19 @@
         <v>5</v>
       </c>
       <c r="AA17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF17">
         <v>5</v>
@@ -2349,19 +2358,19 @@
         <v>5</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB18">
         <v>5</v>
       </c>
       <c r="AC18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD18">
         <v>5</v>
       </c>
       <c r="AE18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF18">
         <v>5</v>
@@ -2450,22 +2459,22 @@
         <v>5</v>
       </c>
       <c r="AA19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG19">
         <v>10</v>
@@ -2548,25 +2557,25 @@
         <v>10</v>
       </c>
       <c r="Z20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB20">
         <v>5</v>
       </c>
       <c r="AC20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG20">
         <v>10</v>
@@ -2652,13 +2661,13 @@
         <v>5</v>
       </c>
       <c r="AA21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB21">
         <v>5</v>
       </c>
       <c r="AC21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD21">
         <v>5</v>
@@ -2753,7 +2762,7 @@
         <v>5</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB22">
         <v>5</v>
@@ -2762,7 +2771,7 @@
         <v>5</v>
       </c>
       <c r="AD22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE22">
         <v>5</v>
@@ -2854,7 +2863,7 @@
         <v>5</v>
       </c>
       <c r="AA23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB23">
         <v>5</v>
@@ -2863,10 +2872,10 @@
         <v>5</v>
       </c>
       <c r="AD23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF23">
         <v>5</v>
@@ -3056,13 +3065,13 @@
         <v>5</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB25">
         <v>5</v>
       </c>
       <c r="AC25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD25">
         <v>5</v>
@@ -3154,22 +3163,22 @@
         <v>10</v>
       </c>
       <c r="Z26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF26">
         <v>5</v>
@@ -3258,19 +3267,19 @@
         <v>5</v>
       </c>
       <c r="AA27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC27">
         <v>5</v>
       </c>
       <c r="AD27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF27">
         <v>5</v>
@@ -3356,25 +3365,25 @@
         <v>10</v>
       </c>
       <c r="Z28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE28">
         <v>10</v>
       </c>
       <c r="AF28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG28">
         <v>10</v>
@@ -3558,25 +3567,25 @@
         <v>10</v>
       </c>
       <c r="Z30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG30">
         <v>10</v>
@@ -3662,19 +3671,19 @@
         <v>5</v>
       </c>
       <c r="AA31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF31">
         <v>5</v>
@@ -3760,25 +3769,25 @@
         <v>10</v>
       </c>
       <c r="Z32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB32">
         <v>5</v>
       </c>
       <c r="AC32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG32">
         <v>10</v>
@@ -3864,22 +3873,22 @@
         <v>5</v>
       </c>
       <c r="AA33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC33">
         <v>10</v>
       </c>
       <c r="AD33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG33">
         <v>10</v>
@@ -4063,25 +4072,25 @@
         <v>10</v>
       </c>
       <c r="Z35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE35">
         <v>10</v>
       </c>
       <c r="AF35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG35">
         <v>10</v>
@@ -4167,19 +4176,19 @@
         <v>5</v>
       </c>
       <c r="AA36">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB36">
         <v>5</v>
       </c>
       <c r="AC36">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD36">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE36">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF36">
         <v>5</v>
@@ -4265,25 +4274,25 @@
         <v>10</v>
       </c>
       <c r="Z37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA37">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE37">
         <v>10</v>
       </c>
       <c r="AF37">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG37">
         <v>10</v>
@@ -4369,7 +4378,7 @@
         <v>5</v>
       </c>
       <c r="AA38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB38">
         <v>5</v>
@@ -4378,13 +4387,13 @@
         <v>5</v>
       </c>
       <c r="AD38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG38">
         <v>10</v>
@@ -4470,19 +4479,19 @@
         <v>5</v>
       </c>
       <c r="AA39">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD39">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF39">
         <v>5</v>
@@ -7379,7 +7388,7 @@
         <v>100</v>
       </c>
       <c r="T39">
-        <v>75</v>
+        <v>82.8</v>
       </c>
       <c r="U39">
         <v>100</v>
@@ -7472,7 +7481,7 @@
         <v>66.7</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>5.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7504,7 +7513,7 @@
         <v>55.6</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7524,19 +7533,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4" s="2">
-        <v>50</v>
+        <v>52.8</v>
       </c>
       <c r="G4" s="2">
-        <v>50</v>
+        <v>47.2</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7568,7 +7577,7 @@
         <v>30.6</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7600,7 +7609,7 @@
         <v>27.8</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7632,7 +7641,7 @@
         <v>27.8</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>7.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7664,7 +7673,7 @@
         <v>16.7</v>
       </c>
       <c r="H8">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7746,7 +7755,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7784,10 +7793,10 @@
         <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -7807,10 +7816,10 @@
         <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -7830,10 +7839,10 @@
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -7853,10 +7862,10 @@
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -7876,10 +7885,10 @@
         <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -7899,10 +7908,10 @@
         <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -7922,10 +7931,10 @@
         <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -7945,10 +7954,10 @@
         <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
@@ -7962,22 +7971,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920181</v>
+        <v>23330051920212</v>
       </c>
       <c r="B10" t="s">
         <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7985,22 +7994,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920184</v>
+        <v>23330051920212</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
         <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -8008,22 +8017,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920185</v>
+        <v>23330051920181</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
         <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -8031,16 +8040,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920189</v>
+        <v>23330051920184</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
         <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E13" t="s">
         <v>5</v>
@@ -8054,7 +8063,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920192</v>
+        <v>23330051920185</v>
       </c>
       <c r="B14" t="s">
         <v>81</v>
@@ -8063,13 +8072,13 @@
         <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -8077,22 +8086,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920329</v>
+        <v>23330051920189</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
         <v>92</v>
       </c>
       <c r="D15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -8100,16 +8109,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920203</v>
+        <v>23330051920192</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
         <v>93</v>
       </c>
       <c r="D16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
@@ -8123,7 +8132,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920204</v>
+        <v>23330051920329</v>
       </c>
       <c r="B17" t="s">
         <v>83</v>
@@ -8132,15 +8141,61 @@
         <v>94</v>
       </c>
       <c r="D17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E17" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F17" t="s">
+        <v>63</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>23330051920203</v>
+      </c>
+      <c r="B18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" t="s">
+        <v>95</v>
+      </c>
+      <c r="D18" t="s">
+        <v>108</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s">
+        <v>64</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>23330051920204</v>
+      </c>
+      <c r="B19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" t="s">
+        <v>109</v>
+      </c>
+      <c r="E19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" t="s">
         <v>62</v>
       </c>
-      <c r="G17">
+      <c r="G19">
         <v>5</v>
       </c>
     </row>
